--- a/Sindhi Muslim/Student Attendance/ECE (ROSE)/ECE (ROSE) Monthly Attendance - November-2024.xlsx
+++ b/Sindhi Muslim/Student Attendance/ECE (ROSE)/ECE (ROSE) Monthly Attendance - November-2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Student Attendance\ECE (ROSE)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061449EB-B020-41B2-8899-8D22BFDD2C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF63DA6-626C-4B99-BFA7-B30B22241703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="132">
   <si>
     <t>S.No</t>
   </si>
@@ -403,6 +403,33 @@
   </si>
   <si>
     <t>Anabia</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>SUNDAY - SUNDAY - SUNDAY - SUNDAY - SUNDAY- SUNDAY</t>
+  </si>
+  <si>
+    <t>IQBAL DAY - IQBAL DAY - IQBAL DAY - IQBAL DAY - IQBAL DAY</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Hoorain Noor</t>
+  </si>
+  <si>
+    <t>Muhammad Akram</t>
+  </si>
+  <si>
+    <t>Abdul Hadi</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -486,7 +513,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -502,6 +529,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,7 +613,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -626,11 +659,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="17" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -647,15 +677,41 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -715,13 +771,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1011,7 +1060,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:AP56"/>
+  <dimension ref="A1:AP58"/>
   <sheetFormatPr defaultColWidth="3.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="1" bestFit="1" customWidth="1"/>
@@ -1056,104 +1105,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
-      <c r="V1" s="22"/>
-      <c r="W1" s="22"/>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="22"/>
-      <c r="AB1" s="22"/>
-      <c r="AC1" s="22"/>
-      <c r="AD1" s="22"/>
-      <c r="AE1" s="22"/>
-      <c r="AF1" s="22"/>
-      <c r="AG1" s="22"/>
-      <c r="AH1" s="22"/>
-      <c r="AI1" s="22"/>
-      <c r="AJ1" s="22"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
+      <c r="AB1" s="28"/>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="28"/>
+      <c r="AJ1" s="28"/>
       <c r="AK1" s="19"/>
       <c r="AL1" s="19"/>
     </row>
     <row r="2" spans="1:42" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="21"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="21"/>
-      <c r="W2" s="21"/>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="21"/>
-      <c r="Z2" s="21"/>
-      <c r="AA2" s="21"/>
-      <c r="AB2" s="21"/>
-      <c r="AC2" s="21"/>
-      <c r="AD2" s="21"/>
-      <c r="AE2" s="21"/>
-      <c r="AF2" s="21"/>
-      <c r="AG2" s="21"/>
-      <c r="AH2" s="21"/>
-      <c r="AI2" s="21"/>
-      <c r="AJ2" s="21"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="27"/>
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="27"/>
+      <c r="AB2" s="27"/>
+      <c r="AC2" s="27"/>
+      <c r="AD2" s="27"/>
+      <c r="AE2" s="27"/>
+      <c r="AF2" s="27"/>
+      <c r="AG2" s="27"/>
+      <c r="AH2" s="27"/>
+      <c r="AI2" s="27"/>
+      <c r="AJ2" s="27"/>
       <c r="AK2" s="18"/>
       <c r="AL2" s="18"/>
       <c r="AM2" s="18"/>
     </row>
     <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="26" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -1280,25 +1329,25 @@
         <f t="shared" si="1"/>
         <v>Sun</v>
       </c>
-      <c r="AK3" s="26" t="s">
+      <c r="AK3" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="AL3" s="26" t="s">
+      <c r="AL3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="AM3" s="23" t="s">
+      <c r="AM3" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="AN3" s="25"/>
+      <c r="AN3" s="24"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
     </row>
     <row r="4" spans="1:42" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="27"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
       <c r="F4" s="16">
         <v>45597</v>
       </c>
@@ -1392,8 +1441,8 @@
       <c r="AJ4" s="16">
         <v>45627</v>
       </c>
-      <c r="AK4" s="26"/>
-      <c r="AL4" s="26"/>
+      <c r="AK4" s="25"/>
+      <c r="AL4" s="25"/>
       <c r="AM4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1417,44 +1466,76 @@
       <c r="E5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="28"/>
+      <c r="F5" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="M5" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N5" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="O5" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S5" s="8"/>
       <c r="T5" s="8"/>
       <c r="U5" s="8"/>
-      <c r="V5" s="8"/>
+      <c r="V5" s="29" t="s">
+        <v>125</v>
+      </c>
       <c r="W5" s="8"/>
       <c r="X5" s="8"/>
-      <c r="Y5" s="28"/>
+      <c r="Y5" s="21"/>
       <c r="Z5" s="8"/>
       <c r="AA5" s="8"/>
       <c r="AB5" s="8"/>
-      <c r="AC5" s="8"/>
+      <c r="AC5" s="29" t="s">
+        <v>125</v>
+      </c>
       <c r="AD5" s="8"/>
       <c r="AE5" s="8"/>
-      <c r="AF5" s="28"/>
+      <c r="AF5" s="21"/>
       <c r="AG5" s="8"/>
       <c r="AH5" s="8"/>
       <c r="AI5" s="8"/>
-      <c r="AJ5" s="8"/>
+      <c r="AJ5" s="29" t="s">
+        <v>125</v>
+      </c>
       <c r="AK5" s="5">
         <f t="shared" ref="AK5:AK34" si="2">COUNTIF(F5:AJ5,"P")</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AL5" s="5">
         <f t="shared" ref="AL5:AL34" si="3">COUNTIF(F5:AJ5,"A")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM5" s="5" t="s">
         <v>9</v>
@@ -1467,7 +1548,7 @@
       </c>
       <c r="AP5" s="3"/>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>2</v>
       </c>
@@ -1481,44 +1562,64 @@
       <c r="E6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="28"/>
+      <c r="F6" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H6" s="29"/>
+      <c r="I6" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M6" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="N6" s="30"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>124</v>
+      </c>
       <c r="S6" s="8"/>
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
+      <c r="V6" s="29"/>
       <c r="W6" s="8"/>
       <c r="X6" s="8"/>
-      <c r="Y6" s="28"/>
+      <c r="Y6" s="21"/>
       <c r="Z6" s="8"/>
       <c r="AA6" s="8"/>
       <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
+      <c r="AC6" s="29"/>
       <c r="AD6" s="8"/>
       <c r="AE6" s="8"/>
-      <c r="AF6" s="28"/>
+      <c r="AF6" s="21"/>
       <c r="AG6" s="8"/>
       <c r="AH6" s="8"/>
       <c r="AI6" s="8"/>
-      <c r="AJ6" s="8"/>
+      <c r="AJ6" s="29"/>
       <c r="AK6" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AL6" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM6" s="5" t="s">
         <v>11</v>
@@ -1529,7 +1630,7 @@
       <c r="AO6" s="3"/>
       <c r="AP6" s="3"/>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>3</v>
       </c>
@@ -1543,51 +1644,71 @@
       <c r="E7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="28"/>
+      <c r="F7" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="H7" s="29"/>
+      <c r="I7" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M7" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N7" s="30"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S7" s="8"/>
       <c r="T7" s="8"/>
       <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
+      <c r="V7" s="29"/>
       <c r="W7" s="8"/>
       <c r="X7" s="8"/>
-      <c r="Y7" s="28"/>
+      <c r="Y7" s="21"/>
       <c r="Z7" s="8"/>
       <c r="AA7" s="8"/>
       <c r="AB7" s="8"/>
-      <c r="AC7" s="8"/>
+      <c r="AC7" s="29"/>
       <c r="AD7" s="8"/>
       <c r="AE7" s="8"/>
-      <c r="AF7" s="28"/>
+      <c r="AF7" s="21"/>
       <c r="AG7" s="8"/>
       <c r="AH7" s="8"/>
       <c r="AI7" s="8"/>
-      <c r="AJ7" s="8"/>
+      <c r="AJ7" s="29"/>
       <c r="AK7" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AL7" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM7" s="3"/>
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
       <c r="AP7" s="3"/>
     </row>
-    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>4</v>
       </c>
@@ -1603,53 +1724,73 @@
       <c r="E8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="28"/>
+      <c r="F8" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="H8" s="29"/>
+      <c r="I8" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M8" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N8" s="30"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S8" s="8"/>
       <c r="T8" s="8"/>
       <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
+      <c r="V8" s="29"/>
       <c r="W8" s="8"/>
       <c r="X8" s="8"/>
-      <c r="Y8" s="28"/>
+      <c r="Y8" s="21"/>
       <c r="Z8" s="8"/>
       <c r="AA8" s="8"/>
       <c r="AB8" s="8"/>
-      <c r="AC8" s="8"/>
+      <c r="AC8" s="29"/>
       <c r="AD8" s="8"/>
       <c r="AE8" s="8"/>
-      <c r="AF8" s="28"/>
+      <c r="AF8" s="21"/>
       <c r="AG8" s="8"/>
       <c r="AH8" s="8"/>
       <c r="AI8" s="8"/>
-      <c r="AJ8" s="8"/>
+      <c r="AJ8" s="29"/>
       <c r="AK8" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AL8" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AM8" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM8" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="AN8" s="24"/>
-      <c r="AO8" s="24"/>
-      <c r="AP8" s="25"/>
+      <c r="AN8" s="23"/>
+      <c r="AO8" s="23"/>
+      <c r="AP8" s="24"/>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>5</v>
       </c>
@@ -1665,44 +1806,64 @@
       <c r="E9" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="28"/>
+      <c r="F9" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H9" s="29"/>
+      <c r="I9" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="M9" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="N9" s="30"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>127</v>
+      </c>
       <c r="S9" s="8"/>
       <c r="T9" s="8"/>
       <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
+      <c r="V9" s="29"/>
       <c r="W9" s="8"/>
       <c r="X9" s="8"/>
-      <c r="Y9" s="28"/>
+      <c r="Y9" s="21"/>
       <c r="Z9" s="8"/>
       <c r="AA9" s="8"/>
       <c r="AB9" s="8"/>
-      <c r="AC9" s="8"/>
+      <c r="AC9" s="29"/>
       <c r="AD9" s="8"/>
       <c r="AE9" s="8"/>
-      <c r="AF9" s="28"/>
+      <c r="AF9" s="21"/>
       <c r="AG9" s="8"/>
       <c r="AH9" s="8"/>
       <c r="AI9" s="8"/>
-      <c r="AJ9" s="8"/>
+      <c r="AJ9" s="29"/>
       <c r="AK9" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL9" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM9" s="5" t="s">
         <v>13</v>
@@ -1717,7 +1878,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>6</v>
       </c>
@@ -1733,44 +1894,64 @@
       <c r="E10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="28"/>
+      <c r="F10" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H10" s="29"/>
+      <c r="I10" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M10" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N10" s="30"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="R10" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S10" s="8"/>
       <c r="T10" s="8"/>
       <c r="U10" s="8"/>
-      <c r="V10" s="8"/>
+      <c r="V10" s="29"/>
       <c r="W10" s="8"/>
       <c r="X10" s="8"/>
-      <c r="Y10" s="28"/>
+      <c r="Y10" s="21"/>
       <c r="Z10" s="8"/>
       <c r="AA10" s="8"/>
       <c r="AB10" s="8"/>
-      <c r="AC10" s="8"/>
+      <c r="AC10" s="29"/>
       <c r="AD10" s="8"/>
       <c r="AE10" s="8"/>
-      <c r="AF10" s="28"/>
+      <c r="AF10" s="21"/>
       <c r="AG10" s="8"/>
       <c r="AH10" s="8"/>
       <c r="AI10" s="8"/>
-      <c r="AJ10" s="8"/>
+      <c r="AJ10" s="29"/>
       <c r="AK10" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AL10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM10" s="5" t="s">
         <v>17</v>
@@ -1788,7 +1969,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>7</v>
       </c>
@@ -1804,62 +1985,82 @@
       <c r="E11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="28"/>
+      <c r="F11" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="H11" s="29"/>
+      <c r="I11" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M11" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="N11" s="30"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R11" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S11" s="8"/>
       <c r="T11" s="8"/>
       <c r="U11" s="8"/>
-      <c r="V11" s="8"/>
+      <c r="V11" s="29"/>
       <c r="W11" s="8"/>
       <c r="X11" s="8"/>
-      <c r="Y11" s="28"/>
+      <c r="Y11" s="21"/>
       <c r="Z11" s="8"/>
       <c r="AA11" s="8"/>
       <c r="AB11" s="8"/>
-      <c r="AC11" s="8"/>
+      <c r="AC11" s="29"/>
       <c r="AD11" s="8"/>
       <c r="AE11" s="8"/>
-      <c r="AF11" s="28"/>
+      <c r="AF11" s="21"/>
       <c r="AG11" s="8"/>
       <c r="AH11" s="8"/>
       <c r="AI11" s="8"/>
-      <c r="AJ11" s="8"/>
+      <c r="AJ11" s="29"/>
       <c r="AK11" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AL11" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM11" s="5" t="s">
         <v>18</v>
       </c>
       <c r="AN11" s="9">
         <f>AK6+AK7+AK8+AK11+AK12+AK13+AK15+AK19+AK20+AK21+AK22+AK23+AK24+AK25+AK27+AK28+AK30+AK40</f>
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="AO11" s="9">
         <f>AK5+AK9+AK10+AK14+AK16+AK17+AK18+AK26+AK29+AK31+AK32+AK33+AK34+AK35+AK36+AK37+AK38+AK39+AK41</f>
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="AP11" s="9">
         <f>AN11+AO11</f>
-        <v>0</v>
+        <v>299</v>
       </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>8</v>
       </c>
@@ -1873,62 +2074,82 @@
       <c r="E12" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="28"/>
+      <c r="F12" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="H12" s="29"/>
+      <c r="I12" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J12" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M12" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N12" s="30"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S12" s="8"/>
       <c r="T12" s="8"/>
       <c r="U12" s="8"/>
-      <c r="V12" s="8"/>
+      <c r="V12" s="29"/>
       <c r="W12" s="8"/>
       <c r="X12" s="8"/>
-      <c r="Y12" s="28"/>
+      <c r="Y12" s="21"/>
       <c r="Z12" s="8"/>
       <c r="AA12" s="8"/>
       <c r="AB12" s="8"/>
-      <c r="AC12" s="8"/>
+      <c r="AC12" s="29"/>
       <c r="AD12" s="8"/>
       <c r="AE12" s="8"/>
-      <c r="AF12" s="28"/>
+      <c r="AF12" s="21"/>
       <c r="AG12" s="8"/>
       <c r="AH12" s="8"/>
       <c r="AI12" s="8"/>
-      <c r="AJ12" s="8"/>
+      <c r="AJ12" s="29"/>
       <c r="AK12" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AL12" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM12" s="5" t="s">
         <v>19</v>
       </c>
       <c r="AN12" s="9">
         <f>AN11/AN10</f>
-        <v>0</v>
+        <v>0.31578947368421051</v>
       </c>
       <c r="AO12" s="9">
         <f>AO11/AO10</f>
-        <v>0</v>
+        <v>0.26190476190476192</v>
       </c>
       <c r="AP12" s="9">
         <f>AP11/AP10</f>
-        <v>0</v>
+        <v>0.28749999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>9</v>
       </c>
@@ -1944,51 +2165,71 @@
       <c r="E13" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="28"/>
+      <c r="F13" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="H13" s="29"/>
+      <c r="I13" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M13" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N13" s="30"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R13" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S13" s="8"/>
       <c r="T13" s="8"/>
       <c r="U13" s="8"/>
-      <c r="V13" s="8"/>
+      <c r="V13" s="29"/>
       <c r="W13" s="8"/>
       <c r="X13" s="8"/>
-      <c r="Y13" s="28"/>
+      <c r="Y13" s="21"/>
       <c r="Z13" s="8"/>
       <c r="AA13" s="8"/>
       <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="29"/>
       <c r="AD13" s="8"/>
       <c r="AE13" s="8"/>
-      <c r="AF13" s="28"/>
+      <c r="AF13" s="21"/>
       <c r="AG13" s="8"/>
       <c r="AH13" s="8"/>
       <c r="AI13" s="8"/>
-      <c r="AJ13" s="8"/>
+      <c r="AJ13" s="29"/>
       <c r="AK13" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AL13" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM13" s="3"/>
       <c r="AN13" s="12"/>
       <c r="AO13" s="12"/>
       <c r="AP13" s="12"/>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>10</v>
       </c>
@@ -2004,51 +2245,71 @@
       <c r="E14" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="28"/>
+      <c r="F14" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="H14" s="29"/>
+      <c r="I14" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="M14" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="N14" s="30"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q14" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>124</v>
+      </c>
       <c r="S14" s="8"/>
       <c r="T14" s="8"/>
       <c r="U14" s="8"/>
-      <c r="V14" s="8"/>
+      <c r="V14" s="29"/>
       <c r="W14" s="8"/>
       <c r="X14" s="8"/>
-      <c r="Y14" s="28"/>
+      <c r="Y14" s="21"/>
       <c r="Z14" s="8"/>
       <c r="AA14" s="8"/>
       <c r="AB14" s="8"/>
-      <c r="AC14" s="8"/>
+      <c r="AC14" s="29"/>
       <c r="AD14" s="8"/>
       <c r="AE14" s="8"/>
-      <c r="AF14" s="28"/>
+      <c r="AF14" s="21"/>
       <c r="AG14" s="8"/>
       <c r="AH14" s="8"/>
       <c r="AI14" s="8"/>
-      <c r="AJ14" s="8"/>
+      <c r="AJ14" s="29"/>
       <c r="AK14" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL14" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM14" s="14"/>
       <c r="AN14" s="14"/>
       <c r="AO14" s="14"/>
       <c r="AP14" s="14"/>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>11</v>
       </c>
@@ -2064,51 +2325,71 @@
       <c r="E15" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="28"/>
+      <c r="F15" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H15" s="29"/>
+      <c r="I15" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M15" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N15" s="30"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R15" s="8" t="s">
+        <v>124</v>
+      </c>
       <c r="S15" s="8"/>
       <c r="T15" s="8"/>
       <c r="U15" s="8"/>
-      <c r="V15" s="8"/>
+      <c r="V15" s="29"/>
       <c r="W15" s="8"/>
       <c r="X15" s="8"/>
-      <c r="Y15" s="28"/>
+      <c r="Y15" s="21"/>
       <c r="Z15" s="8"/>
       <c r="AA15" s="8"/>
       <c r="AB15" s="8"/>
-      <c r="AC15" s="8"/>
+      <c r="AC15" s="29"/>
       <c r="AD15" s="8"/>
       <c r="AE15" s="8"/>
-      <c r="AF15" s="28"/>
+      <c r="AF15" s="21"/>
       <c r="AG15" s="8"/>
       <c r="AH15" s="8"/>
       <c r="AI15" s="8"/>
-      <c r="AJ15" s="8"/>
+      <c r="AJ15" s="29"/>
       <c r="AK15" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AL15" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM15" s="3"/>
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
     </row>
-    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>12</v>
       </c>
@@ -2124,53 +2405,73 @@
       <c r="E16" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="28"/>
+      <c r="F16" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H16" s="29"/>
+      <c r="I16" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M16" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N16" s="30"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q16" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S16" s="8"/>
       <c r="T16" s="8"/>
       <c r="U16" s="8"/>
-      <c r="V16" s="8"/>
+      <c r="V16" s="29"/>
       <c r="W16" s="8"/>
       <c r="X16" s="8"/>
-      <c r="Y16" s="28"/>
+      <c r="Y16" s="21"/>
       <c r="Z16" s="8"/>
       <c r="AA16" s="8"/>
       <c r="AB16" s="8"/>
-      <c r="AC16" s="8"/>
+      <c r="AC16" s="29"/>
       <c r="AD16" s="8"/>
       <c r="AE16" s="8"/>
-      <c r="AF16" s="28"/>
+      <c r="AF16" s="21"/>
       <c r="AG16" s="8"/>
       <c r="AH16" s="8"/>
       <c r="AI16" s="8"/>
-      <c r="AJ16" s="8"/>
+      <c r="AJ16" s="29"/>
       <c r="AK16" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL16" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AM16" s="23" t="s">
+      <c r="AM16" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="AN16" s="24"/>
-      <c r="AO16" s="24"/>
-      <c r="AP16" s="25"/>
+      <c r="AN16" s="23"/>
+      <c r="AO16" s="23"/>
+      <c r="AP16" s="24"/>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>13</v>
       </c>
@@ -2186,44 +2487,64 @@
       <c r="E17" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="28"/>
+      <c r="F17" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H17" s="29"/>
+      <c r="I17" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M17" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N17" s="30"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q17" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>124</v>
+      </c>
       <c r="S17" s="8"/>
       <c r="T17" s="8"/>
       <c r="U17" s="8"/>
-      <c r="V17" s="8"/>
+      <c r="V17" s="29"/>
       <c r="W17" s="8"/>
       <c r="X17" s="8"/>
-      <c r="Y17" s="28"/>
+      <c r="Y17" s="21"/>
       <c r="Z17" s="8"/>
       <c r="AA17" s="8"/>
       <c r="AB17" s="8"/>
-      <c r="AC17" s="8"/>
+      <c r="AC17" s="29"/>
       <c r="AD17" s="8"/>
       <c r="AE17" s="8"/>
-      <c r="AF17" s="28"/>
+      <c r="AF17" s="21"/>
       <c r="AG17" s="8"/>
       <c r="AH17" s="8"/>
       <c r="AI17" s="8"/>
-      <c r="AJ17" s="8"/>
+      <c r="AJ17" s="29"/>
       <c r="AK17" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AL17" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM17" s="5" t="s">
         <v>13</v>
@@ -2238,7 +2559,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>14</v>
       </c>
@@ -2254,44 +2575,64 @@
       <c r="E18" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="28"/>
+      <c r="F18" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="H18" s="29"/>
+      <c r="I18" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="M18" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N18" s="30"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q18" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S18" s="8"/>
       <c r="T18" s="8"/>
       <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
+      <c r="V18" s="29"/>
       <c r="W18" s="8"/>
       <c r="X18" s="8"/>
-      <c r="Y18" s="28"/>
+      <c r="Y18" s="21"/>
       <c r="Z18" s="8"/>
       <c r="AA18" s="8"/>
       <c r="AB18" s="8"/>
-      <c r="AC18" s="8"/>
+      <c r="AC18" s="29"/>
       <c r="AD18" s="8"/>
       <c r="AE18" s="8"/>
-      <c r="AF18" s="28"/>
+      <c r="AF18" s="21"/>
       <c r="AG18" s="8"/>
       <c r="AH18" s="8"/>
       <c r="AI18" s="8"/>
-      <c r="AJ18" s="8"/>
+      <c r="AJ18" s="29"/>
       <c r="AK18" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL18" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM18" s="5" t="s">
         <v>17</v>
@@ -2309,7 +2650,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>15</v>
       </c>
@@ -2325,62 +2666,82 @@
       <c r="E19" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="28"/>
+      <c r="F19" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H19" s="29"/>
+      <c r="I19" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M19" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="N19" s="30"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q19" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R19" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S19" s="8"/>
       <c r="T19" s="8"/>
       <c r="U19" s="8"/>
-      <c r="V19" s="8"/>
+      <c r="V19" s="29"/>
       <c r="W19" s="8"/>
       <c r="X19" s="8"/>
-      <c r="Y19" s="28"/>
+      <c r="Y19" s="21"/>
       <c r="Z19" s="8"/>
       <c r="AA19" s="8"/>
       <c r="AB19" s="8"/>
-      <c r="AC19" s="8"/>
+      <c r="AC19" s="29"/>
       <c r="AD19" s="8"/>
       <c r="AE19" s="8"/>
-      <c r="AF19" s="28"/>
+      <c r="AF19" s="21"/>
       <c r="AG19" s="8"/>
       <c r="AH19" s="8"/>
       <c r="AI19" s="8"/>
-      <c r="AJ19" s="8"/>
+      <c r="AJ19" s="29"/>
       <c r="AK19" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AL19" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM19" s="5" t="s">
         <v>20</v>
       </c>
       <c r="AN19" s="9">
         <f>AN18-AN11</f>
-        <v>494</v>
+        <v>338</v>
       </c>
       <c r="AO19" s="9">
         <f>AO18-AO11</f>
-        <v>546</v>
+        <v>403</v>
       </c>
       <c r="AP19" s="9">
         <f>AN19+AO19</f>
-        <v>1040</v>
+        <v>741</v>
       </c>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>16</v>
       </c>
@@ -2396,62 +2757,82 @@
       <c r="E20" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="28"/>
+      <c r="F20" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H20" s="29"/>
+      <c r="I20" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M20" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N20" s="30"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q20" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S20" s="8"/>
       <c r="T20" s="8"/>
       <c r="U20" s="8"/>
-      <c r="V20" s="8"/>
+      <c r="V20" s="29"/>
       <c r="W20" s="8"/>
       <c r="X20" s="8"/>
-      <c r="Y20" s="28"/>
+      <c r="Y20" s="21"/>
       <c r="Z20" s="8"/>
       <c r="AA20" s="8"/>
       <c r="AB20" s="8"/>
-      <c r="AC20" s="8"/>
+      <c r="AC20" s="29"/>
       <c r="AD20" s="8"/>
       <c r="AE20" s="8"/>
-      <c r="AF20" s="28"/>
+      <c r="AF20" s="21"/>
       <c r="AG20" s="8"/>
       <c r="AH20" s="8"/>
       <c r="AI20" s="8"/>
-      <c r="AJ20" s="8"/>
+      <c r="AJ20" s="29"/>
       <c r="AK20" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AL20" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="AN20" s="15">
         <f>AN19/AN18</f>
-        <v>1</v>
+        <v>0.68421052631578949</v>
       </c>
       <c r="AO20" s="15">
         <f>AO19/AO18</f>
-        <v>1</v>
+        <v>0.73809523809523814</v>
       </c>
       <c r="AP20" s="15">
         <f>AP19/AP18</f>
-        <v>1</v>
+        <v>0.71250000000000002</v>
       </c>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>17</v>
       </c>
@@ -2467,47 +2848,67 @@
       <c r="E21" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="8"/>
-      <c r="R21" s="28"/>
+      <c r="F21" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H21" s="29"/>
+      <c r="I21" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M21" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N21" s="30"/>
+      <c r="O21" s="29"/>
+      <c r="P21" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q21" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R21" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S21" s="8"/>
       <c r="T21" s="8"/>
       <c r="U21" s="8"/>
-      <c r="V21" s="8"/>
+      <c r="V21" s="29"/>
       <c r="W21" s="8"/>
       <c r="X21" s="8"/>
-      <c r="Y21" s="28"/>
+      <c r="Y21" s="21"/>
       <c r="Z21" s="8"/>
       <c r="AA21" s="8"/>
       <c r="AB21" s="8"/>
-      <c r="AC21" s="8"/>
+      <c r="AC21" s="29"/>
       <c r="AD21" s="8"/>
       <c r="AE21" s="8"/>
-      <c r="AF21" s="28"/>
+      <c r="AF21" s="21"/>
       <c r="AG21" s="8"/>
       <c r="AH21" s="8"/>
       <c r="AI21" s="8"/>
-      <c r="AJ21" s="8"/>
+      <c r="AJ21" s="29"/>
       <c r="AK21" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL21" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>18</v>
       </c>
@@ -2523,47 +2924,67 @@
       <c r="E22" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8"/>
-      <c r="Q22" s="8"/>
-      <c r="R22" s="28"/>
+      <c r="F22" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H22" s="29"/>
+      <c r="I22" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M22" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N22" s="30"/>
+      <c r="O22" s="29"/>
+      <c r="P22" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q22" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R22" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S22" s="8"/>
       <c r="T22" s="8"/>
       <c r="U22" s="8"/>
-      <c r="V22" s="8"/>
+      <c r="V22" s="29"/>
       <c r="W22" s="8"/>
       <c r="X22" s="8"/>
-      <c r="Y22" s="28"/>
+      <c r="Y22" s="21"/>
       <c r="Z22" s="8"/>
       <c r="AA22" s="8"/>
       <c r="AB22" s="8"/>
-      <c r="AC22" s="8"/>
+      <c r="AC22" s="29"/>
       <c r="AD22" s="8"/>
       <c r="AE22" s="8"/>
-      <c r="AF22" s="28"/>
+      <c r="AF22" s="21"/>
       <c r="AG22" s="8"/>
       <c r="AH22" s="8"/>
       <c r="AI22" s="8"/>
-      <c r="AJ22" s="8"/>
+      <c r="AJ22" s="29"/>
       <c r="AK22" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL22" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>19</v>
       </c>
@@ -2579,47 +3000,67 @@
       <c r="E23" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="8"/>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="28"/>
+      <c r="F23" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H23" s="29"/>
+      <c r="I23" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M23" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N23" s="30"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q23" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R23" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S23" s="8"/>
       <c r="T23" s="8"/>
       <c r="U23" s="8"/>
-      <c r="V23" s="8"/>
+      <c r="V23" s="29"/>
       <c r="W23" s="8"/>
       <c r="X23" s="8"/>
-      <c r="Y23" s="28"/>
+      <c r="Y23" s="21"/>
       <c r="Z23" s="8"/>
       <c r="AA23" s="8"/>
       <c r="AB23" s="8"/>
-      <c r="AC23" s="8"/>
+      <c r="AC23" s="29"/>
       <c r="AD23" s="8"/>
       <c r="AE23" s="8"/>
-      <c r="AF23" s="28"/>
+      <c r="AF23" s="21"/>
       <c r="AG23" s="8"/>
       <c r="AH23" s="8"/>
       <c r="AI23" s="8"/>
-      <c r="AJ23" s="8"/>
+      <c r="AJ23" s="29"/>
       <c r="AK23" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL23" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>20</v>
       </c>
@@ -2635,47 +3076,67 @@
       <c r="E24" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="28"/>
+      <c r="F24" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H24" s="29"/>
+      <c r="I24" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M24" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N24" s="30"/>
+      <c r="O24" s="29"/>
+      <c r="P24" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q24" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R24" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S24" s="8"/>
       <c r="T24" s="8"/>
       <c r="U24" s="8"/>
-      <c r="V24" s="8"/>
+      <c r="V24" s="29"/>
       <c r="W24" s="8"/>
       <c r="X24" s="8"/>
-      <c r="Y24" s="28"/>
+      <c r="Y24" s="21"/>
       <c r="Z24" s="8"/>
       <c r="AA24" s="8"/>
       <c r="AB24" s="8"/>
-      <c r="AC24" s="8"/>
+      <c r="AC24" s="29"/>
       <c r="AD24" s="8"/>
       <c r="AE24" s="8"/>
-      <c r="AF24" s="28"/>
+      <c r="AF24" s="21"/>
       <c r="AG24" s="8"/>
       <c r="AH24" s="8"/>
       <c r="AI24" s="8"/>
-      <c r="AJ24" s="8"/>
+      <c r="AJ24" s="29"/>
       <c r="AK24" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL24" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>21</v>
       </c>
@@ -2691,47 +3152,67 @@
       <c r="E25" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="8"/>
-      <c r="R25" s="28"/>
+      <c r="F25" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H25" s="29"/>
+      <c r="I25" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M25" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="N25" s="30"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q25" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R25" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S25" s="8"/>
       <c r="T25" s="8"/>
       <c r="U25" s="8"/>
-      <c r="V25" s="8"/>
+      <c r="V25" s="29"/>
       <c r="W25" s="8"/>
       <c r="X25" s="8"/>
-      <c r="Y25" s="28"/>
+      <c r="Y25" s="21"/>
       <c r="Z25" s="8"/>
       <c r="AA25" s="8"/>
       <c r="AB25" s="8"/>
-      <c r="AC25" s="8"/>
+      <c r="AC25" s="29"/>
       <c r="AD25" s="8"/>
       <c r="AE25" s="8"/>
-      <c r="AF25" s="28"/>
+      <c r="AF25" s="21"/>
       <c r="AG25" s="8"/>
       <c r="AH25" s="8"/>
       <c r="AI25" s="8"/>
-      <c r="AJ25" s="8"/>
+      <c r="AJ25" s="29"/>
       <c r="AK25" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AL25" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>22</v>
       </c>
@@ -2747,47 +3228,67 @@
       <c r="E26" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="8"/>
-      <c r="R26" s="28"/>
+      <c r="F26" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H26" s="29"/>
+      <c r="I26" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K26" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M26" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N26" s="30"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q26" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R26" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S26" s="8"/>
       <c r="T26" s="8"/>
       <c r="U26" s="8"/>
-      <c r="V26" s="8"/>
+      <c r="V26" s="29"/>
       <c r="W26" s="8"/>
       <c r="X26" s="8"/>
-      <c r="Y26" s="28"/>
+      <c r="Y26" s="21"/>
       <c r="Z26" s="8"/>
       <c r="AA26" s="8"/>
       <c r="AB26" s="8"/>
-      <c r="AC26" s="8"/>
+      <c r="AC26" s="29"/>
       <c r="AD26" s="8"/>
       <c r="AE26" s="8"/>
-      <c r="AF26" s="28"/>
+      <c r="AF26" s="21"/>
       <c r="AG26" s="8"/>
       <c r="AH26" s="8"/>
       <c r="AI26" s="8"/>
-      <c r="AJ26" s="8"/>
+      <c r="AJ26" s="29"/>
       <c r="AK26" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL26" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <v>23</v>
       </c>
@@ -2803,47 +3304,67 @@
       <c r="E27" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="28"/>
+      <c r="F27" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H27" s="29"/>
+      <c r="I27" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K27" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="L27" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="M27" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="N27" s="30"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q27" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="R27" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S27" s="8"/>
       <c r="T27" s="8"/>
       <c r="U27" s="8"/>
-      <c r="V27" s="8"/>
+      <c r="V27" s="29"/>
       <c r="W27" s="8"/>
       <c r="X27" s="8"/>
-      <c r="Y27" s="28"/>
+      <c r="Y27" s="21"/>
       <c r="Z27" s="8"/>
       <c r="AA27" s="8"/>
       <c r="AB27" s="8"/>
-      <c r="AC27" s="8"/>
+      <c r="AC27" s="29"/>
       <c r="AD27" s="8"/>
       <c r="AE27" s="8"/>
-      <c r="AF27" s="28"/>
+      <c r="AF27" s="21"/>
       <c r="AG27" s="8"/>
       <c r="AH27" s="8"/>
       <c r="AI27" s="8"/>
-      <c r="AJ27" s="8"/>
+      <c r="AJ27" s="29"/>
       <c r="AK27" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL27" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <v>24</v>
       </c>
@@ -2859,47 +3380,67 @@
       <c r="E28" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
-      <c r="P28" s="8"/>
-      <c r="Q28" s="8"/>
-      <c r="R28" s="28"/>
+      <c r="F28" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H28" s="29"/>
+      <c r="I28" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K28" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M28" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N28" s="30"/>
+      <c r="O28" s="29"/>
+      <c r="P28" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q28" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R28" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S28" s="8"/>
       <c r="T28" s="8"/>
       <c r="U28" s="8"/>
-      <c r="V28" s="8"/>
+      <c r="V28" s="29"/>
       <c r="W28" s="8"/>
       <c r="X28" s="8"/>
-      <c r="Y28" s="28"/>
+      <c r="Y28" s="21"/>
       <c r="Z28" s="8"/>
       <c r="AA28" s="8"/>
       <c r="AB28" s="8"/>
-      <c r="AC28" s="8"/>
+      <c r="AC28" s="29"/>
       <c r="AD28" s="8"/>
       <c r="AE28" s="8"/>
-      <c r="AF28" s="28"/>
+      <c r="AF28" s="21"/>
       <c r="AG28" s="8"/>
       <c r="AH28" s="8"/>
       <c r="AI28" s="8"/>
-      <c r="AJ28" s="8"/>
+      <c r="AJ28" s="29"/>
       <c r="AK28" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AL28" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>25</v>
       </c>
@@ -2915,47 +3456,67 @@
       <c r="E29" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="8"/>
-      <c r="R29" s="28"/>
+      <c r="F29" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H29" s="29"/>
+      <c r="I29" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K29" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L29" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M29" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N29" s="30"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q29" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R29" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S29" s="8"/>
       <c r="T29" s="8"/>
       <c r="U29" s="8"/>
-      <c r="V29" s="8"/>
+      <c r="V29" s="29"/>
       <c r="W29" s="8"/>
       <c r="X29" s="8"/>
-      <c r="Y29" s="28"/>
+      <c r="Y29" s="21"/>
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8"/>
-      <c r="AC29" s="8"/>
+      <c r="AC29" s="29"/>
       <c r="AD29" s="8"/>
       <c r="AE29" s="8"/>
-      <c r="AF29" s="28"/>
+      <c r="AF29" s="21"/>
       <c r="AG29" s="8"/>
       <c r="AH29" s="8"/>
       <c r="AI29" s="8"/>
-      <c r="AJ29" s="8"/>
+      <c r="AJ29" s="29"/>
       <c r="AK29" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL29" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <v>26</v>
       </c>
@@ -2971,47 +3532,67 @@
       <c r="E30" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="28"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
-      <c r="P30" s="8"/>
-      <c r="Q30" s="8"/>
-      <c r="R30" s="28"/>
+      <c r="F30" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="H30" s="29"/>
+      <c r="I30" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="J30" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K30" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L30" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M30" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N30" s="30"/>
+      <c r="O30" s="29"/>
+      <c r="P30" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q30" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="R30" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S30" s="8"/>
       <c r="T30" s="8"/>
       <c r="U30" s="8"/>
-      <c r="V30" s="8"/>
+      <c r="V30" s="29"/>
       <c r="W30" s="8"/>
       <c r="X30" s="8"/>
-      <c r="Y30" s="28"/>
+      <c r="Y30" s="21"/>
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8"/>
-      <c r="AC30" s="8"/>
+      <c r="AC30" s="29"/>
       <c r="AD30" s="8"/>
       <c r="AE30" s="8"/>
-      <c r="AF30" s="28"/>
+      <c r="AF30" s="21"/>
       <c r="AG30" s="8"/>
       <c r="AH30" s="8"/>
       <c r="AI30" s="8"/>
-      <c r="AJ30" s="8"/>
+      <c r="AJ30" s="29"/>
       <c r="AK30" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AL30" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>27</v>
       </c>
@@ -3027,47 +3608,67 @@
       <c r="E31" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="8"/>
-      <c r="P31" s="8"/>
-      <c r="Q31" s="8"/>
-      <c r="R31" s="28"/>
+      <c r="F31" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H31" s="29"/>
+      <c r="I31" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K31" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L31" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="M31" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="N31" s="30"/>
+      <c r="O31" s="29"/>
+      <c r="P31" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q31" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R31" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S31" s="8"/>
       <c r="T31" s="8"/>
       <c r="U31" s="8"/>
-      <c r="V31" s="8"/>
+      <c r="V31" s="29"/>
       <c r="W31" s="8"/>
       <c r="X31" s="8"/>
-      <c r="Y31" s="28"/>
+      <c r="Y31" s="21"/>
       <c r="Z31" s="8"/>
       <c r="AA31" s="8"/>
       <c r="AB31" s="8"/>
-      <c r="AC31" s="8"/>
+      <c r="AC31" s="29"/>
       <c r="AD31" s="8"/>
       <c r="AE31" s="8"/>
-      <c r="AF31" s="28"/>
+      <c r="AF31" s="21"/>
       <c r="AG31" s="8"/>
       <c r="AH31" s="8"/>
       <c r="AI31" s="8"/>
-      <c r="AJ31" s="8"/>
+      <c r="AJ31" s="29"/>
       <c r="AK31" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AL31" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <v>28</v>
       </c>
@@ -3083,47 +3684,67 @@
       <c r="E32" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8"/>
-      <c r="O32" s="8"/>
-      <c r="P32" s="8"/>
-      <c r="Q32" s="8"/>
-      <c r="R32" s="28"/>
+      <c r="F32" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H32" s="29"/>
+      <c r="I32" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="J32" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="K32" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="L32" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="M32" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N32" s="30"/>
+      <c r="O32" s="29"/>
+      <c r="P32" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q32" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R32" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S32" s="8"/>
       <c r="T32" s="8"/>
       <c r="U32" s="8"/>
-      <c r="V32" s="8"/>
+      <c r="V32" s="29"/>
       <c r="W32" s="8"/>
       <c r="X32" s="8"/>
-      <c r="Y32" s="28"/>
+      <c r="Y32" s="21"/>
       <c r="Z32" s="8"/>
       <c r="AA32" s="8"/>
       <c r="AB32" s="8"/>
-      <c r="AC32" s="8"/>
+      <c r="AC32" s="29"/>
       <c r="AD32" s="8"/>
       <c r="AE32" s="8"/>
-      <c r="AF32" s="28"/>
+      <c r="AF32" s="21"/>
       <c r="AG32" s="8"/>
       <c r="AH32" s="8"/>
       <c r="AI32" s="8"/>
-      <c r="AJ32" s="8"/>
+      <c r="AJ32" s="29"/>
       <c r="AK32" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AL32" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <v>29</v>
       </c>
@@ -3139,47 +3760,67 @@
       <c r="E33" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="8"/>
-      <c r="P33" s="8"/>
-      <c r="Q33" s="8"/>
-      <c r="R33" s="28"/>
+      <c r="F33" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H33" s="29"/>
+      <c r="I33" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J33" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K33" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L33" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M33" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N33" s="30"/>
+      <c r="O33" s="29"/>
+      <c r="P33" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q33" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R33" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S33" s="8"/>
       <c r="T33" s="8"/>
       <c r="U33" s="8"/>
-      <c r="V33" s="8"/>
+      <c r="V33" s="29"/>
       <c r="W33" s="8"/>
       <c r="X33" s="8"/>
-      <c r="Y33" s="28"/>
+      <c r="Y33" s="21"/>
       <c r="Z33" s="8"/>
       <c r="AA33" s="8"/>
       <c r="AB33" s="8"/>
-      <c r="AC33" s="8"/>
+      <c r="AC33" s="29"/>
       <c r="AD33" s="8"/>
       <c r="AE33" s="8"/>
-      <c r="AF33" s="28"/>
+      <c r="AF33" s="21"/>
       <c r="AG33" s="8"/>
       <c r="AH33" s="8"/>
       <c r="AI33" s="8"/>
-      <c r="AJ33" s="8"/>
+      <c r="AJ33" s="29"/>
       <c r="AK33" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL33" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <v>30</v>
       </c>
@@ -3195,47 +3836,67 @@
       <c r="E34" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="8"/>
-      <c r="P34" s="8"/>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="28"/>
+      <c r="F34" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G34" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H34" s="29"/>
+      <c r="I34" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J34" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K34" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L34" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M34" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N34" s="30"/>
+      <c r="O34" s="29"/>
+      <c r="P34" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q34" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R34" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S34" s="8"/>
       <c r="T34" s="8"/>
       <c r="U34" s="8"/>
-      <c r="V34" s="8"/>
+      <c r="V34" s="29"/>
       <c r="W34" s="8"/>
       <c r="X34" s="8"/>
-      <c r="Y34" s="28"/>
+      <c r="Y34" s="21"/>
       <c r="Z34" s="8"/>
       <c r="AA34" s="8"/>
       <c r="AB34" s="8"/>
-      <c r="AC34" s="8"/>
+      <c r="AC34" s="29"/>
       <c r="AD34" s="8"/>
       <c r="AE34" s="8"/>
-      <c r="AF34" s="28"/>
+      <c r="AF34" s="21"/>
       <c r="AG34" s="8"/>
       <c r="AH34" s="8"/>
       <c r="AI34" s="8"/>
-      <c r="AJ34" s="8"/>
+      <c r="AJ34" s="29"/>
       <c r="AK34" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL34" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <v>31</v>
       </c>
@@ -3251,47 +3912,67 @@
       <c r="E35" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8"/>
-      <c r="O35" s="8"/>
-      <c r="P35" s="8"/>
-      <c r="Q35" s="8"/>
-      <c r="R35" s="28"/>
+      <c r="F35" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G35" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H35" s="29"/>
+      <c r="I35" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J35" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K35" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L35" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M35" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N35" s="30"/>
+      <c r="O35" s="29"/>
+      <c r="P35" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q35" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R35" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S35" s="8"/>
       <c r="T35" s="8"/>
       <c r="U35" s="8"/>
-      <c r="V35" s="8"/>
+      <c r="V35" s="29"/>
       <c r="W35" s="8"/>
       <c r="X35" s="8"/>
-      <c r="Y35" s="28"/>
+      <c r="Y35" s="21"/>
       <c r="Z35" s="8"/>
       <c r="AA35" s="8"/>
       <c r="AB35" s="8"/>
-      <c r="AC35" s="8"/>
+      <c r="AC35" s="29"/>
       <c r="AD35" s="8"/>
       <c r="AE35" s="8"/>
-      <c r="AF35" s="28"/>
+      <c r="AF35" s="21"/>
       <c r="AG35" s="8"/>
       <c r="AH35" s="8"/>
       <c r="AI35" s="8"/>
-      <c r="AJ35" s="8"/>
+      <c r="AJ35" s="29"/>
       <c r="AK35" s="5">
         <f t="shared" ref="AK35:AK52" si="4">COUNTIF(F35:AJ35,"P")</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL35" s="5">
         <f t="shared" ref="AL35:AL52" si="5">COUNTIF(F35:AJ35,"A")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <v>32</v>
       </c>
@@ -3307,47 +3988,67 @@
       <c r="E36" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="20"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="8"/>
-      <c r="N36" s="8"/>
-      <c r="O36" s="8"/>
-      <c r="P36" s="8"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="28"/>
+      <c r="F36" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="G36" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H36" s="29"/>
+      <c r="I36" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J36" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K36" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L36" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M36" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N36" s="30"/>
+      <c r="O36" s="29"/>
+      <c r="P36" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q36" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R36" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S36" s="8"/>
       <c r="T36" s="8"/>
       <c r="U36" s="8"/>
-      <c r="V36" s="8"/>
+      <c r="V36" s="29"/>
       <c r="W36" s="8"/>
       <c r="X36" s="8"/>
-      <c r="Y36" s="28"/>
+      <c r="Y36" s="21"/>
       <c r="Z36" s="8"/>
       <c r="AA36" s="8"/>
       <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
+      <c r="AC36" s="29"/>
       <c r="AD36" s="8"/>
       <c r="AE36" s="8"/>
-      <c r="AF36" s="28"/>
+      <c r="AF36" s="21"/>
       <c r="AG36" s="8"/>
       <c r="AH36" s="8"/>
       <c r="AI36" s="8"/>
-      <c r="AJ36" s="8"/>
+      <c r="AJ36" s="29"/>
       <c r="AK36" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AL36" s="5">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>33</v>
       </c>
@@ -3363,47 +4064,67 @@
       <c r="E37" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="8"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="8"/>
-      <c r="P37" s="8"/>
-      <c r="Q37" s="8"/>
-      <c r="R37" s="28"/>
+      <c r="F37" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="G37" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H37" s="29"/>
+      <c r="I37" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J37" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K37" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="L37" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M37" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N37" s="30"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q37" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R37" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S37" s="8"/>
       <c r="T37" s="8"/>
       <c r="U37" s="8"/>
-      <c r="V37" s="8"/>
+      <c r="V37" s="29"/>
       <c r="W37" s="8"/>
       <c r="X37" s="8"/>
-      <c r="Y37" s="28"/>
+      <c r="Y37" s="21"/>
       <c r="Z37" s="8"/>
       <c r="AA37" s="8"/>
       <c r="AB37" s="8"/>
-      <c r="AC37" s="8"/>
+      <c r="AC37" s="29"/>
       <c r="AD37" s="8"/>
       <c r="AE37" s="8"/>
-      <c r="AF37" s="28"/>
+      <c r="AF37" s="21"/>
       <c r="AG37" s="8"/>
       <c r="AH37" s="8"/>
       <c r="AI37" s="8"/>
-      <c r="AJ37" s="8"/>
+      <c r="AJ37" s="29"/>
       <c r="AK37" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AL37" s="5">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <v>34</v>
       </c>
@@ -3419,47 +4140,67 @@
       <c r="E38" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="20"/>
-      <c r="K38" s="28"/>
-      <c r="L38" s="8"/>
-      <c r="M38" s="8"/>
-      <c r="N38" s="8"/>
-      <c r="O38" s="8"/>
-      <c r="P38" s="8"/>
-      <c r="Q38" s="8"/>
-      <c r="R38" s="28"/>
+      <c r="F38" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G38" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="H38" s="29"/>
+      <c r="I38" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J38" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K38" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="L38" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M38" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="N38" s="30"/>
+      <c r="O38" s="29"/>
+      <c r="P38" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q38" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R38" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S38" s="8"/>
       <c r="T38" s="8"/>
       <c r="U38" s="8"/>
-      <c r="V38" s="8"/>
+      <c r="V38" s="29"/>
       <c r="W38" s="8"/>
       <c r="X38" s="8"/>
-      <c r="Y38" s="28"/>
+      <c r="Y38" s="21"/>
       <c r="Z38" s="8"/>
       <c r="AA38" s="8"/>
       <c r="AB38" s="8"/>
-      <c r="AC38" s="8"/>
+      <c r="AC38" s="29"/>
       <c r="AD38" s="8"/>
       <c r="AE38" s="8"/>
-      <c r="AF38" s="28"/>
+      <c r="AF38" s="21"/>
       <c r="AG38" s="8"/>
       <c r="AH38" s="8"/>
       <c r="AI38" s="8"/>
-      <c r="AJ38" s="8"/>
+      <c r="AJ38" s="29"/>
       <c r="AK38" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AL38" s="5">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <v>35</v>
       </c>
@@ -3475,47 +4216,67 @@
       <c r="E39" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="20"/>
-      <c r="K39" s="28"/>
-      <c r="L39" s="8"/>
-      <c r="M39" s="8"/>
-      <c r="N39" s="8"/>
-      <c r="O39" s="8"/>
-      <c r="P39" s="8"/>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="28"/>
+      <c r="F39" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="G39" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="H39" s="29"/>
+      <c r="I39" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="J39" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K39" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="L39" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M39" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N39" s="30"/>
+      <c r="O39" s="29"/>
+      <c r="P39" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q39" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R39" s="8" t="s">
+        <v>124</v>
+      </c>
       <c r="S39" s="8"/>
       <c r="T39" s="8"/>
       <c r="U39" s="8"/>
-      <c r="V39" s="8"/>
+      <c r="V39" s="29"/>
       <c r="W39" s="8"/>
       <c r="X39" s="8"/>
-      <c r="Y39" s="28"/>
+      <c r="Y39" s="21"/>
       <c r="Z39" s="8"/>
       <c r="AA39" s="8"/>
       <c r="AB39" s="8"/>
-      <c r="AC39" s="8"/>
+      <c r="AC39" s="29"/>
       <c r="AD39" s="8"/>
       <c r="AE39" s="8"/>
-      <c r="AF39" s="28"/>
+      <c r="AF39" s="21"/>
       <c r="AG39" s="8"/>
       <c r="AH39" s="8"/>
       <c r="AI39" s="8"/>
-      <c r="AJ39" s="8"/>
+      <c r="AJ39" s="29"/>
       <c r="AK39" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL39" s="5">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
         <v>36</v>
       </c>
@@ -3531,47 +4292,67 @@
       <c r="E40" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="20"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="8"/>
-      <c r="M40" s="8"/>
-      <c r="N40" s="8"/>
-      <c r="O40" s="8"/>
-      <c r="P40" s="8"/>
-      <c r="Q40" s="8"/>
-      <c r="R40" s="28"/>
+      <c r="F40" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H40" s="29"/>
+      <c r="I40" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K40" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L40" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M40" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N40" s="30"/>
+      <c r="O40" s="29"/>
+      <c r="P40" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q40" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R40" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S40" s="8"/>
       <c r="T40" s="8"/>
       <c r="U40" s="8"/>
-      <c r="V40" s="8"/>
+      <c r="V40" s="29"/>
       <c r="W40" s="8"/>
       <c r="X40" s="8"/>
-      <c r="Y40" s="28"/>
+      <c r="Y40" s="21"/>
       <c r="Z40" s="8"/>
       <c r="AA40" s="8"/>
       <c r="AB40" s="8"/>
-      <c r="AC40" s="8"/>
+      <c r="AC40" s="29"/>
       <c r="AD40" s="8"/>
       <c r="AE40" s="8"/>
-      <c r="AF40" s="28"/>
+      <c r="AF40" s="21"/>
       <c r="AG40" s="8"/>
       <c r="AH40" s="8"/>
       <c r="AI40" s="8"/>
-      <c r="AJ40" s="8"/>
+      <c r="AJ40" s="29"/>
       <c r="AK40" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL40" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>37</v>
       </c>
@@ -3585,47 +4366,67 @@
       <c r="E41" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-      <c r="K41" s="28"/>
-      <c r="L41" s="8"/>
-      <c r="M41" s="8"/>
-      <c r="N41" s="8"/>
-      <c r="O41" s="8"/>
-      <c r="P41" s="8"/>
-      <c r="Q41" s="8"/>
-      <c r="R41" s="28"/>
+      <c r="F41" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="G41" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H41" s="29"/>
+      <c r="I41" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J41" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K41" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L41" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M41" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N41" s="30"/>
+      <c r="O41" s="29"/>
+      <c r="P41" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q41" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R41" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S41" s="8"/>
       <c r="T41" s="8"/>
       <c r="U41" s="8"/>
-      <c r="V41" s="8"/>
+      <c r="V41" s="29"/>
       <c r="W41" s="8"/>
       <c r="X41" s="8"/>
-      <c r="Y41" s="28"/>
+      <c r="Y41" s="21"/>
       <c r="Z41" s="8"/>
       <c r="AA41" s="8"/>
       <c r="AB41" s="8"/>
-      <c r="AC41" s="8"/>
+      <c r="AC41" s="29"/>
       <c r="AD41" s="8"/>
       <c r="AE41" s="8"/>
-      <c r="AF41" s="28"/>
+      <c r="AF41" s="21"/>
       <c r="AG41" s="8"/>
       <c r="AH41" s="8"/>
       <c r="AI41" s="8"/>
-      <c r="AJ41" s="8"/>
+      <c r="AJ41" s="29"/>
       <c r="AK41" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AL41" s="5">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
         <v>38</v>
       </c>
@@ -3641,47 +4442,67 @@
       <c r="E42" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="20"/>
-      <c r="J42" s="20"/>
-      <c r="K42" s="28"/>
-      <c r="L42" s="8"/>
-      <c r="M42" s="8"/>
-      <c r="N42" s="8"/>
-      <c r="O42" s="8"/>
-      <c r="P42" s="8"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="28"/>
+      <c r="F42" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G42" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H42" s="29"/>
+      <c r="I42" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J42" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K42" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L42" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M42" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N42" s="30"/>
+      <c r="O42" s="29"/>
+      <c r="P42" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q42" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="R42" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S42" s="8"/>
       <c r="T42" s="8"/>
       <c r="U42" s="8"/>
-      <c r="V42" s="8"/>
+      <c r="V42" s="29"/>
       <c r="W42" s="8"/>
       <c r="X42" s="8"/>
-      <c r="Y42" s="28"/>
+      <c r="Y42" s="21"/>
       <c r="Z42" s="8"/>
       <c r="AA42" s="8"/>
       <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
+      <c r="AC42" s="29"/>
       <c r="AD42" s="8"/>
       <c r="AE42" s="8"/>
-      <c r="AF42" s="28"/>
+      <c r="AF42" s="21"/>
       <c r="AG42" s="8"/>
       <c r="AH42" s="8"/>
       <c r="AI42" s="8"/>
-      <c r="AJ42" s="8"/>
+      <c r="AJ42" s="29"/>
       <c r="AK42" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AL42" s="5">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <v>39</v>
       </c>
@@ -3697,47 +4518,67 @@
       <c r="E43" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="8"/>
-      <c r="M43" s="8"/>
-      <c r="N43" s="8"/>
-      <c r="O43" s="8"/>
-      <c r="P43" s="8"/>
-      <c r="Q43" s="8"/>
-      <c r="R43" s="28"/>
+      <c r="F43" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G43" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H43" s="29"/>
+      <c r="I43" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J43" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K43" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L43" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M43" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N43" s="30"/>
+      <c r="O43" s="29"/>
+      <c r="P43" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q43" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R43" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S43" s="8"/>
       <c r="T43" s="8"/>
       <c r="U43" s="8"/>
-      <c r="V43" s="8"/>
+      <c r="V43" s="29"/>
       <c r="W43" s="8"/>
       <c r="X43" s="8"/>
-      <c r="Y43" s="28"/>
+      <c r="Y43" s="21"/>
       <c r="Z43" s="8"/>
       <c r="AA43" s="8"/>
       <c r="AB43" s="8"/>
-      <c r="AC43" s="8"/>
+      <c r="AC43" s="29"/>
       <c r="AD43" s="8"/>
       <c r="AE43" s="8"/>
-      <c r="AF43" s="28"/>
+      <c r="AF43" s="21"/>
       <c r="AG43" s="8"/>
       <c r="AH43" s="8"/>
       <c r="AI43" s="8"/>
-      <c r="AJ43" s="8"/>
+      <c r="AJ43" s="29"/>
       <c r="AK43" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL43" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A44" s="9">
         <v>40</v>
       </c>
@@ -3753,47 +4594,67 @@
       <c r="E44" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="8"/>
-      <c r="M44" s="8"/>
-      <c r="N44" s="8"/>
-      <c r="O44" s="8"/>
-      <c r="P44" s="8"/>
-      <c r="Q44" s="8"/>
-      <c r="R44" s="28"/>
+      <c r="F44" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="G44" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="H44" s="29"/>
+      <c r="I44" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J44" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K44" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L44" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M44" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N44" s="30"/>
+      <c r="O44" s="29"/>
+      <c r="P44" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q44" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R44" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S44" s="8"/>
       <c r="T44" s="8"/>
       <c r="U44" s="8"/>
-      <c r="V44" s="8"/>
+      <c r="V44" s="29"/>
       <c r="W44" s="8"/>
       <c r="X44" s="8"/>
-      <c r="Y44" s="28"/>
+      <c r="Y44" s="21"/>
       <c r="Z44" s="8"/>
       <c r="AA44" s="8"/>
       <c r="AB44" s="8"/>
-      <c r="AC44" s="8"/>
+      <c r="AC44" s="29"/>
       <c r="AD44" s="8"/>
       <c r="AE44" s="8"/>
-      <c r="AF44" s="28"/>
+      <c r="AF44" s="21"/>
       <c r="AG44" s="8"/>
       <c r="AH44" s="8"/>
       <c r="AI44" s="8"/>
-      <c r="AJ44" s="8"/>
+      <c r="AJ44" s="29"/>
       <c r="AK44" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AL44" s="5">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A45" s="9">
         <v>41</v>
       </c>
@@ -3809,47 +4670,67 @@
       <c r="E45" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="20"/>
-      <c r="K45" s="28"/>
-      <c r="L45" s="8"/>
-      <c r="M45" s="8"/>
-      <c r="N45" s="8"/>
-      <c r="O45" s="8"/>
-      <c r="P45" s="8"/>
-      <c r="Q45" s="8"/>
-      <c r="R45" s="28"/>
+      <c r="F45" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G45" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H45" s="29"/>
+      <c r="I45" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J45" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K45" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L45" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M45" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N45" s="30"/>
+      <c r="O45" s="29"/>
+      <c r="P45" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q45" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R45" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S45" s="8"/>
       <c r="T45" s="8"/>
       <c r="U45" s="8"/>
-      <c r="V45" s="8"/>
+      <c r="V45" s="29"/>
       <c r="W45" s="8"/>
       <c r="X45" s="8"/>
-      <c r="Y45" s="28"/>
+      <c r="Y45" s="21"/>
       <c r="Z45" s="8"/>
       <c r="AA45" s="8"/>
       <c r="AB45" s="8"/>
-      <c r="AC45" s="8"/>
+      <c r="AC45" s="29"/>
       <c r="AD45" s="8"/>
       <c r="AE45" s="8"/>
-      <c r="AF45" s="28"/>
+      <c r="AF45" s="21"/>
       <c r="AG45" s="8"/>
       <c r="AH45" s="8"/>
       <c r="AI45" s="8"/>
-      <c r="AJ45" s="8"/>
+      <c r="AJ45" s="29"/>
       <c r="AK45" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL45" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A46" s="9">
         <v>42</v>
       </c>
@@ -3865,47 +4746,67 @@
       <c r="E46" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="20"/>
-      <c r="I46" s="20"/>
-      <c r="J46" s="20"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="8"/>
-      <c r="M46" s="8"/>
-      <c r="N46" s="8"/>
-      <c r="O46" s="8"/>
-      <c r="P46" s="8"/>
-      <c r="Q46" s="8"/>
-      <c r="R46" s="28"/>
+      <c r="F46" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G46" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H46" s="29"/>
+      <c r="I46" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J46" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K46" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L46" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M46" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N46" s="30"/>
+      <c r="O46" s="29"/>
+      <c r="P46" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q46" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R46" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S46" s="8"/>
       <c r="T46" s="8"/>
       <c r="U46" s="8"/>
-      <c r="V46" s="8"/>
+      <c r="V46" s="29"/>
       <c r="W46" s="8"/>
       <c r="X46" s="8"/>
-      <c r="Y46" s="28"/>
+      <c r="Y46" s="21"/>
       <c r="Z46" s="8"/>
       <c r="AA46" s="8"/>
       <c r="AB46" s="8"/>
-      <c r="AC46" s="8"/>
+      <c r="AC46" s="29"/>
       <c r="AD46" s="8"/>
       <c r="AE46" s="8"/>
-      <c r="AF46" s="28"/>
+      <c r="AF46" s="21"/>
       <c r="AG46" s="8"/>
       <c r="AH46" s="8"/>
       <c r="AI46" s="8"/>
-      <c r="AJ46" s="8"/>
+      <c r="AJ46" s="29"/>
       <c r="AK46" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL46" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
         <v>43</v>
       </c>
@@ -3919,47 +4820,67 @@
       <c r="E47" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="20"/>
-      <c r="K47" s="28"/>
-      <c r="L47" s="8"/>
-      <c r="M47" s="8"/>
-      <c r="N47" s="8"/>
-      <c r="O47" s="8"/>
-      <c r="P47" s="8"/>
-      <c r="Q47" s="8"/>
-      <c r="R47" s="28"/>
+      <c r="F47" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G47" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H47" s="29"/>
+      <c r="I47" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J47" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K47" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L47" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M47" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N47" s="30"/>
+      <c r="O47" s="29"/>
+      <c r="P47" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q47" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R47" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S47" s="8"/>
       <c r="T47" s="8"/>
       <c r="U47" s="8"/>
-      <c r="V47" s="8"/>
+      <c r="V47" s="29"/>
       <c r="W47" s="8"/>
       <c r="X47" s="8"/>
-      <c r="Y47" s="28"/>
+      <c r="Y47" s="21"/>
       <c r="Z47" s="8"/>
       <c r="AA47" s="8"/>
       <c r="AB47" s="8"/>
-      <c r="AC47" s="8"/>
+      <c r="AC47" s="29"/>
       <c r="AD47" s="8"/>
       <c r="AE47" s="8"/>
-      <c r="AF47" s="28"/>
+      <c r="AF47" s="21"/>
       <c r="AG47" s="8"/>
       <c r="AH47" s="8"/>
       <c r="AI47" s="8"/>
-      <c r="AJ47" s="8"/>
+      <c r="AJ47" s="29"/>
       <c r="AK47" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL47" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
         <v>44</v>
       </c>
@@ -3975,47 +4896,67 @@
       <c r="E48" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
-      <c r="H48" s="20"/>
-      <c r="I48" s="20"/>
-      <c r="J48" s="20"/>
-      <c r="K48" s="28"/>
-      <c r="L48" s="8"/>
-      <c r="M48" s="8"/>
-      <c r="N48" s="8"/>
-      <c r="O48" s="8"/>
-      <c r="P48" s="8"/>
-      <c r="Q48" s="8"/>
-      <c r="R48" s="28"/>
+      <c r="F48" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="G48" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H48" s="29"/>
+      <c r="I48" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J48" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K48" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L48" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="M48" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N48" s="30"/>
+      <c r="O48" s="29"/>
+      <c r="P48" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q48" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R48" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S48" s="8"/>
       <c r="T48" s="8"/>
       <c r="U48" s="8"/>
-      <c r="V48" s="8"/>
+      <c r="V48" s="29"/>
       <c r="W48" s="8"/>
       <c r="X48" s="8"/>
-      <c r="Y48" s="28"/>
+      <c r="Y48" s="21"/>
       <c r="Z48" s="8"/>
       <c r="AA48" s="8"/>
       <c r="AB48" s="8"/>
-      <c r="AC48" s="8"/>
+      <c r="AC48" s="29"/>
       <c r="AD48" s="8"/>
       <c r="AE48" s="8"/>
-      <c r="AF48" s="28"/>
+      <c r="AF48" s="21"/>
       <c r="AG48" s="8"/>
       <c r="AH48" s="8"/>
       <c r="AI48" s="8"/>
-      <c r="AJ48" s="8"/>
+      <c r="AJ48" s="29"/>
       <c r="AK48" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AL48" s="5">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>45</v>
       </c>
@@ -4029,47 +4970,67 @@
       <c r="E49" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="20"/>
-      <c r="G49" s="20"/>
-      <c r="H49" s="20"/>
-      <c r="I49" s="20"/>
-      <c r="J49" s="20"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="8"/>
-      <c r="M49" s="8"/>
-      <c r="N49" s="8"/>
-      <c r="O49" s="8"/>
-      <c r="P49" s="8"/>
-      <c r="Q49" s="8"/>
-      <c r="R49" s="28"/>
+      <c r="F49" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="G49" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H49" s="29"/>
+      <c r="I49" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J49" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K49" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L49" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M49" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N49" s="30"/>
+      <c r="O49" s="29"/>
+      <c r="P49" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q49" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R49" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S49" s="8"/>
       <c r="T49" s="8"/>
       <c r="U49" s="8"/>
-      <c r="V49" s="8"/>
+      <c r="V49" s="29"/>
       <c r="W49" s="8"/>
       <c r="X49" s="8"/>
-      <c r="Y49" s="28"/>
+      <c r="Y49" s="21"/>
       <c r="Z49" s="8"/>
       <c r="AA49" s="8"/>
       <c r="AB49" s="8"/>
-      <c r="AC49" s="8"/>
+      <c r="AC49" s="29"/>
       <c r="AD49" s="8"/>
       <c r="AE49" s="8"/>
-      <c r="AF49" s="28"/>
+      <c r="AF49" s="21"/>
       <c r="AG49" s="8"/>
       <c r="AH49" s="8"/>
       <c r="AI49" s="8"/>
-      <c r="AJ49" s="8"/>
+      <c r="AJ49" s="29"/>
       <c r="AK49" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AL49" s="5">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
         <v>46</v>
       </c>
@@ -4083,47 +5044,67 @@
       <c r="E50" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F50" s="20"/>
-      <c r="G50" s="20"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="20"/>
-      <c r="J50" s="20"/>
-      <c r="K50" s="28"/>
-      <c r="L50" s="8"/>
-      <c r="M50" s="8"/>
-      <c r="N50" s="8"/>
-      <c r="O50" s="8"/>
-      <c r="P50" s="8"/>
-      <c r="Q50" s="8"/>
-      <c r="R50" s="28"/>
+      <c r="F50" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="G50" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H50" s="29"/>
+      <c r="I50" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J50" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="K50" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L50" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M50" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N50" s="30"/>
+      <c r="O50" s="29"/>
+      <c r="P50" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q50" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="R50" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S50" s="8"/>
       <c r="T50" s="8"/>
       <c r="U50" s="8"/>
-      <c r="V50" s="8"/>
+      <c r="V50" s="29"/>
       <c r="W50" s="8"/>
       <c r="X50" s="8"/>
-      <c r="Y50" s="28"/>
+      <c r="Y50" s="21"/>
       <c r="Z50" s="8"/>
       <c r="AA50" s="8"/>
       <c r="AB50" s="8"/>
-      <c r="AC50" s="8"/>
+      <c r="AC50" s="29"/>
       <c r="AD50" s="8"/>
       <c r="AE50" s="8"/>
-      <c r="AF50" s="28"/>
+      <c r="AF50" s="21"/>
       <c r="AG50" s="8"/>
       <c r="AH50" s="8"/>
       <c r="AI50" s="8"/>
-      <c r="AJ50" s="8"/>
+      <c r="AJ50" s="29"/>
       <c r="AK50" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AL50" s="5">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
         <v>47</v>
       </c>
@@ -4137,47 +5118,67 @@
       <c r="E51" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F51" s="20"/>
-      <c r="G51" s="20"/>
-      <c r="H51" s="20"/>
-      <c r="I51" s="20"/>
-      <c r="J51" s="20"/>
-      <c r="K51" s="28"/>
-      <c r="L51" s="8"/>
-      <c r="M51" s="8"/>
-      <c r="N51" s="8"/>
-      <c r="O51" s="8"/>
-      <c r="P51" s="8"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="28"/>
+      <c r="F51" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G51" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H51" s="29"/>
+      <c r="I51" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J51" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K51" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L51" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M51" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N51" s="30"/>
+      <c r="O51" s="29"/>
+      <c r="P51" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q51" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R51" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S51" s="8"/>
       <c r="T51" s="8"/>
       <c r="U51" s="8"/>
-      <c r="V51" s="8"/>
+      <c r="V51" s="29"/>
       <c r="W51" s="8"/>
       <c r="X51" s="8"/>
-      <c r="Y51" s="28"/>
+      <c r="Y51" s="21"/>
       <c r="Z51" s="8"/>
       <c r="AA51" s="8"/>
       <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
+      <c r="AC51" s="29"/>
       <c r="AD51" s="8"/>
       <c r="AE51" s="8"/>
-      <c r="AF51" s="28"/>
+      <c r="AF51" s="21"/>
       <c r="AG51" s="8"/>
       <c r="AH51" s="8"/>
       <c r="AI51" s="8"/>
-      <c r="AJ51" s="8"/>
+      <c r="AJ51" s="29"/>
       <c r="AK51" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL51" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
         <v>48</v>
       </c>
@@ -4191,47 +5192,67 @@
       <c r="E52" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="20"/>
-      <c r="I52" s="20"/>
-      <c r="J52" s="20"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="8"/>
-      <c r="M52" s="8"/>
-      <c r="N52" s="8"/>
-      <c r="O52" s="8"/>
-      <c r="P52" s="8"/>
-      <c r="Q52" s="8"/>
-      <c r="R52" s="28"/>
+      <c r="F52" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G52" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H52" s="29"/>
+      <c r="I52" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J52" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K52" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L52" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M52" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N52" s="30"/>
+      <c r="O52" s="29"/>
+      <c r="P52" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q52" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R52" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S52" s="8"/>
       <c r="T52" s="8"/>
       <c r="U52" s="8"/>
-      <c r="V52" s="8"/>
+      <c r="V52" s="29"/>
       <c r="W52" s="8"/>
       <c r="X52" s="8"/>
-      <c r="Y52" s="28"/>
+      <c r="Y52" s="21"/>
       <c r="Z52" s="8"/>
       <c r="AA52" s="8"/>
       <c r="AB52" s="8"/>
-      <c r="AC52" s="8"/>
+      <c r="AC52" s="29"/>
       <c r="AD52" s="8"/>
       <c r="AE52" s="8"/>
-      <c r="AF52" s="28"/>
+      <c r="AF52" s="21"/>
       <c r="AG52" s="8"/>
       <c r="AH52" s="8"/>
       <c r="AI52" s="8"/>
-      <c r="AJ52" s="8"/>
+      <c r="AJ52" s="29"/>
       <c r="AK52" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL52" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <v>49</v>
       </c>
@@ -4245,47 +5266,67 @@
       <c r="E53" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F53" s="20"/>
-      <c r="G53" s="20"/>
-      <c r="H53" s="20"/>
-      <c r="I53" s="20"/>
-      <c r="J53" s="20"/>
-      <c r="K53" s="28"/>
-      <c r="L53" s="8"/>
-      <c r="M53" s="8"/>
-      <c r="N53" s="8"/>
-      <c r="O53" s="8"/>
-      <c r="P53" s="8"/>
-      <c r="Q53" s="8"/>
-      <c r="R53" s="28"/>
+      <c r="F53" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G53" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H53" s="29"/>
+      <c r="I53" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="J53" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K53" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L53" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="M53" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="N53" s="30"/>
+      <c r="O53" s="29"/>
+      <c r="P53" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q53" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R53" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S53" s="8"/>
       <c r="T53" s="8"/>
       <c r="U53" s="8"/>
-      <c r="V53" s="8"/>
+      <c r="V53" s="29"/>
       <c r="W53" s="8"/>
       <c r="X53" s="8"/>
-      <c r="Y53" s="28"/>
+      <c r="Y53" s="21"/>
       <c r="Z53" s="8"/>
       <c r="AA53" s="8"/>
       <c r="AB53" s="8"/>
-      <c r="AC53" s="8"/>
+      <c r="AC53" s="29"/>
       <c r="AD53" s="8"/>
       <c r="AE53" s="8"/>
-      <c r="AF53" s="28"/>
+      <c r="AF53" s="21"/>
       <c r="AG53" s="8"/>
       <c r="AH53" s="8"/>
       <c r="AI53" s="8"/>
-      <c r="AJ53" s="8"/>
+      <c r="AJ53" s="29"/>
       <c r="AK53" s="5">
         <f t="shared" ref="AK53:AK54" si="6">COUNTIF(F53:AJ53,"P")</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AL53" s="5">
         <f t="shared" ref="AL53:AL54" si="7">COUNTIF(F53:AJ53,"A")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <v>50</v>
       </c>
@@ -4299,47 +5340,67 @@
       <c r="E54" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
-      <c r="J54" s="20"/>
-      <c r="K54" s="28"/>
-      <c r="L54" s="8"/>
-      <c r="M54" s="8"/>
-      <c r="N54" s="8"/>
-      <c r="O54" s="8"/>
-      <c r="P54" s="8"/>
-      <c r="Q54" s="8"/>
-      <c r="R54" s="28"/>
+      <c r="F54" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G54" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H54" s="29"/>
+      <c r="I54" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J54" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K54" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L54" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M54" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N54" s="30"/>
+      <c r="O54" s="29"/>
+      <c r="P54" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q54" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R54" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S54" s="8"/>
       <c r="T54" s="8"/>
       <c r="U54" s="8"/>
-      <c r="V54" s="8"/>
+      <c r="V54" s="29"/>
       <c r="W54" s="8"/>
       <c r="X54" s="8"/>
-      <c r="Y54" s="28"/>
+      <c r="Y54" s="21"/>
       <c r="Z54" s="8"/>
       <c r="AA54" s="8"/>
       <c r="AB54" s="8"/>
-      <c r="AC54" s="8"/>
+      <c r="AC54" s="29"/>
       <c r="AD54" s="8"/>
       <c r="AE54" s="8"/>
-      <c r="AF54" s="28"/>
+      <c r="AF54" s="21"/>
       <c r="AG54" s="8"/>
       <c r="AH54" s="8"/>
       <c r="AI54" s="8"/>
-      <c r="AJ54" s="8"/>
+      <c r="AJ54" s="29"/>
       <c r="AK54" s="5">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL54" s="5">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>51</v>
       </c>
@@ -4351,47 +5412,67 @@
       <c r="E55" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F55" s="20"/>
-      <c r="G55" s="20"/>
-      <c r="H55" s="20"/>
-      <c r="I55" s="20"/>
-      <c r="J55" s="20"/>
-      <c r="K55" s="28"/>
-      <c r="L55" s="8"/>
-      <c r="M55" s="8"/>
-      <c r="N55" s="8"/>
-      <c r="O55" s="8"/>
-      <c r="P55" s="8"/>
-      <c r="Q55" s="8"/>
-      <c r="R55" s="28"/>
+      <c r="F55" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G55" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H55" s="29"/>
+      <c r="I55" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J55" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K55" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L55" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="M55" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="N55" s="30"/>
+      <c r="O55" s="29"/>
+      <c r="P55" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q55" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R55" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="S55" s="8"/>
       <c r="T55" s="8"/>
       <c r="U55" s="8"/>
-      <c r="V55" s="8"/>
+      <c r="V55" s="29"/>
       <c r="W55" s="8"/>
       <c r="X55" s="8"/>
-      <c r="Y55" s="28"/>
+      <c r="Y55" s="21"/>
       <c r="Z55" s="8"/>
       <c r="AA55" s="8"/>
       <c r="AB55" s="8"/>
-      <c r="AC55" s="8"/>
+      <c r="AC55" s="29"/>
       <c r="AD55" s="8"/>
       <c r="AE55" s="8"/>
-      <c r="AF55" s="28"/>
+      <c r="AF55" s="21"/>
       <c r="AG55" s="8"/>
       <c r="AH55" s="8"/>
       <c r="AI55" s="8"/>
-      <c r="AJ55" s="8"/>
+      <c r="AJ55" s="29"/>
       <c r="AK55" s="5">
         <f t="shared" ref="AK55" si="8">COUNTIF(F55:AJ55,"P")</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AL55" s="5">
         <f t="shared" ref="AL55" si="9">COUNTIF(F55:AJ55,"A")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <v>52</v>
       </c>
@@ -4403,48 +5484,224 @@
       <c r="E56" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F56" s="20"/>
-      <c r="G56" s="20"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="20"/>
-      <c r="J56" s="20"/>
-      <c r="K56" s="28"/>
-      <c r="L56" s="8"/>
-      <c r="M56" s="8"/>
-      <c r="N56" s="8"/>
-      <c r="O56" s="8"/>
-      <c r="P56" s="8"/>
-      <c r="Q56" s="8"/>
-      <c r="R56" s="28"/>
+      <c r="F56" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G56" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="H56" s="29"/>
+      <c r="I56" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="J56" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K56" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="L56" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="M56" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="N56" s="30"/>
+      <c r="O56" s="29"/>
+      <c r="P56" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q56" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="R56" s="8" t="s">
+        <v>124</v>
+      </c>
       <c r="S56" s="8"/>
       <c r="T56" s="8"/>
       <c r="U56" s="8"/>
-      <c r="V56" s="8"/>
+      <c r="V56" s="29"/>
       <c r="W56" s="8"/>
       <c r="X56" s="8"/>
-      <c r="Y56" s="28"/>
+      <c r="Y56" s="21"/>
       <c r="Z56" s="8"/>
       <c r="AA56" s="8"/>
       <c r="AB56" s="8"/>
-      <c r="AC56" s="8"/>
+      <c r="AC56" s="29"/>
       <c r="AD56" s="8"/>
       <c r="AE56" s="8"/>
-      <c r="AF56" s="28"/>
+      <c r="AF56" s="21"/>
       <c r="AG56" s="8"/>
       <c r="AH56" s="8"/>
       <c r="AI56" s="8"/>
-      <c r="AJ56" s="8"/>
+      <c r="AJ56" s="29"/>
       <c r="AK56" s="5">
-        <f t="shared" ref="AK56" si="10">COUNTIF(F56:AJ56,"P")</f>
+        <f t="shared" ref="AK56:AK58" si="10">COUNTIF(F56:AJ56,"P")</f>
+        <v>2</v>
+      </c>
+      <c r="AL56" s="5">
+        <f t="shared" ref="AL56:AL58" si="11">COUNTIF(F56:AJ56,"A")</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A57" s="9">
+        <v>53</v>
+      </c>
+      <c r="B57" s="17"/>
+      <c r="C57" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="D57" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="G57" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="H57" s="29"/>
+      <c r="I57" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="J57" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="K57" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="L57" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="M57" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="N57" s="30"/>
+      <c r="O57" s="29"/>
+      <c r="P57" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q57" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R57" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="S57" s="8"/>
+      <c r="T57" s="8"/>
+      <c r="U57" s="8"/>
+      <c r="V57" s="29"/>
+      <c r="W57" s="8"/>
+      <c r="X57" s="8"/>
+      <c r="Y57" s="21"/>
+      <c r="Z57" s="8"/>
+      <c r="AA57" s="8"/>
+      <c r="AB57" s="8"/>
+      <c r="AC57" s="29"/>
+      <c r="AD57" s="8"/>
+      <c r="AE57" s="8"/>
+      <c r="AF57" s="21"/>
+      <c r="AG57" s="8"/>
+      <c r="AH57" s="8"/>
+      <c r="AI57" s="8"/>
+      <c r="AJ57" s="29"/>
+      <c r="AK57" s="5">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="AL57" s="5">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL56" s="5">
-        <f t="shared" ref="AL56" si="11">COUNTIF(F56:AJ56,"A")</f>
+    </row>
+    <row r="58" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A58" s="9">
+        <v>54</v>
+      </c>
+      <c r="B58" s="17"/>
+      <c r="C58" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="D58" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="G58" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="H58" s="29"/>
+      <c r="I58" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="J58" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="K58" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="L58" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="M58" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="N58" s="30"/>
+      <c r="O58" s="29"/>
+      <c r="P58" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q58" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="R58" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="S58" s="8"/>
+      <c r="T58" s="8"/>
+      <c r="U58" s="8"/>
+      <c r="V58" s="29"/>
+      <c r="W58" s="8"/>
+      <c r="X58" s="8"/>
+      <c r="Y58" s="21"/>
+      <c r="Z58" s="8"/>
+      <c r="AA58" s="8"/>
+      <c r="AB58" s="8"/>
+      <c r="AC58" s="29"/>
+      <c r="AD58" s="8"/>
+      <c r="AE58" s="8"/>
+      <c r="AF58" s="21"/>
+      <c r="AG58" s="8"/>
+      <c r="AH58" s="8"/>
+      <c r="AI58" s="8"/>
+      <c r="AJ58" s="29"/>
+      <c r="AK58" s="5">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="AL58" s="5">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
+    <mergeCell ref="A2:AJ2"/>
+    <mergeCell ref="A1:AJ1"/>
+    <mergeCell ref="H5:H58"/>
+    <mergeCell ref="N5:N58"/>
+    <mergeCell ref="O5:O58"/>
+    <mergeCell ref="V5:V58"/>
+    <mergeCell ref="AC5:AC58"/>
+    <mergeCell ref="AJ5:AJ58"/>
     <mergeCell ref="AM16:AP16"/>
     <mergeCell ref="AL3:AL4"/>
     <mergeCell ref="AM3:AN3"/>
@@ -4455,55 +5712,58 @@
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="A2:AJ2"/>
-    <mergeCell ref="A1:AJ1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F6:J56 L6:Q56 S6:X56 Z6:AE56 AG6:AJ56 AM4:AN4 F3:AJ5">
-    <cfRule type="expression" dxfId="9" priority="16">
+  <conditionalFormatting sqref="AM4:AN4 F3:AJ5 F6:G58 I6:M58 AG6:AI58 AD6:AE58 Z6:AB58 W6:X58 P6:U58">
+    <cfRule type="expression" dxfId="10" priority="18">
       <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:J56 L6:Q56 S6:X56 Z6:AE56 AG6:AJ56 F4:AJ5">
-    <cfRule type="expression" dxfId="8" priority="15">
-      <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5:AJ5 F6:J56 L6:Q56 S6:X56 Z6:AE56 AG6:AJ56">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+  <conditionalFormatting sqref="F5:AJ5 F6:G58 I6:M58 AG6:AI58 AD6:AE58 Z6:AB58 W6:X58 P6:U58">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK3:AL3 AK5:AL56">
-    <cfRule type="expression" dxfId="5" priority="18">
+  <conditionalFormatting sqref="AK3:AL3 AK5:AL58">
+    <cfRule type="expression" dxfId="7" priority="20">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM5:AM6">
-    <cfRule type="expression" dxfId="4" priority="11">
+    <cfRule type="expression" dxfId="6" priority="13">
       <formula>AM$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM9:AM12">
-    <cfRule type="expression" dxfId="3" priority="5">
+    <cfRule type="expression" dxfId="5" priority="7">
       <formula>AM$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM17:AM20">
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="4" priority="6">
       <formula>AM$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN9:AP9">
-    <cfRule type="expression" dxfId="1" priority="6">
+    <cfRule type="expression" dxfId="3" priority="8">
       <formula>AN$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN17:AP17">
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="2" priority="5">
       <formula>AN$3="Sun"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:AJ5 F6:G58 I6:M58 P6:U58 W6:AB58 AD6:AI58">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>F$4=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:AJ5 F6:G58 I6:M58 P6:U58 W6:AB58 AD6:AI58">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Sindhi Muslim/Student Attendance/ECE (ROSE)/ECE (ROSE) Monthly Attendance - November-2024.xlsx
+++ b/Sindhi Muslim/Student Attendance/ECE (ROSE)/ECE (ROSE) Monthly Attendance - November-2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Student Attendance\ECE (ROSE)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF63DA6-626C-4B99-BFA7-B30B22241703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB192B1-9D67-4E99-8F14-38EA5E33FB1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="133">
   <si>
     <t>S.No</t>
   </si>
@@ -390,9 +390,6 @@
     <t>Jameel Hussain</t>
   </si>
   <si>
-    <t>Monthly Attendence Month of October-2024</t>
-  </si>
-  <si>
     <t>Israr</t>
   </si>
   <si>
@@ -430,6 +427,12 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>PTM - PTM - PTM - PTM - PTM --TM - PTM - PTM - PTM - PTM</t>
+  </si>
+  <si>
+    <t>Monthly Attendence Month of November-2024</t>
   </si>
 </sst>
 </file>
@@ -613,7 +616,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -677,6 +680,9 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -695,23 +701,6 @@
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="11">
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -756,6 +745,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -771,6 +770,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1105,86 +1111,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-      <c r="AB1" s="28"/>
-      <c r="AC1" s="28"/>
-      <c r="AD1" s="28"/>
-      <c r="AE1" s="28"/>
-      <c r="AF1" s="28"/>
-      <c r="AG1" s="28"/>
-      <c r="AH1" s="28"/>
-      <c r="AI1" s="28"/>
-      <c r="AJ1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="29"/>
+      <c r="AC1" s="29"/>
+      <c r="AD1" s="29"/>
+      <c r="AE1" s="29"/>
+      <c r="AF1" s="29"/>
+      <c r="AG1" s="29"/>
+      <c r="AH1" s="29"/>
+      <c r="AI1" s="29"/>
+      <c r="AJ1" s="29"/>
       <c r="AK1" s="19"/>
       <c r="AL1" s="19"/>
     </row>
     <row r="2" spans="1:42" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="27"/>
-      <c r="V2" s="27"/>
-      <c r="W2" s="27"/>
-      <c r="X2" s="27"/>
-      <c r="Y2" s="27"/>
-      <c r="Z2" s="27"/>
-      <c r="AA2" s="27"/>
-      <c r="AB2" s="27"/>
-      <c r="AC2" s="27"/>
-      <c r="AD2" s="27"/>
-      <c r="AE2" s="27"/>
-      <c r="AF2" s="27"/>
-      <c r="AG2" s="27"/>
-      <c r="AH2" s="27"/>
-      <c r="AI2" s="27"/>
-      <c r="AJ2" s="27"/>
+      <c r="A2" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="28"/>
+      <c r="AA2" s="28"/>
+      <c r="AB2" s="28"/>
+      <c r="AC2" s="28"/>
+      <c r="AD2" s="28"/>
+      <c r="AE2" s="28"/>
+      <c r="AF2" s="28"/>
+      <c r="AG2" s="28"/>
+      <c r="AH2" s="28"/>
+      <c r="AI2" s="28"/>
+      <c r="AJ2" s="28"/>
       <c r="AK2" s="18"/>
       <c r="AL2" s="18"/>
       <c r="AM2" s="18"/>
@@ -1467,49 +1473,55 @@
         <v>8</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H5" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="H5" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="M5" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="N5" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="I5" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="J5" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="K5" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="L5" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="M5" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N5" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="O5" s="29" t="s">
-        <v>125</v>
+      <c r="O5" s="30" t="s">
+        <v>124</v>
       </c>
       <c r="P5" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="S5" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T5" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="U5" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V5" s="30" t="s">
         <v>124</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="29" t="s">
-        <v>125</v>
       </c>
       <c r="W5" s="8"/>
       <c r="X5" s="8"/>
@@ -1517,8 +1529,8 @@
       <c r="Z5" s="8"/>
       <c r="AA5" s="8"/>
       <c r="AB5" s="8"/>
-      <c r="AC5" s="29" t="s">
-        <v>125</v>
+      <c r="AC5" s="30" t="s">
+        <v>124</v>
       </c>
       <c r="AD5" s="8"/>
       <c r="AE5" s="8"/>
@@ -1526,12 +1538,12 @@
       <c r="AG5" s="8"/>
       <c r="AH5" s="8"/>
       <c r="AI5" s="8"/>
-      <c r="AJ5" s="29" t="s">
-        <v>125</v>
+      <c r="AJ5" s="30" t="s">
+        <v>124</v>
       </c>
       <c r="AK5" s="5">
         <f t="shared" ref="AK5:AK34" si="2">COUNTIF(F5:AJ5,"P")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL5" s="5">
         <f t="shared" ref="AL5:AL34" si="3">COUNTIF(F5:AJ5,"A")</f>
@@ -1563,56 +1575,60 @@
         <v>8</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H6" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H6" s="30"/>
       <c r="I6" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J6" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K6" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L6" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M6" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="N6" s="30"/>
-      <c r="O6" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="N6" s="31"/>
+      <c r="O6" s="30"/>
       <c r="P6" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="S6" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="T6" s="27"/>
+      <c r="U6" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="V6" s="30"/>
       <c r="W6" s="8"/>
       <c r="X6" s="8"/>
       <c r="Y6" s="21"/>
       <c r="Z6" s="8"/>
       <c r="AA6" s="8"/>
       <c r="AB6" s="8"/>
-      <c r="AC6" s="29"/>
+      <c r="AC6" s="30"/>
       <c r="AD6" s="8"/>
       <c r="AE6" s="8"/>
       <c r="AF6" s="21"/>
       <c r="AG6" s="8"/>
       <c r="AH6" s="8"/>
       <c r="AI6" s="8"/>
-      <c r="AJ6" s="29"/>
+      <c r="AJ6" s="30"/>
       <c r="AK6" s="5">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -1645,59 +1661,63 @@
         <v>8</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="H7" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="H7" s="30"/>
       <c r="I7" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J7" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K7" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L7" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M7" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N7" s="30"/>
-      <c r="O7" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N7" s="31"/>
+      <c r="O7" s="30"/>
       <c r="P7" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S7" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T7" s="27"/>
+      <c r="U7" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="V7" s="30"/>
       <c r="W7" s="8"/>
       <c r="X7" s="8"/>
       <c r="Y7" s="21"/>
       <c r="Z7" s="8"/>
       <c r="AA7" s="8"/>
       <c r="AB7" s="8"/>
-      <c r="AC7" s="29"/>
+      <c r="AC7" s="30"/>
       <c r="AD7" s="8"/>
       <c r="AE7" s="8"/>
       <c r="AF7" s="21"/>
       <c r="AG7" s="8"/>
       <c r="AH7" s="8"/>
       <c r="AI7" s="8"/>
-      <c r="AJ7" s="29"/>
+      <c r="AJ7" s="30"/>
       <c r="AK7" s="5">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL7" s="5">
         <f t="shared" si="3"/>
@@ -1725,59 +1745,63 @@
         <v>8</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="H8" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="H8" s="30"/>
       <c r="I8" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K8" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L8" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M8" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N8" s="30"/>
-      <c r="O8" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N8" s="31"/>
+      <c r="O8" s="30"/>
       <c r="P8" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S8" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T8" s="27"/>
+      <c r="U8" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V8" s="30"/>
       <c r="W8" s="8"/>
       <c r="X8" s="8"/>
       <c r="Y8" s="21"/>
       <c r="Z8" s="8"/>
       <c r="AA8" s="8"/>
       <c r="AB8" s="8"/>
-      <c r="AC8" s="29"/>
+      <c r="AC8" s="30"/>
       <c r="AD8" s="8"/>
       <c r="AE8" s="8"/>
       <c r="AF8" s="21"/>
       <c r="AG8" s="8"/>
       <c r="AH8" s="8"/>
       <c r="AI8" s="8"/>
-      <c r="AJ8" s="29"/>
+      <c r="AJ8" s="30"/>
       <c r="AK8" s="5">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL8" s="5">
         <f t="shared" si="3"/>
@@ -1807,56 +1831,60 @@
         <v>8</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H9" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H9" s="30"/>
       <c r="I9" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K9" s="20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L9" s="20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M9" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="N9" s="30"/>
-      <c r="O9" s="29"/>
+        <v>126</v>
+      </c>
+      <c r="N9" s="31"/>
+      <c r="O9" s="30"/>
       <c r="P9" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="29"/>
+        <v>126</v>
+      </c>
+      <c r="S9" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="T9" s="27"/>
+      <c r="U9" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="V9" s="30"/>
       <c r="W9" s="8"/>
       <c r="X9" s="8"/>
       <c r="Y9" s="21"/>
       <c r="Z9" s="8"/>
       <c r="AA9" s="8"/>
       <c r="AB9" s="8"/>
-      <c r="AC9" s="29"/>
+      <c r="AC9" s="30"/>
       <c r="AD9" s="8"/>
       <c r="AE9" s="8"/>
       <c r="AF9" s="21"/>
       <c r="AG9" s="8"/>
       <c r="AH9" s="8"/>
       <c r="AI9" s="8"/>
-      <c r="AJ9" s="29"/>
+      <c r="AJ9" s="30"/>
       <c r="AK9" s="5">
         <f t="shared" si="2"/>
         <v>3</v>
@@ -1895,59 +1923,63 @@
         <v>8</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H10" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H10" s="30"/>
       <c r="I10" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J10" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K10" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L10" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M10" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N10" s="30"/>
-      <c r="O10" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N10" s="31"/>
+      <c r="O10" s="30"/>
       <c r="P10" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S10" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T10" s="27"/>
+      <c r="U10" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V10" s="30"/>
       <c r="W10" s="8"/>
       <c r="X10" s="8"/>
       <c r="Y10" s="21"/>
       <c r="Z10" s="8"/>
       <c r="AA10" s="8"/>
       <c r="AB10" s="8"/>
-      <c r="AC10" s="29"/>
+      <c r="AC10" s="30"/>
       <c r="AD10" s="8"/>
       <c r="AE10" s="8"/>
       <c r="AF10" s="21"/>
       <c r="AG10" s="8"/>
       <c r="AH10" s="8"/>
       <c r="AI10" s="8"/>
-      <c r="AJ10" s="29"/>
+      <c r="AJ10" s="30"/>
       <c r="AK10" s="5">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL10" s="5">
         <f t="shared" si="3"/>
@@ -1986,78 +2018,82 @@
         <v>8</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="H11" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="H11" s="30"/>
       <c r="I11" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K11" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L11" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M11" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="N11" s="30"/>
-      <c r="O11" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="N11" s="31"/>
+      <c r="O11" s="30"/>
       <c r="P11" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S11" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="T11" s="27"/>
+      <c r="U11" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="V11" s="30"/>
       <c r="W11" s="8"/>
       <c r="X11" s="8"/>
       <c r="Y11" s="21"/>
       <c r="Z11" s="8"/>
       <c r="AA11" s="8"/>
       <c r="AB11" s="8"/>
-      <c r="AC11" s="29"/>
+      <c r="AC11" s="30"/>
       <c r="AD11" s="8"/>
       <c r="AE11" s="8"/>
       <c r="AF11" s="21"/>
       <c r="AG11" s="8"/>
       <c r="AH11" s="8"/>
       <c r="AI11" s="8"/>
-      <c r="AJ11" s="29"/>
+      <c r="AJ11" s="30"/>
       <c r="AK11" s="5">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="AL11" s="5">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM11" s="5" t="s">
         <v>18</v>
       </c>
       <c r="AN11" s="9">
         <f>AK6+AK7+AK8+AK11+AK12+AK13+AK15+AK19+AK20+AK21+AK22+AK23+AK24+AK25+AK27+AK28+AK30+AK40</f>
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="AO11" s="9">
         <f>AK5+AK9+AK10+AK14+AK16+AK17+AK18+AK26+AK29+AK31+AK32+AK33+AK34+AK35+AK36+AK37+AK38+AK39+AK41</f>
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="AP11" s="9">
         <f>AN11+AO11</f>
-        <v>299</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
@@ -2075,78 +2111,82 @@
         <v>8</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="H12" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="H12" s="30"/>
       <c r="I12" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J12" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K12" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L12" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M12" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N12" s="30"/>
-      <c r="O12" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N12" s="31"/>
+      <c r="O12" s="30"/>
       <c r="P12" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q12" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S12" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="T12" s="27"/>
+      <c r="U12" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V12" s="30"/>
       <c r="W12" s="8"/>
       <c r="X12" s="8"/>
       <c r="Y12" s="21"/>
       <c r="Z12" s="8"/>
       <c r="AA12" s="8"/>
       <c r="AB12" s="8"/>
-      <c r="AC12" s="29"/>
+      <c r="AC12" s="30"/>
       <c r="AD12" s="8"/>
       <c r="AE12" s="8"/>
       <c r="AF12" s="21"/>
       <c r="AG12" s="8"/>
       <c r="AH12" s="8"/>
       <c r="AI12" s="8"/>
-      <c r="AJ12" s="29"/>
+      <c r="AJ12" s="30"/>
       <c r="AK12" s="5">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL12" s="5">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM12" s="5" t="s">
         <v>19</v>
       </c>
       <c r="AN12" s="9">
         <f>AN11/AN10</f>
-        <v>0.31578947368421051</v>
+        <v>0.36639676113360325</v>
       </c>
       <c r="AO12" s="9">
         <f>AO11/AO10</f>
-        <v>0.26190476190476192</v>
+        <v>0.304029304029304</v>
       </c>
       <c r="AP12" s="9">
         <f>AP11/AP10</f>
-        <v>0.28749999999999998</v>
+        <v>0.33365384615384613</v>
       </c>
     </row>
     <row r="13" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
@@ -2166,63 +2206,67 @@
         <v>8</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="H13" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="H13" s="30"/>
       <c r="I13" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J13" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K13" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L13" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M13" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N13" s="30"/>
-      <c r="O13" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N13" s="31"/>
+      <c r="O13" s="30"/>
       <c r="P13" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S13" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="T13" s="27"/>
+      <c r="U13" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V13" s="30"/>
       <c r="W13" s="8"/>
       <c r="X13" s="8"/>
       <c r="Y13" s="21"/>
       <c r="Z13" s="8"/>
       <c r="AA13" s="8"/>
       <c r="AB13" s="8"/>
-      <c r="AC13" s="29"/>
+      <c r="AC13" s="30"/>
       <c r="AD13" s="8"/>
       <c r="AE13" s="8"/>
       <c r="AF13" s="21"/>
       <c r="AG13" s="8"/>
       <c r="AH13" s="8"/>
       <c r="AI13" s="8"/>
-      <c r="AJ13" s="29"/>
+      <c r="AJ13" s="30"/>
       <c r="AK13" s="5">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL13" s="5">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM13" s="3"/>
       <c r="AN13" s="12"/>
@@ -2246,63 +2290,67 @@
         <v>8</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="H14" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="H14" s="30"/>
       <c r="I14" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J14" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K14" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L14" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M14" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="N14" s="30"/>
-      <c r="O14" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="N14" s="31"/>
+      <c r="O14" s="30"/>
       <c r="P14" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q14" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="S14" s="8"/>
-      <c r="T14" s="8"/>
-      <c r="U14" s="8"/>
-      <c r="V14" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="S14" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="T14" s="27"/>
+      <c r="U14" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V14" s="30"/>
       <c r="W14" s="8"/>
       <c r="X14" s="8"/>
       <c r="Y14" s="21"/>
       <c r="Z14" s="8"/>
       <c r="AA14" s="8"/>
       <c r="AB14" s="8"/>
-      <c r="AC14" s="29"/>
+      <c r="AC14" s="30"/>
       <c r="AD14" s="8"/>
       <c r="AE14" s="8"/>
       <c r="AF14" s="21"/>
       <c r="AG14" s="8"/>
       <c r="AH14" s="8"/>
       <c r="AI14" s="8"/>
-      <c r="AJ14" s="29"/>
+      <c r="AJ14" s="30"/>
       <c r="AK14" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL14" s="5">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM14" s="14"/>
       <c r="AN14" s="14"/>
@@ -2326,59 +2374,63 @@
         <v>8</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H15" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H15" s="30"/>
       <c r="I15" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J15" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L15" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M15" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N15" s="30"/>
-      <c r="O15" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N15" s="31"/>
+      <c r="O15" s="30"/>
       <c r="P15" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q15" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="S15" s="8"/>
-      <c r="T15" s="8"/>
-      <c r="U15" s="8"/>
-      <c r="V15" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="S15" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T15" s="27"/>
+      <c r="U15" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V15" s="30"/>
       <c r="W15" s="8"/>
       <c r="X15" s="8"/>
       <c r="Y15" s="21"/>
       <c r="Z15" s="8"/>
       <c r="AA15" s="8"/>
       <c r="AB15" s="8"/>
-      <c r="AC15" s="29"/>
+      <c r="AC15" s="30"/>
       <c r="AD15" s="8"/>
       <c r="AE15" s="8"/>
       <c r="AF15" s="21"/>
       <c r="AG15" s="8"/>
       <c r="AH15" s="8"/>
       <c r="AI15" s="8"/>
-      <c r="AJ15" s="29"/>
+      <c r="AJ15" s="30"/>
       <c r="AK15" s="5">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL15" s="5">
         <f t="shared" si="3"/>
@@ -2406,59 +2458,63 @@
         <v>8</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H16" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H16" s="30"/>
       <c r="I16" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J16" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K16" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L16" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M16" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N16" s="30"/>
-      <c r="O16" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N16" s="31"/>
+      <c r="O16" s="30"/>
       <c r="P16" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q16" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="8"/>
-      <c r="V16" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S16" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T16" s="27"/>
+      <c r="U16" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V16" s="30"/>
       <c r="W16" s="8"/>
       <c r="X16" s="8"/>
       <c r="Y16" s="21"/>
       <c r="Z16" s="8"/>
       <c r="AA16" s="8"/>
       <c r="AB16" s="8"/>
-      <c r="AC16" s="29"/>
+      <c r="AC16" s="30"/>
       <c r="AD16" s="8"/>
       <c r="AE16" s="8"/>
       <c r="AF16" s="21"/>
       <c r="AG16" s="8"/>
       <c r="AH16" s="8"/>
       <c r="AI16" s="8"/>
-      <c r="AJ16" s="29"/>
+      <c r="AJ16" s="30"/>
       <c r="AK16" s="5">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL16" s="5">
         <f t="shared" si="3"/>
@@ -2488,63 +2544,67 @@
         <v>8</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H17" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H17" s="30"/>
       <c r="I17" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K17" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L17" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M17" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N17" s="30"/>
-      <c r="O17" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N17" s="31"/>
+      <c r="O17" s="30"/>
       <c r="P17" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R17" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
-      <c r="V17" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="S17" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="T17" s="27"/>
+      <c r="U17" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V17" s="30"/>
       <c r="W17" s="8"/>
       <c r="X17" s="8"/>
       <c r="Y17" s="21"/>
       <c r="Z17" s="8"/>
       <c r="AA17" s="8"/>
       <c r="AB17" s="8"/>
-      <c r="AC17" s="29"/>
+      <c r="AC17" s="30"/>
       <c r="AD17" s="8"/>
       <c r="AE17" s="8"/>
       <c r="AF17" s="21"/>
       <c r="AG17" s="8"/>
       <c r="AH17" s="8"/>
       <c r="AI17" s="8"/>
-      <c r="AJ17" s="29"/>
+      <c r="AJ17" s="30"/>
       <c r="AK17" s="5">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL17" s="5">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM17" s="5" t="s">
         <v>13</v>
@@ -2576,63 +2636,67 @@
         <v>8</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="H18" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="H18" s="30"/>
       <c r="I18" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J18" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K18" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L18" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M18" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N18" s="30"/>
-      <c r="O18" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N18" s="31"/>
+      <c r="O18" s="30"/>
       <c r="P18" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R18" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S18" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="T18" s="27"/>
+      <c r="U18" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="V18" s="30"/>
       <c r="W18" s="8"/>
       <c r="X18" s="8"/>
       <c r="Y18" s="21"/>
       <c r="Z18" s="8"/>
       <c r="AA18" s="8"/>
       <c r="AB18" s="8"/>
-      <c r="AC18" s="29"/>
+      <c r="AC18" s="30"/>
       <c r="AD18" s="8"/>
       <c r="AE18" s="8"/>
       <c r="AF18" s="21"/>
       <c r="AG18" s="8"/>
       <c r="AH18" s="8"/>
       <c r="AI18" s="8"/>
-      <c r="AJ18" s="29"/>
+      <c r="AJ18" s="30"/>
       <c r="AK18" s="5">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="AL18" s="5">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM18" s="5" t="s">
         <v>17</v>
@@ -2667,59 +2731,63 @@
         <v>8</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H19" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H19" s="30"/>
       <c r="I19" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J19" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K19" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L19" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M19" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="N19" s="30"/>
-      <c r="O19" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="N19" s="31"/>
+      <c r="O19" s="30"/>
       <c r="P19" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q19" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R19" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S19" s="8"/>
-      <c r="T19" s="8"/>
-      <c r="U19" s="8"/>
-      <c r="V19" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S19" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T19" s="27"/>
+      <c r="U19" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V19" s="30"/>
       <c r="W19" s="8"/>
       <c r="X19" s="8"/>
       <c r="Y19" s="21"/>
       <c r="Z19" s="8"/>
       <c r="AA19" s="8"/>
       <c r="AB19" s="8"/>
-      <c r="AC19" s="29"/>
+      <c r="AC19" s="30"/>
       <c r="AD19" s="8"/>
       <c r="AE19" s="8"/>
       <c r="AF19" s="21"/>
       <c r="AG19" s="8"/>
       <c r="AH19" s="8"/>
       <c r="AI19" s="8"/>
-      <c r="AJ19" s="29"/>
+      <c r="AJ19" s="30"/>
       <c r="AK19" s="5">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL19" s="5">
         <f t="shared" si="3"/>
@@ -2730,15 +2798,15 @@
       </c>
       <c r="AN19" s="9">
         <f>AN18-AN11</f>
-        <v>338</v>
+        <v>313</v>
       </c>
       <c r="AO19" s="9">
         <f>AO18-AO11</f>
-        <v>403</v>
+        <v>380</v>
       </c>
       <c r="AP19" s="9">
         <f>AN19+AO19</f>
-        <v>741</v>
+        <v>693</v>
       </c>
     </row>
     <row r="20" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
@@ -2758,59 +2826,63 @@
         <v>8</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G20" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H20" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H20" s="30"/>
       <c r="I20" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J20" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K20" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L20" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M20" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N20" s="30"/>
-      <c r="O20" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N20" s="31"/>
+      <c r="O20" s="30"/>
       <c r="P20" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q20" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R20" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S20" s="8"/>
-      <c r="T20" s="8"/>
-      <c r="U20" s="8"/>
-      <c r="V20" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S20" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T20" s="27"/>
+      <c r="U20" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V20" s="30"/>
       <c r="W20" s="8"/>
       <c r="X20" s="8"/>
       <c r="Y20" s="21"/>
       <c r="Z20" s="8"/>
       <c r="AA20" s="8"/>
       <c r="AB20" s="8"/>
-      <c r="AC20" s="29"/>
+      <c r="AC20" s="30"/>
       <c r="AD20" s="8"/>
       <c r="AE20" s="8"/>
       <c r="AF20" s="21"/>
       <c r="AG20" s="8"/>
       <c r="AH20" s="8"/>
       <c r="AI20" s="8"/>
-      <c r="AJ20" s="29"/>
+      <c r="AJ20" s="30"/>
       <c r="AK20" s="5">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL20" s="5">
         <f t="shared" si="3"/>
@@ -2821,15 +2893,15 @@
       </c>
       <c r="AN20" s="15">
         <f>AN19/AN18</f>
-        <v>0.68421052631578949</v>
+        <v>0.6336032388663968</v>
       </c>
       <c r="AO20" s="15">
         <f>AO19/AO18</f>
-        <v>0.73809523809523814</v>
+        <v>0.69597069597069594</v>
       </c>
       <c r="AP20" s="15">
         <f>AP19/AP18</f>
-        <v>0.71250000000000002</v>
+        <v>0.66634615384615381</v>
       </c>
     </row>
     <row r="21" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
@@ -2849,63 +2921,67 @@
         <v>8</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H21" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H21" s="30"/>
       <c r="I21" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K21" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L21" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M21" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N21" s="30"/>
-      <c r="O21" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N21" s="31"/>
+      <c r="O21" s="30"/>
       <c r="P21" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q21" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R21" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S21" s="8"/>
-      <c r="T21" s="8"/>
-      <c r="U21" s="8"/>
-      <c r="V21" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S21" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="T21" s="27"/>
+      <c r="U21" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V21" s="30"/>
       <c r="W21" s="8"/>
       <c r="X21" s="8"/>
       <c r="Y21" s="21"/>
       <c r="Z21" s="8"/>
       <c r="AA21" s="8"/>
       <c r="AB21" s="8"/>
-      <c r="AC21" s="29"/>
+      <c r="AC21" s="30"/>
       <c r="AD21" s="8"/>
       <c r="AE21" s="8"/>
       <c r="AF21" s="21"/>
       <c r="AG21" s="8"/>
       <c r="AH21" s="8"/>
       <c r="AI21" s="8"/>
-      <c r="AJ21" s="29"/>
+      <c r="AJ21" s="30"/>
       <c r="AK21" s="5">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL21" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
@@ -2925,63 +3001,67 @@
         <v>8</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H22" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H22" s="30"/>
       <c r="I22" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J22" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K22" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L22" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M22" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N22" s="30"/>
-      <c r="O22" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N22" s="31"/>
+      <c r="O22" s="30"/>
       <c r="P22" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q22" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R22" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S22" s="8"/>
-      <c r="T22" s="8"/>
-      <c r="U22" s="8"/>
-      <c r="V22" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S22" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="T22" s="27"/>
+      <c r="U22" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V22" s="30"/>
       <c r="W22" s="8"/>
       <c r="X22" s="8"/>
       <c r="Y22" s="21"/>
       <c r="Z22" s="8"/>
       <c r="AA22" s="8"/>
       <c r="AB22" s="8"/>
-      <c r="AC22" s="29"/>
+      <c r="AC22" s="30"/>
       <c r="AD22" s="8"/>
       <c r="AE22" s="8"/>
       <c r="AF22" s="21"/>
       <c r="AG22" s="8"/>
       <c r="AH22" s="8"/>
       <c r="AI22" s="8"/>
-      <c r="AJ22" s="29"/>
+      <c r="AJ22" s="30"/>
       <c r="AK22" s="5">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL22" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
@@ -3001,59 +3081,63 @@
         <v>8</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H23" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H23" s="30"/>
       <c r="I23" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J23" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K23" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L23" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M23" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N23" s="30"/>
-      <c r="O23" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N23" s="31"/>
+      <c r="O23" s="30"/>
       <c r="P23" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q23" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R23" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S23" s="8"/>
-      <c r="T23" s="8"/>
-      <c r="U23" s="8"/>
-      <c r="V23" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S23" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T23" s="27"/>
+      <c r="U23" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V23" s="30"/>
       <c r="W23" s="8"/>
       <c r="X23" s="8"/>
       <c r="Y23" s="21"/>
       <c r="Z23" s="8"/>
       <c r="AA23" s="8"/>
       <c r="AB23" s="8"/>
-      <c r="AC23" s="29"/>
+      <c r="AC23" s="30"/>
       <c r="AD23" s="8"/>
       <c r="AE23" s="8"/>
       <c r="AF23" s="21"/>
       <c r="AG23" s="8"/>
       <c r="AH23" s="8"/>
       <c r="AI23" s="8"/>
-      <c r="AJ23" s="29"/>
+      <c r="AJ23" s="30"/>
       <c r="AK23" s="5">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL23" s="5">
         <f t="shared" si="3"/>
@@ -3077,63 +3161,67 @@
         <v>8</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H24" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H24" s="30"/>
       <c r="I24" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J24" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K24" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L24" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M24" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N24" s="30"/>
-      <c r="O24" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N24" s="31"/>
+      <c r="O24" s="30"/>
       <c r="P24" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q24" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R24" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S24" s="8"/>
-      <c r="T24" s="8"/>
-      <c r="U24" s="8"/>
-      <c r="V24" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S24" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="T24" s="27"/>
+      <c r="U24" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V24" s="30"/>
       <c r="W24" s="8"/>
       <c r="X24" s="8"/>
       <c r="Y24" s="21"/>
       <c r="Z24" s="8"/>
       <c r="AA24" s="8"/>
       <c r="AB24" s="8"/>
-      <c r="AC24" s="29"/>
+      <c r="AC24" s="30"/>
       <c r="AD24" s="8"/>
       <c r="AE24" s="8"/>
       <c r="AF24" s="21"/>
       <c r="AG24" s="8"/>
       <c r="AH24" s="8"/>
       <c r="AI24" s="8"/>
-      <c r="AJ24" s="29"/>
+      <c r="AJ24" s="30"/>
       <c r="AK24" s="5">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL24" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
@@ -3153,63 +3241,67 @@
         <v>8</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H25" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H25" s="30"/>
       <c r="I25" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J25" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K25" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L25" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M25" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="N25" s="30"/>
-      <c r="O25" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="N25" s="31"/>
+      <c r="O25" s="30"/>
       <c r="P25" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q25" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R25" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S25" s="8"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="8"/>
-      <c r="V25" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S25" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="T25" s="27"/>
+      <c r="U25" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V25" s="30"/>
       <c r="W25" s="8"/>
       <c r="X25" s="8"/>
       <c r="Y25" s="21"/>
       <c r="Z25" s="8"/>
       <c r="AA25" s="8"/>
       <c r="AB25" s="8"/>
-      <c r="AC25" s="29"/>
+      <c r="AC25" s="30"/>
       <c r="AD25" s="8"/>
       <c r="AE25" s="8"/>
       <c r="AF25" s="21"/>
       <c r="AG25" s="8"/>
       <c r="AH25" s="8"/>
       <c r="AI25" s="8"/>
-      <c r="AJ25" s="29"/>
+      <c r="AJ25" s="30"/>
       <c r="AK25" s="5">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL25" s="5">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
@@ -3229,63 +3321,67 @@
         <v>8</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H26" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H26" s="30"/>
       <c r="I26" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J26" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K26" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L26" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M26" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N26" s="30"/>
-      <c r="O26" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N26" s="31"/>
+      <c r="O26" s="30"/>
       <c r="P26" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q26" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R26" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S26" s="8"/>
-      <c r="T26" s="8"/>
-      <c r="U26" s="8"/>
-      <c r="V26" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S26" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="T26" s="27"/>
+      <c r="U26" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V26" s="30"/>
       <c r="W26" s="8"/>
       <c r="X26" s="8"/>
       <c r="Y26" s="21"/>
       <c r="Z26" s="8"/>
       <c r="AA26" s="8"/>
       <c r="AB26" s="8"/>
-      <c r="AC26" s="29"/>
+      <c r="AC26" s="30"/>
       <c r="AD26" s="8"/>
       <c r="AE26" s="8"/>
       <c r="AF26" s="21"/>
       <c r="AG26" s="8"/>
       <c r="AH26" s="8"/>
       <c r="AI26" s="8"/>
-      <c r="AJ26" s="29"/>
+      <c r="AJ26" s="30"/>
       <c r="AK26" s="5">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL26" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
@@ -3305,59 +3401,63 @@
         <v>8</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H27" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H27" s="30"/>
       <c r="I27" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K27" s="20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L27" s="20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M27" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="N27" s="30"/>
-      <c r="O27" s="29"/>
+        <v>126</v>
+      </c>
+      <c r="N27" s="31"/>
+      <c r="O27" s="30"/>
       <c r="P27" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q27" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R27" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S27" s="8"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="8"/>
-      <c r="V27" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S27" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T27" s="27"/>
+      <c r="U27" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V27" s="30"/>
       <c r="W27" s="8"/>
       <c r="X27" s="8"/>
       <c r="Y27" s="21"/>
       <c r="Z27" s="8"/>
       <c r="AA27" s="8"/>
       <c r="AB27" s="8"/>
-      <c r="AC27" s="29"/>
+      <c r="AC27" s="30"/>
       <c r="AD27" s="8"/>
       <c r="AE27" s="8"/>
       <c r="AF27" s="21"/>
       <c r="AG27" s="8"/>
       <c r="AH27" s="8"/>
       <c r="AI27" s="8"/>
-      <c r="AJ27" s="29"/>
+      <c r="AJ27" s="30"/>
       <c r="AK27" s="5">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AL27" s="5">
         <f t="shared" si="3"/>
@@ -3381,59 +3481,63 @@
         <v>8</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G28" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H28" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H28" s="30"/>
       <c r="I28" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J28" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K28" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L28" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M28" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N28" s="30"/>
-      <c r="O28" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N28" s="31"/>
+      <c r="O28" s="30"/>
       <c r="P28" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q28" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R28" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S28" s="8"/>
-      <c r="T28" s="8"/>
-      <c r="U28" s="8"/>
-      <c r="V28" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S28" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T28" s="27"/>
+      <c r="U28" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V28" s="30"/>
       <c r="W28" s="8"/>
       <c r="X28" s="8"/>
       <c r="Y28" s="21"/>
       <c r="Z28" s="8"/>
       <c r="AA28" s="8"/>
       <c r="AB28" s="8"/>
-      <c r="AC28" s="29"/>
+      <c r="AC28" s="30"/>
       <c r="AD28" s="8"/>
       <c r="AE28" s="8"/>
       <c r="AF28" s="21"/>
       <c r="AG28" s="8"/>
       <c r="AH28" s="8"/>
       <c r="AI28" s="8"/>
-      <c r="AJ28" s="29"/>
+      <c r="AJ28" s="30"/>
       <c r="AK28" s="5">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL28" s="5">
         <f t="shared" si="3"/>
@@ -3457,59 +3561,63 @@
         <v>8</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H29" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H29" s="30"/>
       <c r="I29" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K29" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L29" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M29" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N29" s="30"/>
-      <c r="O29" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N29" s="31"/>
+      <c r="O29" s="30"/>
       <c r="P29" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q29" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R29" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S29" s="8"/>
-      <c r="T29" s="8"/>
-      <c r="U29" s="8"/>
-      <c r="V29" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S29" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T29" s="27"/>
+      <c r="U29" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V29" s="30"/>
       <c r="W29" s="8"/>
       <c r="X29" s="8"/>
       <c r="Y29" s="21"/>
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8"/>
-      <c r="AC29" s="29"/>
+      <c r="AC29" s="30"/>
       <c r="AD29" s="8"/>
       <c r="AE29" s="8"/>
       <c r="AF29" s="21"/>
       <c r="AG29" s="8"/>
       <c r="AH29" s="8"/>
       <c r="AI29" s="8"/>
-      <c r="AJ29" s="29"/>
+      <c r="AJ29" s="30"/>
       <c r="AK29" s="5">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL29" s="5">
         <f t="shared" si="3"/>
@@ -3533,59 +3641,63 @@
         <v>8</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="H30" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="H30" s="30"/>
       <c r="I30" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J30" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K30" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L30" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M30" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N30" s="30"/>
-      <c r="O30" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N30" s="31"/>
+      <c r="O30" s="30"/>
       <c r="P30" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q30" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R30" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S30" s="8"/>
-      <c r="T30" s="8"/>
-      <c r="U30" s="8"/>
-      <c r="V30" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S30" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T30" s="27"/>
+      <c r="U30" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V30" s="30"/>
       <c r="W30" s="8"/>
       <c r="X30" s="8"/>
       <c r="Y30" s="21"/>
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8"/>
-      <c r="AC30" s="29"/>
+      <c r="AC30" s="30"/>
       <c r="AD30" s="8"/>
       <c r="AE30" s="8"/>
       <c r="AF30" s="21"/>
       <c r="AG30" s="8"/>
       <c r="AH30" s="8"/>
       <c r="AI30" s="8"/>
-      <c r="AJ30" s="29"/>
+      <c r="AJ30" s="30"/>
       <c r="AK30" s="5">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL30" s="5">
         <f t="shared" si="3"/>
@@ -3609,59 +3721,63 @@
         <v>8</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H31" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H31" s="30"/>
       <c r="I31" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K31" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L31" s="20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M31" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="N31" s="30"/>
-      <c r="O31" s="29"/>
+        <v>126</v>
+      </c>
+      <c r="N31" s="31"/>
+      <c r="O31" s="30"/>
       <c r="P31" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q31" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R31" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S31" s="8"/>
-      <c r="T31" s="8"/>
-      <c r="U31" s="8"/>
-      <c r="V31" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S31" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T31" s="27"/>
+      <c r="U31" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="V31" s="30"/>
       <c r="W31" s="8"/>
       <c r="X31" s="8"/>
       <c r="Y31" s="21"/>
       <c r="Z31" s="8"/>
       <c r="AA31" s="8"/>
       <c r="AB31" s="8"/>
-      <c r="AC31" s="29"/>
+      <c r="AC31" s="30"/>
       <c r="AD31" s="8"/>
       <c r="AE31" s="8"/>
       <c r="AF31" s="21"/>
       <c r="AG31" s="8"/>
       <c r="AH31" s="8"/>
       <c r="AI31" s="8"/>
-      <c r="AJ31" s="29"/>
+      <c r="AJ31" s="30"/>
       <c r="AK31" s="5">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL31" s="5">
         <f t="shared" si="3"/>
@@ -3685,63 +3801,67 @@
         <v>8</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H32" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H32" s="30"/>
       <c r="I32" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J32" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K32" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L32" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M32" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N32" s="30"/>
-      <c r="O32" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N32" s="31"/>
+      <c r="O32" s="30"/>
       <c r="P32" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q32" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R32" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S32" s="8"/>
-      <c r="T32" s="8"/>
-      <c r="U32" s="8"/>
-      <c r="V32" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S32" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="T32" s="27"/>
+      <c r="U32" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V32" s="30"/>
       <c r="W32" s="8"/>
       <c r="X32" s="8"/>
       <c r="Y32" s="21"/>
       <c r="Z32" s="8"/>
       <c r="AA32" s="8"/>
       <c r="AB32" s="8"/>
-      <c r="AC32" s="29"/>
+      <c r="AC32" s="30"/>
       <c r="AD32" s="8"/>
       <c r="AE32" s="8"/>
       <c r="AF32" s="21"/>
       <c r="AG32" s="8"/>
       <c r="AH32" s="8"/>
       <c r="AI32" s="8"/>
-      <c r="AJ32" s="29"/>
+      <c r="AJ32" s="30"/>
       <c r="AK32" s="5">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL32" s="5">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
@@ -3761,59 +3881,63 @@
         <v>8</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H33" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H33" s="30"/>
       <c r="I33" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J33" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K33" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L33" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M33" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N33" s="30"/>
-      <c r="O33" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N33" s="31"/>
+      <c r="O33" s="30"/>
       <c r="P33" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q33" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R33" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S33" s="8"/>
-      <c r="T33" s="8"/>
-      <c r="U33" s="8"/>
-      <c r="V33" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S33" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T33" s="27"/>
+      <c r="U33" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V33" s="30"/>
       <c r="W33" s="8"/>
       <c r="X33" s="8"/>
       <c r="Y33" s="21"/>
       <c r="Z33" s="8"/>
       <c r="AA33" s="8"/>
       <c r="AB33" s="8"/>
-      <c r="AC33" s="29"/>
+      <c r="AC33" s="30"/>
       <c r="AD33" s="8"/>
       <c r="AE33" s="8"/>
       <c r="AF33" s="21"/>
       <c r="AG33" s="8"/>
       <c r="AH33" s="8"/>
       <c r="AI33" s="8"/>
-      <c r="AJ33" s="29"/>
+      <c r="AJ33" s="30"/>
       <c r="AK33" s="5">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL33" s="5">
         <f t="shared" si="3"/>
@@ -3837,59 +3961,63 @@
         <v>8</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G34" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H34" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H34" s="30"/>
       <c r="I34" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J34" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K34" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L34" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M34" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N34" s="30"/>
-      <c r="O34" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N34" s="31"/>
+      <c r="O34" s="30"/>
       <c r="P34" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q34" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R34" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S34" s="8"/>
-      <c r="T34" s="8"/>
-      <c r="U34" s="8"/>
-      <c r="V34" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S34" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T34" s="27"/>
+      <c r="U34" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V34" s="30"/>
       <c r="W34" s="8"/>
       <c r="X34" s="8"/>
       <c r="Y34" s="21"/>
       <c r="Z34" s="8"/>
       <c r="AA34" s="8"/>
       <c r="AB34" s="8"/>
-      <c r="AC34" s="29"/>
+      <c r="AC34" s="30"/>
       <c r="AD34" s="8"/>
       <c r="AE34" s="8"/>
       <c r="AF34" s="21"/>
       <c r="AG34" s="8"/>
       <c r="AH34" s="8"/>
       <c r="AI34" s="8"/>
-      <c r="AJ34" s="29"/>
+      <c r="AJ34" s="30"/>
       <c r="AK34" s="5">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL34" s="5">
         <f t="shared" si="3"/>
@@ -3913,63 +4041,67 @@
         <v>8</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H35" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H35" s="30"/>
       <c r="I35" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J35" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K35" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L35" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M35" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N35" s="30"/>
-      <c r="O35" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N35" s="31"/>
+      <c r="O35" s="30"/>
       <c r="P35" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q35" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R35" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S35" s="8"/>
-      <c r="T35" s="8"/>
-      <c r="U35" s="8"/>
-      <c r="V35" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S35" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="T35" s="27"/>
+      <c r="U35" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V35" s="30"/>
       <c r="W35" s="8"/>
       <c r="X35" s="8"/>
       <c r="Y35" s="21"/>
       <c r="Z35" s="8"/>
       <c r="AA35" s="8"/>
       <c r="AB35" s="8"/>
-      <c r="AC35" s="29"/>
+      <c r="AC35" s="30"/>
       <c r="AD35" s="8"/>
       <c r="AE35" s="8"/>
       <c r="AF35" s="21"/>
       <c r="AG35" s="8"/>
       <c r="AH35" s="8"/>
       <c r="AI35" s="8"/>
-      <c r="AJ35" s="29"/>
+      <c r="AJ35" s="30"/>
       <c r="AK35" s="5">
         <f t="shared" ref="AK35:AK52" si="4">COUNTIF(F35:AJ35,"P")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL35" s="5">
         <f t="shared" ref="AL35:AL52" si="5">COUNTIF(F35:AJ35,"A")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
@@ -3989,63 +4121,67 @@
         <v>8</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H36" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H36" s="30"/>
       <c r="I36" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J36" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K36" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L36" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M36" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N36" s="30"/>
-      <c r="O36" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N36" s="31"/>
+      <c r="O36" s="30"/>
       <c r="P36" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q36" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R36" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S36" s="8"/>
-      <c r="T36" s="8"/>
-      <c r="U36" s="8"/>
-      <c r="V36" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S36" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="T36" s="27"/>
+      <c r="U36" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V36" s="30"/>
       <c r="W36" s="8"/>
       <c r="X36" s="8"/>
       <c r="Y36" s="21"/>
       <c r="Z36" s="8"/>
       <c r="AA36" s="8"/>
       <c r="AB36" s="8"/>
-      <c r="AC36" s="29"/>
+      <c r="AC36" s="30"/>
       <c r="AD36" s="8"/>
       <c r="AE36" s="8"/>
       <c r="AF36" s="21"/>
       <c r="AG36" s="8"/>
       <c r="AH36" s="8"/>
       <c r="AI36" s="8"/>
-      <c r="AJ36" s="29"/>
+      <c r="AJ36" s="30"/>
       <c r="AK36" s="5">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL36" s="5">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
@@ -4065,63 +4201,67 @@
         <v>8</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H37" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H37" s="30"/>
       <c r="I37" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J37" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K37" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L37" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M37" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N37" s="30"/>
-      <c r="O37" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N37" s="31"/>
+      <c r="O37" s="30"/>
       <c r="P37" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q37" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R37" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S37" s="8"/>
-      <c r="T37" s="8"/>
-      <c r="U37" s="8"/>
-      <c r="V37" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S37" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="T37" s="27"/>
+      <c r="U37" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="V37" s="30"/>
       <c r="W37" s="8"/>
       <c r="X37" s="8"/>
       <c r="Y37" s="21"/>
       <c r="Z37" s="8"/>
       <c r="AA37" s="8"/>
       <c r="AB37" s="8"/>
-      <c r="AC37" s="29"/>
+      <c r="AC37" s="30"/>
       <c r="AD37" s="8"/>
       <c r="AE37" s="8"/>
       <c r="AF37" s="21"/>
       <c r="AG37" s="8"/>
       <c r="AH37" s="8"/>
       <c r="AI37" s="8"/>
-      <c r="AJ37" s="29"/>
+      <c r="AJ37" s="30"/>
       <c r="AK37" s="5">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="AL37" s="5">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
@@ -4141,63 +4281,67 @@
         <v>8</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G38" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="H38" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="H38" s="30"/>
       <c r="I38" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J38" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K38" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L38" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M38" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="N38" s="30"/>
-      <c r="O38" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="N38" s="31"/>
+      <c r="O38" s="30"/>
       <c r="P38" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q38" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R38" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S38" s="8"/>
-      <c r="T38" s="8"/>
-      <c r="U38" s="8"/>
-      <c r="V38" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S38" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="T38" s="27"/>
+      <c r="U38" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V38" s="30"/>
       <c r="W38" s="8"/>
       <c r="X38" s="8"/>
       <c r="Y38" s="21"/>
       <c r="Z38" s="8"/>
       <c r="AA38" s="8"/>
       <c r="AB38" s="8"/>
-      <c r="AC38" s="29"/>
+      <c r="AC38" s="30"/>
       <c r="AD38" s="8"/>
       <c r="AE38" s="8"/>
       <c r="AF38" s="21"/>
       <c r="AG38" s="8"/>
       <c r="AH38" s="8"/>
       <c r="AI38" s="8"/>
-      <c r="AJ38" s="29"/>
+      <c r="AJ38" s="30"/>
       <c r="AK38" s="5">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL38" s="5">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
@@ -4217,59 +4361,63 @@
         <v>8</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G39" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="H39" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="H39" s="30"/>
       <c r="I39" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J39" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K39" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L39" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M39" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N39" s="30"/>
-      <c r="O39" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N39" s="31"/>
+      <c r="O39" s="30"/>
       <c r="P39" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q39" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R39" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="S39" s="8"/>
-      <c r="T39" s="8"/>
-      <c r="U39" s="8"/>
-      <c r="V39" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="S39" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T39" s="27"/>
+      <c r="U39" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="V39" s="30"/>
       <c r="W39" s="8"/>
       <c r="X39" s="8"/>
       <c r="Y39" s="21"/>
       <c r="Z39" s="8"/>
       <c r="AA39" s="8"/>
       <c r="AB39" s="8"/>
-      <c r="AC39" s="29"/>
+      <c r="AC39" s="30"/>
       <c r="AD39" s="8"/>
       <c r="AE39" s="8"/>
       <c r="AF39" s="21"/>
       <c r="AG39" s="8"/>
       <c r="AH39" s="8"/>
       <c r="AI39" s="8"/>
-      <c r="AJ39" s="29"/>
+      <c r="AJ39" s="30"/>
       <c r="AK39" s="5">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL39" s="5">
         <f t="shared" si="5"/>
@@ -4293,59 +4441,63 @@
         <v>8</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H40" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H40" s="30"/>
       <c r="I40" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J40" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K40" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L40" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M40" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N40" s="30"/>
-      <c r="O40" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N40" s="31"/>
+      <c r="O40" s="30"/>
       <c r="P40" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q40" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R40" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S40" s="8"/>
-      <c r="T40" s="8"/>
-      <c r="U40" s="8"/>
-      <c r="V40" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S40" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T40" s="27"/>
+      <c r="U40" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V40" s="30"/>
       <c r="W40" s="8"/>
       <c r="X40" s="8"/>
       <c r="Y40" s="21"/>
       <c r="Z40" s="8"/>
       <c r="AA40" s="8"/>
       <c r="AB40" s="8"/>
-      <c r="AC40" s="29"/>
+      <c r="AC40" s="30"/>
       <c r="AD40" s="8"/>
       <c r="AE40" s="8"/>
       <c r="AF40" s="21"/>
       <c r="AG40" s="8"/>
       <c r="AH40" s="8"/>
       <c r="AI40" s="8"/>
-      <c r="AJ40" s="29"/>
+      <c r="AJ40" s="30"/>
       <c r="AK40" s="5">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL40" s="5">
         <f t="shared" si="5"/>
@@ -4367,59 +4519,63 @@
         <v>8</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G41" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H41" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H41" s="30"/>
       <c r="I41" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J41" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K41" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L41" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M41" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N41" s="30"/>
-      <c r="O41" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N41" s="31"/>
+      <c r="O41" s="30"/>
       <c r="P41" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q41" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R41" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S41" s="8"/>
-      <c r="T41" s="8"/>
-      <c r="U41" s="8"/>
-      <c r="V41" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S41" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T41" s="27"/>
+      <c r="U41" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V41" s="30"/>
       <c r="W41" s="8"/>
       <c r="X41" s="8"/>
       <c r="Y41" s="21"/>
       <c r="Z41" s="8"/>
       <c r="AA41" s="8"/>
       <c r="AB41" s="8"/>
-      <c r="AC41" s="29"/>
+      <c r="AC41" s="30"/>
       <c r="AD41" s="8"/>
       <c r="AE41" s="8"/>
       <c r="AF41" s="21"/>
       <c r="AG41" s="8"/>
       <c r="AH41" s="8"/>
       <c r="AI41" s="8"/>
-      <c r="AJ41" s="29"/>
+      <c r="AJ41" s="30"/>
       <c r="AK41" s="5">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL41" s="5">
         <f t="shared" si="5"/>
@@ -4443,59 +4599,63 @@
         <v>8</v>
       </c>
       <c r="F42" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G42" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H42" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H42" s="30"/>
       <c r="I42" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J42" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K42" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L42" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M42" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N42" s="30"/>
-      <c r="O42" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N42" s="31"/>
+      <c r="O42" s="30"/>
       <c r="P42" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q42" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R42" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S42" s="8"/>
-      <c r="T42" s="8"/>
-      <c r="U42" s="8"/>
-      <c r="V42" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S42" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T42" s="27"/>
+      <c r="U42" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V42" s="30"/>
       <c r="W42" s="8"/>
       <c r="X42" s="8"/>
       <c r="Y42" s="21"/>
       <c r="Z42" s="8"/>
       <c r="AA42" s="8"/>
       <c r="AB42" s="8"/>
-      <c r="AC42" s="29"/>
+      <c r="AC42" s="30"/>
       <c r="AD42" s="8"/>
       <c r="AE42" s="8"/>
       <c r="AF42" s="21"/>
       <c r="AG42" s="8"/>
       <c r="AH42" s="8"/>
       <c r="AI42" s="8"/>
-      <c r="AJ42" s="29"/>
+      <c r="AJ42" s="30"/>
       <c r="AK42" s="5">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL42" s="5">
         <f t="shared" si="5"/>
@@ -4519,59 +4679,63 @@
         <v>8</v>
       </c>
       <c r="F43" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G43" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H43" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H43" s="30"/>
       <c r="I43" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J43" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K43" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L43" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M43" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N43" s="30"/>
-      <c r="O43" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N43" s="31"/>
+      <c r="O43" s="30"/>
       <c r="P43" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q43" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R43" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S43" s="8"/>
-      <c r="T43" s="8"/>
-      <c r="U43" s="8"/>
-      <c r="V43" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S43" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T43" s="27"/>
+      <c r="U43" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V43" s="30"/>
       <c r="W43" s="8"/>
       <c r="X43" s="8"/>
       <c r="Y43" s="21"/>
       <c r="Z43" s="8"/>
       <c r="AA43" s="8"/>
       <c r="AB43" s="8"/>
-      <c r="AC43" s="29"/>
+      <c r="AC43" s="30"/>
       <c r="AD43" s="8"/>
       <c r="AE43" s="8"/>
       <c r="AF43" s="21"/>
       <c r="AG43" s="8"/>
       <c r="AH43" s="8"/>
       <c r="AI43" s="8"/>
-      <c r="AJ43" s="29"/>
+      <c r="AJ43" s="30"/>
       <c r="AK43" s="5">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL43" s="5">
         <f t="shared" si="5"/>
@@ -4595,59 +4759,63 @@
         <v>8</v>
       </c>
       <c r="F44" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G44" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="H44" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="H44" s="30"/>
       <c r="I44" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J44" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K44" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L44" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M44" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N44" s="30"/>
-      <c r="O44" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N44" s="31"/>
+      <c r="O44" s="30"/>
       <c r="P44" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q44" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R44" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S44" s="8"/>
-      <c r="T44" s="8"/>
-      <c r="U44" s="8"/>
-      <c r="V44" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S44" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T44" s="27"/>
+      <c r="U44" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V44" s="30"/>
       <c r="W44" s="8"/>
       <c r="X44" s="8"/>
       <c r="Y44" s="21"/>
       <c r="Z44" s="8"/>
       <c r="AA44" s="8"/>
       <c r="AB44" s="8"/>
-      <c r="AC44" s="29"/>
+      <c r="AC44" s="30"/>
       <c r="AD44" s="8"/>
       <c r="AE44" s="8"/>
       <c r="AF44" s="21"/>
       <c r="AG44" s="8"/>
       <c r="AH44" s="8"/>
       <c r="AI44" s="8"/>
-      <c r="AJ44" s="29"/>
+      <c r="AJ44" s="30"/>
       <c r="AK44" s="5">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL44" s="5">
         <f t="shared" si="5"/>
@@ -4671,59 +4839,63 @@
         <v>8</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H45" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H45" s="30"/>
       <c r="I45" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J45" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K45" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L45" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M45" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N45" s="30"/>
-      <c r="O45" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N45" s="31"/>
+      <c r="O45" s="30"/>
       <c r="P45" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q45" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R45" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S45" s="8"/>
-      <c r="T45" s="8"/>
-      <c r="U45" s="8"/>
-      <c r="V45" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S45" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T45" s="27"/>
+      <c r="U45" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V45" s="30"/>
       <c r="W45" s="8"/>
       <c r="X45" s="8"/>
       <c r="Y45" s="21"/>
       <c r="Z45" s="8"/>
       <c r="AA45" s="8"/>
       <c r="AB45" s="8"/>
-      <c r="AC45" s="29"/>
+      <c r="AC45" s="30"/>
       <c r="AD45" s="8"/>
       <c r="AE45" s="8"/>
       <c r="AF45" s="21"/>
       <c r="AG45" s="8"/>
       <c r="AH45" s="8"/>
       <c r="AI45" s="8"/>
-      <c r="AJ45" s="29"/>
+      <c r="AJ45" s="30"/>
       <c r="AK45" s="5">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL45" s="5">
         <f t="shared" si="5"/>
@@ -4747,59 +4919,63 @@
         <v>8</v>
       </c>
       <c r="F46" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G46" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H46" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H46" s="30"/>
       <c r="I46" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J46" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K46" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L46" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M46" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N46" s="30"/>
-      <c r="O46" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N46" s="31"/>
+      <c r="O46" s="30"/>
       <c r="P46" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q46" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R46" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S46" s="8"/>
-      <c r="T46" s="8"/>
-      <c r="U46" s="8"/>
-      <c r="V46" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S46" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T46" s="27"/>
+      <c r="U46" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V46" s="30"/>
       <c r="W46" s="8"/>
       <c r="X46" s="8"/>
       <c r="Y46" s="21"/>
       <c r="Z46" s="8"/>
       <c r="AA46" s="8"/>
       <c r="AB46" s="8"/>
-      <c r="AC46" s="29"/>
+      <c r="AC46" s="30"/>
       <c r="AD46" s="8"/>
       <c r="AE46" s="8"/>
       <c r="AF46" s="21"/>
       <c r="AG46" s="8"/>
       <c r="AH46" s="8"/>
       <c r="AI46" s="8"/>
-      <c r="AJ46" s="29"/>
+      <c r="AJ46" s="30"/>
       <c r="AK46" s="5">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL46" s="5">
         <f t="shared" si="5"/>
@@ -4821,59 +4997,63 @@
         <v>8</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G47" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H47" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H47" s="30"/>
       <c r="I47" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J47" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K47" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L47" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M47" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N47" s="30"/>
-      <c r="O47" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N47" s="31"/>
+      <c r="O47" s="30"/>
       <c r="P47" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q47" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R47" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S47" s="8"/>
-      <c r="T47" s="8"/>
-      <c r="U47" s="8"/>
-      <c r="V47" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S47" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T47" s="27"/>
+      <c r="U47" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V47" s="30"/>
       <c r="W47" s="8"/>
       <c r="X47" s="8"/>
       <c r="Y47" s="21"/>
       <c r="Z47" s="8"/>
       <c r="AA47" s="8"/>
       <c r="AB47" s="8"/>
-      <c r="AC47" s="29"/>
+      <c r="AC47" s="30"/>
       <c r="AD47" s="8"/>
       <c r="AE47" s="8"/>
       <c r="AF47" s="21"/>
       <c r="AG47" s="8"/>
       <c r="AH47" s="8"/>
       <c r="AI47" s="8"/>
-      <c r="AJ47" s="29"/>
+      <c r="AJ47" s="30"/>
       <c r="AK47" s="5">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL47" s="5">
         <f t="shared" si="5"/>
@@ -4897,63 +5077,67 @@
         <v>8</v>
       </c>
       <c r="F48" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G48" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H48" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H48" s="30"/>
       <c r="I48" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J48" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K48" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L48" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M48" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N48" s="30"/>
-      <c r="O48" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N48" s="31"/>
+      <c r="O48" s="30"/>
       <c r="P48" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q48" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R48" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S48" s="8"/>
-      <c r="T48" s="8"/>
-      <c r="U48" s="8"/>
-      <c r="V48" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S48" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="T48" s="27"/>
+      <c r="U48" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V48" s="30"/>
       <c r="W48" s="8"/>
       <c r="X48" s="8"/>
       <c r="Y48" s="21"/>
       <c r="Z48" s="8"/>
       <c r="AA48" s="8"/>
       <c r="AB48" s="8"/>
-      <c r="AC48" s="29"/>
+      <c r="AC48" s="30"/>
       <c r="AD48" s="8"/>
       <c r="AE48" s="8"/>
       <c r="AF48" s="21"/>
       <c r="AG48" s="8"/>
       <c r="AH48" s="8"/>
       <c r="AI48" s="8"/>
-      <c r="AJ48" s="29"/>
+      <c r="AJ48" s="30"/>
       <c r="AK48" s="5">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL48" s="5">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
@@ -4971,59 +5155,63 @@
         <v>8</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G49" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H49" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H49" s="30"/>
       <c r="I49" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J49" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K49" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L49" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M49" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N49" s="30"/>
-      <c r="O49" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N49" s="31"/>
+      <c r="O49" s="30"/>
       <c r="P49" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q49" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R49" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S49" s="8"/>
-      <c r="T49" s="8"/>
-      <c r="U49" s="8"/>
-      <c r="V49" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S49" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T49" s="27"/>
+      <c r="U49" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V49" s="30"/>
       <c r="W49" s="8"/>
       <c r="X49" s="8"/>
       <c r="Y49" s="21"/>
       <c r="Z49" s="8"/>
       <c r="AA49" s="8"/>
       <c r="AB49" s="8"/>
-      <c r="AC49" s="29"/>
+      <c r="AC49" s="30"/>
       <c r="AD49" s="8"/>
       <c r="AE49" s="8"/>
       <c r="AF49" s="21"/>
       <c r="AG49" s="8"/>
       <c r="AH49" s="8"/>
       <c r="AI49" s="8"/>
-      <c r="AJ49" s="29"/>
+      <c r="AJ49" s="30"/>
       <c r="AK49" s="5">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL49" s="5">
         <f t="shared" si="5"/>
@@ -5045,59 +5233,63 @@
         <v>8</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G50" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H50" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H50" s="30"/>
       <c r="I50" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J50" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K50" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L50" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M50" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N50" s="30"/>
-      <c r="O50" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N50" s="31"/>
+      <c r="O50" s="30"/>
       <c r="P50" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q50" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R50" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S50" s="8"/>
-      <c r="T50" s="8"/>
-      <c r="U50" s="8"/>
-      <c r="V50" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S50" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T50" s="27"/>
+      <c r="U50" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="V50" s="30"/>
       <c r="W50" s="8"/>
       <c r="X50" s="8"/>
       <c r="Y50" s="21"/>
       <c r="Z50" s="8"/>
       <c r="AA50" s="8"/>
       <c r="AB50" s="8"/>
-      <c r="AC50" s="29"/>
+      <c r="AC50" s="30"/>
       <c r="AD50" s="8"/>
       <c r="AE50" s="8"/>
       <c r="AF50" s="21"/>
       <c r="AG50" s="8"/>
       <c r="AH50" s="8"/>
       <c r="AI50" s="8"/>
-      <c r="AJ50" s="29"/>
+      <c r="AJ50" s="30"/>
       <c r="AK50" s="5">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL50" s="5">
         <f t="shared" si="5"/>
@@ -5119,59 +5311,63 @@
         <v>8</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G51" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H51" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H51" s="30"/>
       <c r="I51" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J51" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K51" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L51" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M51" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N51" s="30"/>
-      <c r="O51" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N51" s="31"/>
+      <c r="O51" s="30"/>
       <c r="P51" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q51" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R51" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S51" s="8"/>
-      <c r="T51" s="8"/>
-      <c r="U51" s="8"/>
-      <c r="V51" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S51" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T51" s="27"/>
+      <c r="U51" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V51" s="30"/>
       <c r="W51" s="8"/>
       <c r="X51" s="8"/>
       <c r="Y51" s="21"/>
       <c r="Z51" s="8"/>
       <c r="AA51" s="8"/>
       <c r="AB51" s="8"/>
-      <c r="AC51" s="29"/>
+      <c r="AC51" s="30"/>
       <c r="AD51" s="8"/>
       <c r="AE51" s="8"/>
       <c r="AF51" s="21"/>
       <c r="AG51" s="8"/>
       <c r="AH51" s="8"/>
       <c r="AI51" s="8"/>
-      <c r="AJ51" s="29"/>
+      <c r="AJ51" s="30"/>
       <c r="AK51" s="5">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL51" s="5">
         <f t="shared" si="5"/>
@@ -5193,63 +5389,67 @@
         <v>8</v>
       </c>
       <c r="F52" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G52" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H52" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H52" s="30"/>
       <c r="I52" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J52" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K52" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L52" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M52" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N52" s="30"/>
-      <c r="O52" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N52" s="31"/>
+      <c r="O52" s="30"/>
       <c r="P52" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q52" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R52" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S52" s="8"/>
-      <c r="T52" s="8"/>
-      <c r="U52" s="8"/>
-      <c r="V52" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S52" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="T52" s="27"/>
+      <c r="U52" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V52" s="30"/>
       <c r="W52" s="8"/>
       <c r="X52" s="8"/>
       <c r="Y52" s="21"/>
       <c r="Z52" s="8"/>
       <c r="AA52" s="8"/>
       <c r="AB52" s="8"/>
-      <c r="AC52" s="29"/>
+      <c r="AC52" s="30"/>
       <c r="AD52" s="8"/>
       <c r="AE52" s="8"/>
       <c r="AF52" s="21"/>
       <c r="AG52" s="8"/>
       <c r="AH52" s="8"/>
       <c r="AI52" s="8"/>
-      <c r="AJ52" s="29"/>
+      <c r="AJ52" s="30"/>
       <c r="AK52" s="5">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL52" s="5">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
@@ -5267,59 +5467,63 @@
         <v>8</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G53" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H53" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H53" s="30"/>
       <c r="I53" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J53" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K53" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L53" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M53" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="N53" s="30"/>
-      <c r="O53" s="29"/>
+        <v>126</v>
+      </c>
+      <c r="N53" s="31"/>
+      <c r="O53" s="30"/>
       <c r="P53" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q53" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R53" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S53" s="8"/>
-      <c r="T53" s="8"/>
-      <c r="U53" s="8"/>
-      <c r="V53" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S53" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T53" s="27"/>
+      <c r="U53" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="V53" s="30"/>
       <c r="W53" s="8"/>
       <c r="X53" s="8"/>
       <c r="Y53" s="21"/>
       <c r="Z53" s="8"/>
       <c r="AA53" s="8"/>
       <c r="AB53" s="8"/>
-      <c r="AC53" s="29"/>
+      <c r="AC53" s="30"/>
       <c r="AD53" s="8"/>
       <c r="AE53" s="8"/>
       <c r="AF53" s="21"/>
       <c r="AG53" s="8"/>
       <c r="AH53" s="8"/>
       <c r="AI53" s="8"/>
-      <c r="AJ53" s="29"/>
+      <c r="AJ53" s="30"/>
       <c r="AK53" s="5">
         <f t="shared" ref="AK53:AK54" si="6">COUNTIF(F53:AJ53,"P")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL53" s="5">
         <f t="shared" ref="AL53:AL54" si="7">COUNTIF(F53:AJ53,"A")</f>
@@ -5332,68 +5536,72 @@
       </c>
       <c r="B54" s="17"/>
       <c r="C54" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="D54" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="D54" s="17" t="s">
-        <v>120</v>
-      </c>
       <c r="E54" s="7" t="s">
         <v>8</v>
       </c>
       <c r="F54" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G54" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H54" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H54" s="30"/>
       <c r="I54" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J54" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K54" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L54" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M54" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N54" s="30"/>
-      <c r="O54" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N54" s="31"/>
+      <c r="O54" s="30"/>
       <c r="P54" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q54" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R54" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S54" s="8"/>
-      <c r="T54" s="8"/>
-      <c r="U54" s="8"/>
-      <c r="V54" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S54" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T54" s="27"/>
+      <c r="U54" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V54" s="30"/>
       <c r="W54" s="8"/>
       <c r="X54" s="8"/>
       <c r="Y54" s="21"/>
       <c r="Z54" s="8"/>
       <c r="AA54" s="8"/>
       <c r="AB54" s="8"/>
-      <c r="AC54" s="29"/>
+      <c r="AC54" s="30"/>
       <c r="AD54" s="8"/>
       <c r="AE54" s="8"/>
       <c r="AF54" s="21"/>
       <c r="AG54" s="8"/>
       <c r="AH54" s="8"/>
       <c r="AI54" s="8"/>
-      <c r="AJ54" s="29"/>
+      <c r="AJ54" s="30"/>
       <c r="AK54" s="5">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL54" s="5">
         <f t="shared" si="7"/>
@@ -5406,66 +5614,70 @@
       </c>
       <c r="B55" s="17"/>
       <c r="C55" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D55" s="17"/>
       <c r="E55" s="7" t="s">
         <v>8</v>
       </c>
       <c r="F55" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G55" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H55" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H55" s="30"/>
       <c r="I55" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J55" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K55" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L55" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M55" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N55" s="30"/>
-      <c r="O55" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="N55" s="31"/>
+      <c r="O55" s="30"/>
       <c r="P55" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q55" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R55" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S55" s="8"/>
-      <c r="T55" s="8"/>
-      <c r="U55" s="8"/>
-      <c r="V55" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S55" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T55" s="27"/>
+      <c r="U55" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V55" s="30"/>
       <c r="W55" s="8"/>
       <c r="X55" s="8"/>
       <c r="Y55" s="21"/>
       <c r="Z55" s="8"/>
       <c r="AA55" s="8"/>
       <c r="AB55" s="8"/>
-      <c r="AC55" s="29"/>
+      <c r="AC55" s="30"/>
       <c r="AD55" s="8"/>
       <c r="AE55" s="8"/>
       <c r="AF55" s="21"/>
       <c r="AG55" s="8"/>
       <c r="AH55" s="8"/>
       <c r="AI55" s="8"/>
-      <c r="AJ55" s="29"/>
+      <c r="AJ55" s="30"/>
       <c r="AK55" s="5">
         <f t="shared" ref="AK55" si="8">COUNTIF(F55:AJ55,"P")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL55" s="5">
         <f t="shared" ref="AL55" si="9">COUNTIF(F55:AJ55,"A")</f>
@@ -5478,70 +5690,74 @@
       </c>
       <c r="B56" s="17"/>
       <c r="C56" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D56" s="17"/>
       <c r="E56" s="7" t="s">
         <v>8</v>
       </c>
       <c r="F56" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G56" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="H56" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="H56" s="30"/>
       <c r="I56" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J56" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K56" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L56" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M56" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="N56" s="30"/>
-      <c r="O56" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="N56" s="31"/>
+      <c r="O56" s="30"/>
       <c r="P56" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q56" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R56" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="S56" s="8"/>
-      <c r="T56" s="8"/>
-      <c r="U56" s="8"/>
-      <c r="V56" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="S56" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="T56" s="27"/>
+      <c r="U56" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="V56" s="30"/>
       <c r="W56" s="8"/>
       <c r="X56" s="8"/>
       <c r="Y56" s="21"/>
       <c r="Z56" s="8"/>
       <c r="AA56" s="8"/>
       <c r="AB56" s="8"/>
-      <c r="AC56" s="29"/>
+      <c r="AC56" s="30"/>
       <c r="AD56" s="8"/>
       <c r="AE56" s="8"/>
       <c r="AF56" s="21"/>
       <c r="AG56" s="8"/>
       <c r="AH56" s="8"/>
       <c r="AI56" s="8"/>
-      <c r="AJ56" s="29"/>
+      <c r="AJ56" s="30"/>
       <c r="AK56" s="5">
         <f t="shared" ref="AK56:AK58" si="10">COUNTIF(F56:AJ56,"P")</f>
         <v>2</v>
       </c>
       <c r="AL56" s="5">
         <f t="shared" ref="AL56:AL58" si="11">COUNTIF(F56:AJ56,"A")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
@@ -5550,68 +5766,72 @@
       </c>
       <c r="B57" s="17"/>
       <c r="C57" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="D57" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="D57" s="17" t="s">
-        <v>129</v>
-      </c>
       <c r="E57" s="7" t="s">
         <v>8</v>
       </c>
       <c r="F57" s="20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G57" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="H57" s="29"/>
+        <v>130</v>
+      </c>
+      <c r="H57" s="30"/>
       <c r="I57" s="20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J57" s="20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K57" s="20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L57" s="20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M57" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="N57" s="30"/>
-      <c r="O57" s="29"/>
+        <v>130</v>
+      </c>
+      <c r="N57" s="31"/>
+      <c r="O57" s="30"/>
       <c r="P57" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q57" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R57" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S57" s="8"/>
-      <c r="T57" s="8"/>
-      <c r="U57" s="8"/>
-      <c r="V57" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S57" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T57" s="27"/>
+      <c r="U57" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V57" s="30"/>
       <c r="W57" s="8"/>
       <c r="X57" s="8"/>
       <c r="Y57" s="21"/>
       <c r="Z57" s="8"/>
       <c r="AA57" s="8"/>
       <c r="AB57" s="8"/>
-      <c r="AC57" s="29"/>
+      <c r="AC57" s="30"/>
       <c r="AD57" s="8"/>
       <c r="AE57" s="8"/>
       <c r="AF57" s="21"/>
       <c r="AG57" s="8"/>
       <c r="AH57" s="8"/>
       <c r="AI57" s="8"/>
-      <c r="AJ57" s="29"/>
+      <c r="AJ57" s="30"/>
       <c r="AK57" s="5">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL57" s="5">
         <f t="shared" si="11"/>
@@ -5624,68 +5844,72 @@
       </c>
       <c r="B58" s="17"/>
       <c r="C58" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="D58" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="D58" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" s="20" t="s">
-        <v>131</v>
-      </c>
       <c r="G58" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="H58" s="29"/>
+        <v>130</v>
+      </c>
+      <c r="H58" s="30"/>
       <c r="I58" s="20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J58" s="20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K58" s="20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L58" s="20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M58" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="N58" s="30"/>
-      <c r="O58" s="29"/>
+        <v>130</v>
+      </c>
+      <c r="N58" s="31"/>
+      <c r="O58" s="30"/>
       <c r="P58" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q58" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R58" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S58" s="8"/>
-      <c r="T58" s="8"/>
-      <c r="U58" s="8"/>
-      <c r="V58" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="S58" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="T58" s="27"/>
+      <c r="U58" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="V58" s="30"/>
       <c r="W58" s="8"/>
       <c r="X58" s="8"/>
       <c r="Y58" s="21"/>
       <c r="Z58" s="8"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="29"/>
+      <c r="AC58" s="30"/>
       <c r="AD58" s="8"/>
       <c r="AE58" s="8"/>
       <c r="AF58" s="21"/>
       <c r="AG58" s="8"/>
       <c r="AH58" s="8"/>
       <c r="AI58" s="8"/>
-      <c r="AJ58" s="29"/>
+      <c r="AJ58" s="30"/>
       <c r="AK58" s="5">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL58" s="5">
         <f t="shared" si="11"/>
@@ -5693,7 +5917,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
     <mergeCell ref="A2:AJ2"/>
     <mergeCell ref="A1:AJ1"/>
     <mergeCell ref="H5:H58"/>
@@ -5712,58 +5936,59 @@
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="T5:T58"/>
   </mergeCells>
-  <conditionalFormatting sqref="AM4:AN4 F3:AJ5 F6:G58 I6:M58 AG6:AI58 AD6:AE58 Z6:AB58 W6:X58 P6:U58">
+  <conditionalFormatting sqref="F3:AJ5 F6:G58 I6:M58 P6:S58 U6:U58 W6:X58 Z6:AB58 AD6:AE58 AG6:AI58 AM4:AN4">
     <cfRule type="expression" dxfId="10" priority="18">
       <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:AJ5 F6:G58 I6:M58 AG6:AI58 AD6:AE58 Z6:AB58 W6:X58 P6:U58">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+  <conditionalFormatting sqref="F3:AJ5 F6:G58 I6:M58 P6:S58 U6:U58 W6:AB58 AD6:AI58">
+    <cfRule type="expression" dxfId="9" priority="2">
+      <formula>F$4=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:AJ5 F6:G58 I6:M58 P6:S58 U6:U58 W6:X58 Z6:AB58 AD6:AE58 AG6:AI58">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F5:AJ5 F6:G58 I6:M58 P6:S58 U6:U58 W6:AB58 AD6:AI58">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+      <formula>"L"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AK3:AL3 AK5:AL58">
-    <cfRule type="expression" dxfId="7" priority="20">
+    <cfRule type="expression" dxfId="5" priority="20">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM5:AM6">
-    <cfRule type="expression" dxfId="6" priority="13">
+    <cfRule type="expression" dxfId="4" priority="13">
       <formula>AM$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM9:AM12">
-    <cfRule type="expression" dxfId="5" priority="7">
+    <cfRule type="expression" dxfId="3" priority="7">
       <formula>AM$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM17:AM20">
-    <cfRule type="expression" dxfId="4" priority="6">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>AM$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN9:AP9">
-    <cfRule type="expression" dxfId="3" priority="8">
+    <cfRule type="expression" dxfId="1" priority="8">
       <formula>AN$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN17:AP17">
-    <cfRule type="expression" dxfId="2" priority="5">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>AN$3="Sun"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:AJ5 F6:G58 I6:M58 P6:U58 W6:AB58 AD6:AI58">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>F$4=TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5:AJ5 F6:G58 I6:M58 P6:U58 W6:AB58 AD6:AI58">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Sindhi Muslim/Student Attendance/ECE (ROSE)/ECE (ROSE) Monthly Attendance - November-2024.xlsx
+++ b/Sindhi Muslim/Student Attendance/ECE (ROSE)/ECE (ROSE) Monthly Attendance - November-2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Student Attendance\ECE (ROSE)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB192B1-9D67-4E99-8F14-38EA5E33FB1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E2ADD6-C952-403F-A873-3AC0BF0A2592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -665,6 +665,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="17" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -682,18 +694,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1111,104 +1111,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="29"/>
-      <c r="V1" s="29"/>
-      <c r="W1" s="29"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="29"/>
-      <c r="AA1" s="29"/>
-      <c r="AB1" s="29"/>
-      <c r="AC1" s="29"/>
-      <c r="AD1" s="29"/>
-      <c r="AE1" s="29"/>
-      <c r="AF1" s="29"/>
-      <c r="AG1" s="29"/>
-      <c r="AH1" s="29"/>
-      <c r="AI1" s="29"/>
-      <c r="AJ1" s="29"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="23"/>
+      <c r="AB1" s="23"/>
+      <c r="AC1" s="23"/>
+      <c r="AD1" s="23"/>
+      <c r="AE1" s="23"/>
+      <c r="AF1" s="23"/>
+      <c r="AG1" s="23"/>
+      <c r="AH1" s="23"/>
+      <c r="AI1" s="23"/>
+      <c r="AJ1" s="23"/>
       <c r="AK1" s="19"/>
       <c r="AL1" s="19"/>
     </row>
     <row r="2" spans="1:42" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="28"/>
-      <c r="V2" s="28"/>
-      <c r="W2" s="28"/>
-      <c r="X2" s="28"/>
-      <c r="Y2" s="28"/>
-      <c r="Z2" s="28"/>
-      <c r="AA2" s="28"/>
-      <c r="AB2" s="28"/>
-      <c r="AC2" s="28"/>
-      <c r="AD2" s="28"/>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="28"/>
-      <c r="AG2" s="28"/>
-      <c r="AH2" s="28"/>
-      <c r="AI2" s="28"/>
-      <c r="AJ2" s="28"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
+      <c r="U2" s="22"/>
+      <c r="V2" s="22"/>
+      <c r="W2" s="22"/>
+      <c r="X2" s="22"/>
+      <c r="Y2" s="22"/>
+      <c r="Z2" s="22"/>
+      <c r="AA2" s="22"/>
+      <c r="AB2" s="22"/>
+      <c r="AC2" s="22"/>
+      <c r="AD2" s="22"/>
+      <c r="AE2" s="22"/>
+      <c r="AF2" s="22"/>
+      <c r="AG2" s="22"/>
+      <c r="AH2" s="22"/>
+      <c r="AI2" s="22"/>
+      <c r="AJ2" s="22"/>
       <c r="AK2" s="18"/>
       <c r="AL2" s="18"/>
       <c r="AM2" s="18"/>
     </row>
     <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="30" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -1335,25 +1335,25 @@
         <f t="shared" si="1"/>
         <v>Sun</v>
       </c>
-      <c r="AK3" s="25" t="s">
+      <c r="AK3" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="AL3" s="25" t="s">
+      <c r="AL3" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="AM3" s="22" t="s">
+      <c r="AM3" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="AN3" s="24"/>
+      <c r="AN3" s="28"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
     </row>
     <row r="4" spans="1:42" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="26"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
+      <c r="A4" s="30"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="16">
         <v>45597</v>
       </c>
@@ -1447,8 +1447,8 @@
       <c r="AJ4" s="16">
         <v>45627</v>
       </c>
-      <c r="AK4" s="25"/>
-      <c r="AL4" s="25"/>
+      <c r="AK4" s="29"/>
+      <c r="AL4" s="29"/>
       <c r="AM4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1478,7 +1478,7 @@
       <c r="G5" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H5" s="30" t="s">
+      <c r="H5" s="24" t="s">
         <v>124</v>
       </c>
       <c r="I5" s="20" t="s">
@@ -1496,10 +1496,10 @@
       <c r="M5" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N5" s="31" t="s">
+      <c r="N5" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="O5" s="30" t="s">
+      <c r="O5" s="24" t="s">
         <v>124</v>
       </c>
       <c r="P5" s="8" t="s">
@@ -1514,13 +1514,13 @@
       <c r="S5" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T5" s="27" t="s">
+      <c r="T5" s="31" t="s">
         <v>131</v>
       </c>
       <c r="U5" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V5" s="30" t="s">
+      <c r="V5" s="24" t="s">
         <v>124</v>
       </c>
       <c r="W5" s="8"/>
@@ -1529,7 +1529,7 @@
       <c r="Z5" s="8"/>
       <c r="AA5" s="8"/>
       <c r="AB5" s="8"/>
-      <c r="AC5" s="30" t="s">
+      <c r="AC5" s="24" t="s">
         <v>124</v>
       </c>
       <c r="AD5" s="8"/>
@@ -1538,7 +1538,7 @@
       <c r="AG5" s="8"/>
       <c r="AH5" s="8"/>
       <c r="AI5" s="8"/>
-      <c r="AJ5" s="30" t="s">
+      <c r="AJ5" s="24" t="s">
         <v>124</v>
       </c>
       <c r="AK5" s="5">
@@ -1580,7 +1580,7 @@
       <c r="G6" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H6" s="30"/>
+      <c r="H6" s="24"/>
       <c r="I6" s="20" t="s">
         <v>122</v>
       </c>
@@ -1596,8 +1596,8 @@
       <c r="M6" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="N6" s="31"/>
-      <c r="O6" s="30"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="24"/>
       <c r="P6" s="8" t="s">
         <v>122</v>
       </c>
@@ -1610,25 +1610,25 @@
       <c r="S6" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="T6" s="27"/>
+      <c r="T6" s="31"/>
       <c r="U6" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="V6" s="30"/>
+      <c r="V6" s="24"/>
       <c r="W6" s="8"/>
       <c r="X6" s="8"/>
       <c r="Y6" s="21"/>
       <c r="Z6" s="8"/>
       <c r="AA6" s="8"/>
       <c r="AB6" s="8"/>
-      <c r="AC6" s="30"/>
+      <c r="AC6" s="24"/>
       <c r="AD6" s="8"/>
       <c r="AE6" s="8"/>
       <c r="AF6" s="21"/>
       <c r="AG6" s="8"/>
       <c r="AH6" s="8"/>
       <c r="AI6" s="8"/>
-      <c r="AJ6" s="30"/>
+      <c r="AJ6" s="24"/>
       <c r="AK6" s="5">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -1666,7 +1666,7 @@
       <c r="G7" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="H7" s="30"/>
+      <c r="H7" s="24"/>
       <c r="I7" s="20" t="s">
         <v>122</v>
       </c>
@@ -1682,8 +1682,8 @@
       <c r="M7" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N7" s="31"/>
-      <c r="O7" s="30"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="24"/>
       <c r="P7" s="8" t="s">
         <v>122</v>
       </c>
@@ -1696,25 +1696,25 @@
       <c r="S7" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T7" s="27"/>
+      <c r="T7" s="31"/>
       <c r="U7" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="V7" s="30"/>
+      <c r="V7" s="24"/>
       <c r="W7" s="8"/>
       <c r="X7" s="8"/>
       <c r="Y7" s="21"/>
       <c r="Z7" s="8"/>
       <c r="AA7" s="8"/>
       <c r="AB7" s="8"/>
-      <c r="AC7" s="30"/>
+      <c r="AC7" s="24"/>
       <c r="AD7" s="8"/>
       <c r="AE7" s="8"/>
       <c r="AF7" s="21"/>
       <c r="AG7" s="8"/>
       <c r="AH7" s="8"/>
       <c r="AI7" s="8"/>
-      <c r="AJ7" s="30"/>
+      <c r="AJ7" s="24"/>
       <c r="AK7" s="5">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -1750,7 +1750,7 @@
       <c r="G8" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="H8" s="30"/>
+      <c r="H8" s="24"/>
       <c r="I8" s="20" t="s">
         <v>122</v>
       </c>
@@ -1766,8 +1766,8 @@
       <c r="M8" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N8" s="31"/>
-      <c r="O8" s="30"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="24"/>
       <c r="P8" s="8" t="s">
         <v>122</v>
       </c>
@@ -1780,25 +1780,25 @@
       <c r="S8" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T8" s="27"/>
+      <c r="T8" s="31"/>
       <c r="U8" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V8" s="30"/>
+      <c r="V8" s="24"/>
       <c r="W8" s="8"/>
       <c r="X8" s="8"/>
       <c r="Y8" s="21"/>
       <c r="Z8" s="8"/>
       <c r="AA8" s="8"/>
       <c r="AB8" s="8"/>
-      <c r="AC8" s="30"/>
+      <c r="AC8" s="24"/>
       <c r="AD8" s="8"/>
       <c r="AE8" s="8"/>
       <c r="AF8" s="21"/>
       <c r="AG8" s="8"/>
       <c r="AH8" s="8"/>
       <c r="AI8" s="8"/>
-      <c r="AJ8" s="30"/>
+      <c r="AJ8" s="24"/>
       <c r="AK8" s="5">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -1807,12 +1807,12 @@
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AM8" s="22" t="s">
+      <c r="AM8" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="AN8" s="23"/>
-      <c r="AO8" s="23"/>
-      <c r="AP8" s="24"/>
+      <c r="AN8" s="27"/>
+      <c r="AO8" s="27"/>
+      <c r="AP8" s="28"/>
     </row>
     <row r="9" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
@@ -1836,7 +1836,7 @@
       <c r="G9" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H9" s="30"/>
+      <c r="H9" s="24"/>
       <c r="I9" s="20" t="s">
         <v>122</v>
       </c>
@@ -1852,8 +1852,8 @@
       <c r="M9" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="N9" s="31"/>
-      <c r="O9" s="30"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="24"/>
       <c r="P9" s="8" t="s">
         <v>126</v>
       </c>
@@ -1866,25 +1866,25 @@
       <c r="S9" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="T9" s="27"/>
+      <c r="T9" s="31"/>
       <c r="U9" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="V9" s="30"/>
+      <c r="V9" s="24"/>
       <c r="W9" s="8"/>
       <c r="X9" s="8"/>
       <c r="Y9" s="21"/>
       <c r="Z9" s="8"/>
       <c r="AA9" s="8"/>
       <c r="AB9" s="8"/>
-      <c r="AC9" s="30"/>
+      <c r="AC9" s="24"/>
       <c r="AD9" s="8"/>
       <c r="AE9" s="8"/>
       <c r="AF9" s="21"/>
       <c r="AG9" s="8"/>
       <c r="AH9" s="8"/>
       <c r="AI9" s="8"/>
-      <c r="AJ9" s="30"/>
+      <c r="AJ9" s="24"/>
       <c r="AK9" s="5">
         <f t="shared" si="2"/>
         <v>3</v>
@@ -1928,7 +1928,7 @@
       <c r="G10" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H10" s="30"/>
+      <c r="H10" s="24"/>
       <c r="I10" s="20" t="s">
         <v>122</v>
       </c>
@@ -1944,8 +1944,8 @@
       <c r="M10" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N10" s="31"/>
-      <c r="O10" s="30"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="24"/>
       <c r="P10" s="8" t="s">
         <v>123</v>
       </c>
@@ -1958,25 +1958,25 @@
       <c r="S10" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T10" s="27"/>
+      <c r="T10" s="31"/>
       <c r="U10" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V10" s="30"/>
+      <c r="V10" s="24"/>
       <c r="W10" s="8"/>
       <c r="X10" s="8"/>
       <c r="Y10" s="21"/>
       <c r="Z10" s="8"/>
       <c r="AA10" s="8"/>
       <c r="AB10" s="8"/>
-      <c r="AC10" s="30"/>
+      <c r="AC10" s="24"/>
       <c r="AD10" s="8"/>
       <c r="AE10" s="8"/>
       <c r="AF10" s="21"/>
       <c r="AG10" s="8"/>
       <c r="AH10" s="8"/>
       <c r="AI10" s="8"/>
-      <c r="AJ10" s="30"/>
+      <c r="AJ10" s="24"/>
       <c r="AK10" s="5">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -2023,7 +2023,7 @@
       <c r="G11" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="H11" s="30"/>
+      <c r="H11" s="24"/>
       <c r="I11" s="20" t="s">
         <v>122</v>
       </c>
@@ -2039,8 +2039,8 @@
       <c r="M11" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="N11" s="31"/>
-      <c r="O11" s="30"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="24"/>
       <c r="P11" s="8" t="s">
         <v>122</v>
       </c>
@@ -2053,25 +2053,25 @@
       <c r="S11" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="T11" s="27"/>
+      <c r="T11" s="31"/>
       <c r="U11" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="V11" s="30"/>
+      <c r="V11" s="24"/>
       <c r="W11" s="8"/>
       <c r="X11" s="8"/>
       <c r="Y11" s="21"/>
       <c r="Z11" s="8"/>
       <c r="AA11" s="8"/>
       <c r="AB11" s="8"/>
-      <c r="AC11" s="30"/>
+      <c r="AC11" s="24"/>
       <c r="AD11" s="8"/>
       <c r="AE11" s="8"/>
       <c r="AF11" s="21"/>
       <c r="AG11" s="8"/>
       <c r="AH11" s="8"/>
       <c r="AI11" s="8"/>
-      <c r="AJ11" s="30"/>
+      <c r="AJ11" s="24"/>
       <c r="AK11" s="5">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -2116,7 +2116,7 @@
       <c r="G12" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="30"/>
+      <c r="H12" s="24"/>
       <c r="I12" s="20" t="s">
         <v>122</v>
       </c>
@@ -2132,8 +2132,8 @@
       <c r="M12" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N12" s="31"/>
-      <c r="O12" s="30"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="24"/>
       <c r="P12" s="8" t="s">
         <v>122</v>
       </c>
@@ -2146,25 +2146,25 @@
       <c r="S12" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="T12" s="27"/>
+      <c r="T12" s="31"/>
       <c r="U12" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V12" s="30"/>
+      <c r="V12" s="24"/>
       <c r="W12" s="8"/>
       <c r="X12" s="8"/>
       <c r="Y12" s="21"/>
       <c r="Z12" s="8"/>
       <c r="AA12" s="8"/>
       <c r="AB12" s="8"/>
-      <c r="AC12" s="30"/>
+      <c r="AC12" s="24"/>
       <c r="AD12" s="8"/>
       <c r="AE12" s="8"/>
       <c r="AF12" s="21"/>
       <c r="AG12" s="8"/>
       <c r="AH12" s="8"/>
       <c r="AI12" s="8"/>
-      <c r="AJ12" s="30"/>
+      <c r="AJ12" s="24"/>
       <c r="AK12" s="5">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -2211,7 +2211,7 @@
       <c r="G13" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="H13" s="30"/>
+      <c r="H13" s="24"/>
       <c r="I13" s="20" t="s">
         <v>122</v>
       </c>
@@ -2227,8 +2227,8 @@
       <c r="M13" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N13" s="31"/>
-      <c r="O13" s="30"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="24"/>
       <c r="P13" s="8" t="s">
         <v>122</v>
       </c>
@@ -2241,25 +2241,25 @@
       <c r="S13" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="T13" s="27"/>
+      <c r="T13" s="31"/>
       <c r="U13" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V13" s="30"/>
+      <c r="V13" s="24"/>
       <c r="W13" s="8"/>
       <c r="X13" s="8"/>
       <c r="Y13" s="21"/>
       <c r="Z13" s="8"/>
       <c r="AA13" s="8"/>
       <c r="AB13" s="8"/>
-      <c r="AC13" s="30"/>
+      <c r="AC13" s="24"/>
       <c r="AD13" s="8"/>
       <c r="AE13" s="8"/>
       <c r="AF13" s="21"/>
       <c r="AG13" s="8"/>
       <c r="AH13" s="8"/>
       <c r="AI13" s="8"/>
-      <c r="AJ13" s="30"/>
+      <c r="AJ13" s="24"/>
       <c r="AK13" s="5">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -2295,7 +2295,7 @@
       <c r="G14" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="H14" s="30"/>
+      <c r="H14" s="24"/>
       <c r="I14" s="20" t="s">
         <v>123</v>
       </c>
@@ -2311,8 +2311,8 @@
       <c r="M14" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="N14" s="31"/>
-      <c r="O14" s="30"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="24"/>
       <c r="P14" s="8" t="s">
         <v>123</v>
       </c>
@@ -2325,25 +2325,25 @@
       <c r="S14" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="T14" s="27"/>
+      <c r="T14" s="31"/>
       <c r="U14" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V14" s="30"/>
+      <c r="V14" s="24"/>
       <c r="W14" s="8"/>
       <c r="X14" s="8"/>
       <c r="Y14" s="21"/>
       <c r="Z14" s="8"/>
       <c r="AA14" s="8"/>
       <c r="AB14" s="8"/>
-      <c r="AC14" s="30"/>
+      <c r="AC14" s="24"/>
       <c r="AD14" s="8"/>
       <c r="AE14" s="8"/>
       <c r="AF14" s="21"/>
       <c r="AG14" s="8"/>
       <c r="AH14" s="8"/>
       <c r="AI14" s="8"/>
-      <c r="AJ14" s="30"/>
+      <c r="AJ14" s="24"/>
       <c r="AK14" s="5">
         <f t="shared" si="2"/>
         <v>1</v>
@@ -2379,7 +2379,7 @@
       <c r="G15" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H15" s="30"/>
+      <c r="H15" s="24"/>
       <c r="I15" s="20" t="s">
         <v>123</v>
       </c>
@@ -2395,8 +2395,8 @@
       <c r="M15" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N15" s="31"/>
-      <c r="O15" s="30"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="24"/>
       <c r="P15" s="8" t="s">
         <v>123</v>
       </c>
@@ -2409,25 +2409,25 @@
       <c r="S15" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T15" s="27"/>
+      <c r="T15" s="31"/>
       <c r="U15" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V15" s="30"/>
+      <c r="V15" s="24"/>
       <c r="W15" s="8"/>
       <c r="X15" s="8"/>
       <c r="Y15" s="21"/>
       <c r="Z15" s="8"/>
       <c r="AA15" s="8"/>
       <c r="AB15" s="8"/>
-      <c r="AC15" s="30"/>
+      <c r="AC15" s="24"/>
       <c r="AD15" s="8"/>
       <c r="AE15" s="8"/>
       <c r="AF15" s="21"/>
       <c r="AG15" s="8"/>
       <c r="AH15" s="8"/>
       <c r="AI15" s="8"/>
-      <c r="AJ15" s="30"/>
+      <c r="AJ15" s="24"/>
       <c r="AK15" s="5">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -2463,7 +2463,7 @@
       <c r="G16" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H16" s="30"/>
+      <c r="H16" s="24"/>
       <c r="I16" s="20" t="s">
         <v>122</v>
       </c>
@@ -2479,8 +2479,8 @@
       <c r="M16" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N16" s="31"/>
-      <c r="O16" s="30"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="24"/>
       <c r="P16" s="8" t="s">
         <v>122</v>
       </c>
@@ -2493,25 +2493,25 @@
       <c r="S16" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T16" s="27"/>
+      <c r="T16" s="31"/>
       <c r="U16" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V16" s="30"/>
+      <c r="V16" s="24"/>
       <c r="W16" s="8"/>
       <c r="X16" s="8"/>
       <c r="Y16" s="21"/>
       <c r="Z16" s="8"/>
       <c r="AA16" s="8"/>
       <c r="AB16" s="8"/>
-      <c r="AC16" s="30"/>
+      <c r="AC16" s="24"/>
       <c r="AD16" s="8"/>
       <c r="AE16" s="8"/>
       <c r="AF16" s="21"/>
       <c r="AG16" s="8"/>
       <c r="AH16" s="8"/>
       <c r="AI16" s="8"/>
-      <c r="AJ16" s="30"/>
+      <c r="AJ16" s="24"/>
       <c r="AK16" s="5">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -2520,12 +2520,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AM16" s="22" t="s">
+      <c r="AM16" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="AN16" s="23"/>
-      <c r="AO16" s="23"/>
-      <c r="AP16" s="24"/>
+      <c r="AN16" s="27"/>
+      <c r="AO16" s="27"/>
+      <c r="AP16" s="28"/>
     </row>
     <row r="17" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
@@ -2549,7 +2549,7 @@
       <c r="G17" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H17" s="30"/>
+      <c r="H17" s="24"/>
       <c r="I17" s="20" t="s">
         <v>122</v>
       </c>
@@ -2565,8 +2565,8 @@
       <c r="M17" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N17" s="31"/>
-      <c r="O17" s="30"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="24"/>
       <c r="P17" s="8" t="s">
         <v>122</v>
       </c>
@@ -2579,25 +2579,25 @@
       <c r="S17" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="T17" s="27"/>
+      <c r="T17" s="31"/>
       <c r="U17" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V17" s="30"/>
+      <c r="V17" s="24"/>
       <c r="W17" s="8"/>
       <c r="X17" s="8"/>
       <c r="Y17" s="21"/>
       <c r="Z17" s="8"/>
       <c r="AA17" s="8"/>
       <c r="AB17" s="8"/>
-      <c r="AC17" s="30"/>
+      <c r="AC17" s="24"/>
       <c r="AD17" s="8"/>
       <c r="AE17" s="8"/>
       <c r="AF17" s="21"/>
       <c r="AG17" s="8"/>
       <c r="AH17" s="8"/>
       <c r="AI17" s="8"/>
-      <c r="AJ17" s="30"/>
+      <c r="AJ17" s="24"/>
       <c r="AK17" s="5">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -2641,7 +2641,7 @@
       <c r="G18" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="H18" s="30"/>
+      <c r="H18" s="24"/>
       <c r="I18" s="20" t="s">
         <v>123</v>
       </c>
@@ -2657,8 +2657,8 @@
       <c r="M18" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N18" s="31"/>
-      <c r="O18" s="30"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="24"/>
       <c r="P18" s="8" t="s">
         <v>122</v>
       </c>
@@ -2671,25 +2671,25 @@
       <c r="S18" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="T18" s="27"/>
+      <c r="T18" s="31"/>
       <c r="U18" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="V18" s="30"/>
+      <c r="V18" s="24"/>
       <c r="W18" s="8"/>
       <c r="X18" s="8"/>
       <c r="Y18" s="21"/>
       <c r="Z18" s="8"/>
       <c r="AA18" s="8"/>
       <c r="AB18" s="8"/>
-      <c r="AC18" s="30"/>
+      <c r="AC18" s="24"/>
       <c r="AD18" s="8"/>
       <c r="AE18" s="8"/>
       <c r="AF18" s="21"/>
       <c r="AG18" s="8"/>
       <c r="AH18" s="8"/>
       <c r="AI18" s="8"/>
-      <c r="AJ18" s="30"/>
+      <c r="AJ18" s="24"/>
       <c r="AK18" s="5">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -2736,7 +2736,7 @@
       <c r="G19" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H19" s="30"/>
+      <c r="H19" s="24"/>
       <c r="I19" s="20" t="s">
         <v>122</v>
       </c>
@@ -2752,8 +2752,8 @@
       <c r="M19" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="N19" s="31"/>
-      <c r="O19" s="30"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="24"/>
       <c r="P19" s="8" t="s">
         <v>122</v>
       </c>
@@ -2766,25 +2766,25 @@
       <c r="S19" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T19" s="27"/>
+      <c r="T19" s="31"/>
       <c r="U19" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V19" s="30"/>
+      <c r="V19" s="24"/>
       <c r="W19" s="8"/>
       <c r="X19" s="8"/>
       <c r="Y19" s="21"/>
       <c r="Z19" s="8"/>
       <c r="AA19" s="8"/>
       <c r="AB19" s="8"/>
-      <c r="AC19" s="30"/>
+      <c r="AC19" s="24"/>
       <c r="AD19" s="8"/>
       <c r="AE19" s="8"/>
       <c r="AF19" s="21"/>
       <c r="AG19" s="8"/>
       <c r="AH19" s="8"/>
       <c r="AI19" s="8"/>
-      <c r="AJ19" s="30"/>
+      <c r="AJ19" s="24"/>
       <c r="AK19" s="5">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -2831,7 +2831,7 @@
       <c r="G20" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H20" s="30"/>
+      <c r="H20" s="24"/>
       <c r="I20" s="20" t="s">
         <v>122</v>
       </c>
@@ -2847,8 +2847,8 @@
       <c r="M20" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N20" s="31"/>
-      <c r="O20" s="30"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="24"/>
       <c r="P20" s="8" t="s">
         <v>123</v>
       </c>
@@ -2861,25 +2861,25 @@
       <c r="S20" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T20" s="27"/>
+      <c r="T20" s="31"/>
       <c r="U20" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V20" s="30"/>
+      <c r="V20" s="24"/>
       <c r="W20" s="8"/>
       <c r="X20" s="8"/>
       <c r="Y20" s="21"/>
       <c r="Z20" s="8"/>
       <c r="AA20" s="8"/>
       <c r="AB20" s="8"/>
-      <c r="AC20" s="30"/>
+      <c r="AC20" s="24"/>
       <c r="AD20" s="8"/>
       <c r="AE20" s="8"/>
       <c r="AF20" s="21"/>
       <c r="AG20" s="8"/>
       <c r="AH20" s="8"/>
       <c r="AI20" s="8"/>
-      <c r="AJ20" s="30"/>
+      <c r="AJ20" s="24"/>
       <c r="AK20" s="5">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -2926,7 +2926,7 @@
       <c r="G21" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H21" s="30"/>
+      <c r="H21" s="24"/>
       <c r="I21" s="20" t="s">
         <v>122</v>
       </c>
@@ -2942,8 +2942,8 @@
       <c r="M21" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N21" s="31"/>
-      <c r="O21" s="30"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="24"/>
       <c r="P21" s="8" t="s">
         <v>122</v>
       </c>
@@ -2956,25 +2956,25 @@
       <c r="S21" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="T21" s="27"/>
+      <c r="T21" s="31"/>
       <c r="U21" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V21" s="30"/>
+      <c r="V21" s="24"/>
       <c r="W21" s="8"/>
       <c r="X21" s="8"/>
       <c r="Y21" s="21"/>
       <c r="Z21" s="8"/>
       <c r="AA21" s="8"/>
       <c r="AB21" s="8"/>
-      <c r="AC21" s="30"/>
+      <c r="AC21" s="24"/>
       <c r="AD21" s="8"/>
       <c r="AE21" s="8"/>
       <c r="AF21" s="21"/>
       <c r="AG21" s="8"/>
       <c r="AH21" s="8"/>
       <c r="AI21" s="8"/>
-      <c r="AJ21" s="30"/>
+      <c r="AJ21" s="24"/>
       <c r="AK21" s="5">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -3006,7 +3006,7 @@
       <c r="G22" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H22" s="30"/>
+      <c r="H22" s="24"/>
       <c r="I22" s="20" t="s">
         <v>122</v>
       </c>
@@ -3022,8 +3022,8 @@
       <c r="M22" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N22" s="31"/>
-      <c r="O22" s="30"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="24"/>
       <c r="P22" s="8" t="s">
         <v>122</v>
       </c>
@@ -3036,25 +3036,25 @@
       <c r="S22" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="T22" s="27"/>
+      <c r="T22" s="31"/>
       <c r="U22" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V22" s="30"/>
+      <c r="V22" s="24"/>
       <c r="W22" s="8"/>
       <c r="X22" s="8"/>
       <c r="Y22" s="21"/>
       <c r="Z22" s="8"/>
       <c r="AA22" s="8"/>
       <c r="AB22" s="8"/>
-      <c r="AC22" s="30"/>
+      <c r="AC22" s="24"/>
       <c r="AD22" s="8"/>
       <c r="AE22" s="8"/>
       <c r="AF22" s="21"/>
       <c r="AG22" s="8"/>
       <c r="AH22" s="8"/>
       <c r="AI22" s="8"/>
-      <c r="AJ22" s="30"/>
+      <c r="AJ22" s="24"/>
       <c r="AK22" s="5">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -3086,7 +3086,7 @@
       <c r="G23" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H23" s="30"/>
+      <c r="H23" s="24"/>
       <c r="I23" s="20" t="s">
         <v>122</v>
       </c>
@@ -3102,8 +3102,8 @@
       <c r="M23" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N23" s="31"/>
-      <c r="O23" s="30"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="24"/>
       <c r="P23" s="8" t="s">
         <v>122</v>
       </c>
@@ -3116,25 +3116,25 @@
       <c r="S23" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T23" s="27"/>
+      <c r="T23" s="31"/>
       <c r="U23" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V23" s="30"/>
+      <c r="V23" s="24"/>
       <c r="W23" s="8"/>
       <c r="X23" s="8"/>
       <c r="Y23" s="21"/>
       <c r="Z23" s="8"/>
       <c r="AA23" s="8"/>
       <c r="AB23" s="8"/>
-      <c r="AC23" s="30"/>
+      <c r="AC23" s="24"/>
       <c r="AD23" s="8"/>
       <c r="AE23" s="8"/>
       <c r="AF23" s="21"/>
       <c r="AG23" s="8"/>
       <c r="AH23" s="8"/>
       <c r="AI23" s="8"/>
-      <c r="AJ23" s="30"/>
+      <c r="AJ23" s="24"/>
       <c r="AK23" s="5">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -3166,7 +3166,7 @@
       <c r="G24" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H24" s="30"/>
+      <c r="H24" s="24"/>
       <c r="I24" s="20" t="s">
         <v>122</v>
       </c>
@@ -3182,8 +3182,8 @@
       <c r="M24" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N24" s="31"/>
-      <c r="O24" s="30"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="24"/>
       <c r="P24" s="8" t="s">
         <v>122</v>
       </c>
@@ -3196,25 +3196,25 @@
       <c r="S24" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="T24" s="27"/>
+      <c r="T24" s="31"/>
       <c r="U24" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V24" s="30"/>
+      <c r="V24" s="24"/>
       <c r="W24" s="8"/>
       <c r="X24" s="8"/>
       <c r="Y24" s="21"/>
       <c r="Z24" s="8"/>
       <c r="AA24" s="8"/>
       <c r="AB24" s="8"/>
-      <c r="AC24" s="30"/>
+      <c r="AC24" s="24"/>
       <c r="AD24" s="8"/>
       <c r="AE24" s="8"/>
       <c r="AF24" s="21"/>
       <c r="AG24" s="8"/>
       <c r="AH24" s="8"/>
       <c r="AI24" s="8"/>
-      <c r="AJ24" s="30"/>
+      <c r="AJ24" s="24"/>
       <c r="AK24" s="5">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -3246,7 +3246,7 @@
       <c r="G25" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H25" s="30"/>
+      <c r="H25" s="24"/>
       <c r="I25" s="20" t="s">
         <v>122</v>
       </c>
@@ -3262,8 +3262,8 @@
       <c r="M25" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="N25" s="31"/>
-      <c r="O25" s="30"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="24"/>
       <c r="P25" s="8" t="s">
         <v>122</v>
       </c>
@@ -3276,25 +3276,25 @@
       <c r="S25" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="T25" s="27"/>
+      <c r="T25" s="31"/>
       <c r="U25" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V25" s="30"/>
+      <c r="V25" s="24"/>
       <c r="W25" s="8"/>
       <c r="X25" s="8"/>
       <c r="Y25" s="21"/>
       <c r="Z25" s="8"/>
       <c r="AA25" s="8"/>
       <c r="AB25" s="8"/>
-      <c r="AC25" s="30"/>
+      <c r="AC25" s="24"/>
       <c r="AD25" s="8"/>
       <c r="AE25" s="8"/>
       <c r="AF25" s="21"/>
       <c r="AG25" s="8"/>
       <c r="AH25" s="8"/>
       <c r="AI25" s="8"/>
-      <c r="AJ25" s="30"/>
+      <c r="AJ25" s="24"/>
       <c r="AK25" s="5">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -3326,7 +3326,7 @@
       <c r="G26" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H26" s="30"/>
+      <c r="H26" s="24"/>
       <c r="I26" s="20" t="s">
         <v>122</v>
       </c>
@@ -3342,8 +3342,8 @@
       <c r="M26" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N26" s="31"/>
-      <c r="O26" s="30"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="24"/>
       <c r="P26" s="8" t="s">
         <v>122</v>
       </c>
@@ -3356,25 +3356,25 @@
       <c r="S26" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="T26" s="27"/>
+      <c r="T26" s="31"/>
       <c r="U26" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V26" s="30"/>
+      <c r="V26" s="24"/>
       <c r="W26" s="8"/>
       <c r="X26" s="8"/>
       <c r="Y26" s="21"/>
       <c r="Z26" s="8"/>
       <c r="AA26" s="8"/>
       <c r="AB26" s="8"/>
-      <c r="AC26" s="30"/>
+      <c r="AC26" s="24"/>
       <c r="AD26" s="8"/>
       <c r="AE26" s="8"/>
       <c r="AF26" s="21"/>
       <c r="AG26" s="8"/>
       <c r="AH26" s="8"/>
       <c r="AI26" s="8"/>
-      <c r="AJ26" s="30"/>
+      <c r="AJ26" s="24"/>
       <c r="AK26" s="5">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -3406,7 +3406,7 @@
       <c r="G27" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H27" s="30"/>
+      <c r="H27" s="24"/>
       <c r="I27" s="20" t="s">
         <v>122</v>
       </c>
@@ -3422,8 +3422,8 @@
       <c r="M27" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="N27" s="31"/>
-      <c r="O27" s="30"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="24"/>
       <c r="P27" s="8" t="s">
         <v>122</v>
       </c>
@@ -3436,25 +3436,25 @@
       <c r="S27" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T27" s="27"/>
+      <c r="T27" s="31"/>
       <c r="U27" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V27" s="30"/>
+      <c r="V27" s="24"/>
       <c r="W27" s="8"/>
       <c r="X27" s="8"/>
       <c r="Y27" s="21"/>
       <c r="Z27" s="8"/>
       <c r="AA27" s="8"/>
       <c r="AB27" s="8"/>
-      <c r="AC27" s="30"/>
+      <c r="AC27" s="24"/>
       <c r="AD27" s="8"/>
       <c r="AE27" s="8"/>
       <c r="AF27" s="21"/>
       <c r="AG27" s="8"/>
       <c r="AH27" s="8"/>
       <c r="AI27" s="8"/>
-      <c r="AJ27" s="30"/>
+      <c r="AJ27" s="24"/>
       <c r="AK27" s="5">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -3486,7 +3486,7 @@
       <c r="G28" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H28" s="30"/>
+      <c r="H28" s="24"/>
       <c r="I28" s="20" t="s">
         <v>123</v>
       </c>
@@ -3502,8 +3502,8 @@
       <c r="M28" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N28" s="31"/>
-      <c r="O28" s="30"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="24"/>
       <c r="P28" s="8" t="s">
         <v>122</v>
       </c>
@@ -3516,25 +3516,25 @@
       <c r="S28" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T28" s="27"/>
+      <c r="T28" s="31"/>
       <c r="U28" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V28" s="30"/>
+      <c r="V28" s="24"/>
       <c r="W28" s="8"/>
       <c r="X28" s="8"/>
       <c r="Y28" s="21"/>
       <c r="Z28" s="8"/>
       <c r="AA28" s="8"/>
       <c r="AB28" s="8"/>
-      <c r="AC28" s="30"/>
+      <c r="AC28" s="24"/>
       <c r="AD28" s="8"/>
       <c r="AE28" s="8"/>
       <c r="AF28" s="21"/>
       <c r="AG28" s="8"/>
       <c r="AH28" s="8"/>
       <c r="AI28" s="8"/>
-      <c r="AJ28" s="30"/>
+      <c r="AJ28" s="24"/>
       <c r="AK28" s="5">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -3566,7 +3566,7 @@
       <c r="G29" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H29" s="30"/>
+      <c r="H29" s="24"/>
       <c r="I29" s="20" t="s">
         <v>122</v>
       </c>
@@ -3582,8 +3582,8 @@
       <c r="M29" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N29" s="31"/>
-      <c r="O29" s="30"/>
+      <c r="N29" s="25"/>
+      <c r="O29" s="24"/>
       <c r="P29" s="8" t="s">
         <v>122</v>
       </c>
@@ -3596,25 +3596,25 @@
       <c r="S29" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T29" s="27"/>
+      <c r="T29" s="31"/>
       <c r="U29" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V29" s="30"/>
+      <c r="V29" s="24"/>
       <c r="W29" s="8"/>
       <c r="X29" s="8"/>
       <c r="Y29" s="21"/>
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8"/>
-      <c r="AC29" s="30"/>
+      <c r="AC29" s="24"/>
       <c r="AD29" s="8"/>
       <c r="AE29" s="8"/>
       <c r="AF29" s="21"/>
       <c r="AG29" s="8"/>
       <c r="AH29" s="8"/>
       <c r="AI29" s="8"/>
-      <c r="AJ29" s="30"/>
+      <c r="AJ29" s="24"/>
       <c r="AK29" s="5">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -3646,7 +3646,7 @@
       <c r="G30" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="H30" s="30"/>
+      <c r="H30" s="24"/>
       <c r="I30" s="20" t="s">
         <v>123</v>
       </c>
@@ -3662,8 +3662,8 @@
       <c r="M30" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N30" s="31"/>
-      <c r="O30" s="30"/>
+      <c r="N30" s="25"/>
+      <c r="O30" s="24"/>
       <c r="P30" s="8" t="s">
         <v>122</v>
       </c>
@@ -3676,25 +3676,25 @@
       <c r="S30" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T30" s="27"/>
+      <c r="T30" s="31"/>
       <c r="U30" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V30" s="30"/>
+      <c r="V30" s="24"/>
       <c r="W30" s="8"/>
       <c r="X30" s="8"/>
       <c r="Y30" s="21"/>
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8"/>
-      <c r="AC30" s="30"/>
+      <c r="AC30" s="24"/>
       <c r="AD30" s="8"/>
       <c r="AE30" s="8"/>
       <c r="AF30" s="21"/>
       <c r="AG30" s="8"/>
       <c r="AH30" s="8"/>
       <c r="AI30" s="8"/>
-      <c r="AJ30" s="30"/>
+      <c r="AJ30" s="24"/>
       <c r="AK30" s="5">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -3726,7 +3726,7 @@
       <c r="G31" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H31" s="30"/>
+      <c r="H31" s="24"/>
       <c r="I31" s="20" t="s">
         <v>122</v>
       </c>
@@ -3742,8 +3742,8 @@
       <c r="M31" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="N31" s="31"/>
-      <c r="O31" s="30"/>
+      <c r="N31" s="25"/>
+      <c r="O31" s="24"/>
       <c r="P31" s="8" t="s">
         <v>123</v>
       </c>
@@ -3756,25 +3756,25 @@
       <c r="S31" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T31" s="27"/>
+      <c r="T31" s="31"/>
       <c r="U31" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="V31" s="30"/>
+      <c r="V31" s="24"/>
       <c r="W31" s="8"/>
       <c r="X31" s="8"/>
       <c r="Y31" s="21"/>
       <c r="Z31" s="8"/>
       <c r="AA31" s="8"/>
       <c r="AB31" s="8"/>
-      <c r="AC31" s="30"/>
+      <c r="AC31" s="24"/>
       <c r="AD31" s="8"/>
       <c r="AE31" s="8"/>
       <c r="AF31" s="21"/>
       <c r="AG31" s="8"/>
       <c r="AH31" s="8"/>
       <c r="AI31" s="8"/>
-      <c r="AJ31" s="30"/>
+      <c r="AJ31" s="24"/>
       <c r="AK31" s="5">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -3806,7 +3806,7 @@
       <c r="G32" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H32" s="30"/>
+      <c r="H32" s="24"/>
       <c r="I32" s="20" t="s">
         <v>123</v>
       </c>
@@ -3822,8 +3822,8 @@
       <c r="M32" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N32" s="31"/>
-      <c r="O32" s="30"/>
+      <c r="N32" s="25"/>
+      <c r="O32" s="24"/>
       <c r="P32" s="8" t="s">
         <v>122</v>
       </c>
@@ -3836,25 +3836,25 @@
       <c r="S32" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="T32" s="27"/>
+      <c r="T32" s="31"/>
       <c r="U32" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V32" s="30"/>
+      <c r="V32" s="24"/>
       <c r="W32" s="8"/>
       <c r="X32" s="8"/>
       <c r="Y32" s="21"/>
       <c r="Z32" s="8"/>
       <c r="AA32" s="8"/>
       <c r="AB32" s="8"/>
-      <c r="AC32" s="30"/>
+      <c r="AC32" s="24"/>
       <c r="AD32" s="8"/>
       <c r="AE32" s="8"/>
       <c r="AF32" s="21"/>
       <c r="AG32" s="8"/>
       <c r="AH32" s="8"/>
       <c r="AI32" s="8"/>
-      <c r="AJ32" s="30"/>
+      <c r="AJ32" s="24"/>
       <c r="AK32" s="5">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -3886,7 +3886,7 @@
       <c r="G33" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H33" s="30"/>
+      <c r="H33" s="24"/>
       <c r="I33" s="20" t="s">
         <v>122</v>
       </c>
@@ -3902,8 +3902,8 @@
       <c r="M33" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N33" s="31"/>
-      <c r="O33" s="30"/>
+      <c r="N33" s="25"/>
+      <c r="O33" s="24"/>
       <c r="P33" s="8" t="s">
         <v>122</v>
       </c>
@@ -3916,25 +3916,25 @@
       <c r="S33" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T33" s="27"/>
+      <c r="T33" s="31"/>
       <c r="U33" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V33" s="30"/>
+      <c r="V33" s="24"/>
       <c r="W33" s="8"/>
       <c r="X33" s="8"/>
       <c r="Y33" s="21"/>
       <c r="Z33" s="8"/>
       <c r="AA33" s="8"/>
       <c r="AB33" s="8"/>
-      <c r="AC33" s="30"/>
+      <c r="AC33" s="24"/>
       <c r="AD33" s="8"/>
       <c r="AE33" s="8"/>
       <c r="AF33" s="21"/>
       <c r="AG33" s="8"/>
       <c r="AH33" s="8"/>
       <c r="AI33" s="8"/>
-      <c r="AJ33" s="30"/>
+      <c r="AJ33" s="24"/>
       <c r="AK33" s="5">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -3966,7 +3966,7 @@
       <c r="G34" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H34" s="30"/>
+      <c r="H34" s="24"/>
       <c r="I34" s="20" t="s">
         <v>122</v>
       </c>
@@ -3982,8 +3982,8 @@
       <c r="M34" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N34" s="31"/>
-      <c r="O34" s="30"/>
+      <c r="N34" s="25"/>
+      <c r="O34" s="24"/>
       <c r="P34" s="8" t="s">
         <v>122</v>
       </c>
@@ -3996,25 +3996,25 @@
       <c r="S34" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T34" s="27"/>
+      <c r="T34" s="31"/>
       <c r="U34" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V34" s="30"/>
+      <c r="V34" s="24"/>
       <c r="W34" s="8"/>
       <c r="X34" s="8"/>
       <c r="Y34" s="21"/>
       <c r="Z34" s="8"/>
       <c r="AA34" s="8"/>
       <c r="AB34" s="8"/>
-      <c r="AC34" s="30"/>
+      <c r="AC34" s="24"/>
       <c r="AD34" s="8"/>
       <c r="AE34" s="8"/>
       <c r="AF34" s="21"/>
       <c r="AG34" s="8"/>
       <c r="AH34" s="8"/>
       <c r="AI34" s="8"/>
-      <c r="AJ34" s="30"/>
+      <c r="AJ34" s="24"/>
       <c r="AK34" s="5">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -4046,7 +4046,7 @@
       <c r="G35" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H35" s="30"/>
+      <c r="H35" s="24"/>
       <c r="I35" s="20" t="s">
         <v>122</v>
       </c>
@@ -4062,8 +4062,8 @@
       <c r="M35" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N35" s="31"/>
-      <c r="O35" s="30"/>
+      <c r="N35" s="25"/>
+      <c r="O35" s="24"/>
       <c r="P35" s="8" t="s">
         <v>122</v>
       </c>
@@ -4076,25 +4076,25 @@
       <c r="S35" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="T35" s="27"/>
+      <c r="T35" s="31"/>
       <c r="U35" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V35" s="30"/>
+      <c r="V35" s="24"/>
       <c r="W35" s="8"/>
       <c r="X35" s="8"/>
       <c r="Y35" s="21"/>
       <c r="Z35" s="8"/>
       <c r="AA35" s="8"/>
       <c r="AB35" s="8"/>
-      <c r="AC35" s="30"/>
+      <c r="AC35" s="24"/>
       <c r="AD35" s="8"/>
       <c r="AE35" s="8"/>
       <c r="AF35" s="21"/>
       <c r="AG35" s="8"/>
       <c r="AH35" s="8"/>
       <c r="AI35" s="8"/>
-      <c r="AJ35" s="30"/>
+      <c r="AJ35" s="24"/>
       <c r="AK35" s="5">
         <f t="shared" ref="AK35:AK52" si="4">COUNTIF(F35:AJ35,"P")</f>
         <v>11</v>
@@ -4126,7 +4126,7 @@
       <c r="G36" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H36" s="30"/>
+      <c r="H36" s="24"/>
       <c r="I36" s="20" t="s">
         <v>122</v>
       </c>
@@ -4142,8 +4142,8 @@
       <c r="M36" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N36" s="31"/>
-      <c r="O36" s="30"/>
+      <c r="N36" s="25"/>
+      <c r="O36" s="24"/>
       <c r="P36" s="8" t="s">
         <v>122</v>
       </c>
@@ -4156,25 +4156,25 @@
       <c r="S36" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="T36" s="27"/>
+      <c r="T36" s="31"/>
       <c r="U36" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V36" s="30"/>
+      <c r="V36" s="24"/>
       <c r="W36" s="8"/>
       <c r="X36" s="8"/>
       <c r="Y36" s="21"/>
       <c r="Z36" s="8"/>
       <c r="AA36" s="8"/>
       <c r="AB36" s="8"/>
-      <c r="AC36" s="30"/>
+      <c r="AC36" s="24"/>
       <c r="AD36" s="8"/>
       <c r="AE36" s="8"/>
       <c r="AF36" s="21"/>
       <c r="AG36" s="8"/>
       <c r="AH36" s="8"/>
       <c r="AI36" s="8"/>
-      <c r="AJ36" s="30"/>
+      <c r="AJ36" s="24"/>
       <c r="AK36" s="5">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -4206,7 +4206,7 @@
       <c r="G37" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H37" s="30"/>
+      <c r="H37" s="24"/>
       <c r="I37" s="20" t="s">
         <v>122</v>
       </c>
@@ -4222,8 +4222,8 @@
       <c r="M37" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N37" s="31"/>
-      <c r="O37" s="30"/>
+      <c r="N37" s="25"/>
+      <c r="O37" s="24"/>
       <c r="P37" s="8" t="s">
         <v>122</v>
       </c>
@@ -4236,25 +4236,25 @@
       <c r="S37" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="T37" s="27"/>
+      <c r="T37" s="31"/>
       <c r="U37" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="V37" s="30"/>
+      <c r="V37" s="24"/>
       <c r="W37" s="8"/>
       <c r="X37" s="8"/>
       <c r="Y37" s="21"/>
       <c r="Z37" s="8"/>
       <c r="AA37" s="8"/>
       <c r="AB37" s="8"/>
-      <c r="AC37" s="30"/>
+      <c r="AC37" s="24"/>
       <c r="AD37" s="8"/>
       <c r="AE37" s="8"/>
       <c r="AF37" s="21"/>
       <c r="AG37" s="8"/>
       <c r="AH37" s="8"/>
       <c r="AI37" s="8"/>
-      <c r="AJ37" s="30"/>
+      <c r="AJ37" s="24"/>
       <c r="AK37" s="5">
         <f t="shared" si="4"/>
         <v>8</v>
@@ -4286,7 +4286,7 @@
       <c r="G38" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="H38" s="30"/>
+      <c r="H38" s="24"/>
       <c r="I38" s="20" t="s">
         <v>122</v>
       </c>
@@ -4302,8 +4302,8 @@
       <c r="M38" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="N38" s="31"/>
-      <c r="O38" s="30"/>
+      <c r="N38" s="25"/>
+      <c r="O38" s="24"/>
       <c r="P38" s="8" t="s">
         <v>122</v>
       </c>
@@ -4316,25 +4316,25 @@
       <c r="S38" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="T38" s="27"/>
+      <c r="T38" s="31"/>
       <c r="U38" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V38" s="30"/>
+      <c r="V38" s="24"/>
       <c r="W38" s="8"/>
       <c r="X38" s="8"/>
       <c r="Y38" s="21"/>
       <c r="Z38" s="8"/>
       <c r="AA38" s="8"/>
       <c r="AB38" s="8"/>
-      <c r="AC38" s="30"/>
+      <c r="AC38" s="24"/>
       <c r="AD38" s="8"/>
       <c r="AE38" s="8"/>
       <c r="AF38" s="21"/>
       <c r="AG38" s="8"/>
       <c r="AH38" s="8"/>
       <c r="AI38" s="8"/>
-      <c r="AJ38" s="30"/>
+      <c r="AJ38" s="24"/>
       <c r="AK38" s="5">
         <f t="shared" si="4"/>
         <v>8</v>
@@ -4366,7 +4366,7 @@
       <c r="G39" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="H39" s="30"/>
+      <c r="H39" s="24"/>
       <c r="I39" s="20" t="s">
         <v>123</v>
       </c>
@@ -4382,8 +4382,8 @@
       <c r="M39" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N39" s="31"/>
-      <c r="O39" s="30"/>
+      <c r="N39" s="25"/>
+      <c r="O39" s="24"/>
       <c r="P39" s="8" t="s">
         <v>122</v>
       </c>
@@ -4396,25 +4396,25 @@
       <c r="S39" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T39" s="27"/>
+      <c r="T39" s="31"/>
       <c r="U39" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="V39" s="30"/>
+      <c r="V39" s="24"/>
       <c r="W39" s="8"/>
       <c r="X39" s="8"/>
       <c r="Y39" s="21"/>
       <c r="Z39" s="8"/>
       <c r="AA39" s="8"/>
       <c r="AB39" s="8"/>
-      <c r="AC39" s="30"/>
+      <c r="AC39" s="24"/>
       <c r="AD39" s="8"/>
       <c r="AE39" s="8"/>
       <c r="AF39" s="21"/>
       <c r="AG39" s="8"/>
       <c r="AH39" s="8"/>
       <c r="AI39" s="8"/>
-      <c r="AJ39" s="30"/>
+      <c r="AJ39" s="24"/>
       <c r="AK39" s="5">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -4446,7 +4446,7 @@
       <c r="G40" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H40" s="30"/>
+      <c r="H40" s="24"/>
       <c r="I40" s="20" t="s">
         <v>122</v>
       </c>
@@ -4462,8 +4462,8 @@
       <c r="M40" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N40" s="31"/>
-      <c r="O40" s="30"/>
+      <c r="N40" s="25"/>
+      <c r="O40" s="24"/>
       <c r="P40" s="8" t="s">
         <v>122</v>
       </c>
@@ -4476,25 +4476,25 @@
       <c r="S40" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T40" s="27"/>
+      <c r="T40" s="31"/>
       <c r="U40" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V40" s="30"/>
+      <c r="V40" s="24"/>
       <c r="W40" s="8"/>
       <c r="X40" s="8"/>
       <c r="Y40" s="21"/>
       <c r="Z40" s="8"/>
       <c r="AA40" s="8"/>
       <c r="AB40" s="8"/>
-      <c r="AC40" s="30"/>
+      <c r="AC40" s="24"/>
       <c r="AD40" s="8"/>
       <c r="AE40" s="8"/>
       <c r="AF40" s="21"/>
       <c r="AG40" s="8"/>
       <c r="AH40" s="8"/>
       <c r="AI40" s="8"/>
-      <c r="AJ40" s="30"/>
+      <c r="AJ40" s="24"/>
       <c r="AK40" s="5">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -4524,7 +4524,7 @@
       <c r="G41" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H41" s="30"/>
+      <c r="H41" s="24"/>
       <c r="I41" s="20" t="s">
         <v>122</v>
       </c>
@@ -4540,8 +4540,8 @@
       <c r="M41" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N41" s="31"/>
-      <c r="O41" s="30"/>
+      <c r="N41" s="25"/>
+      <c r="O41" s="24"/>
       <c r="P41" s="8" t="s">
         <v>122</v>
       </c>
@@ -4554,25 +4554,25 @@
       <c r="S41" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T41" s="27"/>
+      <c r="T41" s="31"/>
       <c r="U41" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V41" s="30"/>
+      <c r="V41" s="24"/>
       <c r="W41" s="8"/>
       <c r="X41" s="8"/>
       <c r="Y41" s="21"/>
       <c r="Z41" s="8"/>
       <c r="AA41" s="8"/>
       <c r="AB41" s="8"/>
-      <c r="AC41" s="30"/>
+      <c r="AC41" s="24"/>
       <c r="AD41" s="8"/>
       <c r="AE41" s="8"/>
       <c r="AF41" s="21"/>
       <c r="AG41" s="8"/>
       <c r="AH41" s="8"/>
       <c r="AI41" s="8"/>
-      <c r="AJ41" s="30"/>
+      <c r="AJ41" s="24"/>
       <c r="AK41" s="5">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -4604,7 +4604,7 @@
       <c r="G42" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H42" s="30"/>
+      <c r="H42" s="24"/>
       <c r="I42" s="20" t="s">
         <v>122</v>
       </c>
@@ -4620,8 +4620,8 @@
       <c r="M42" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N42" s="31"/>
-      <c r="O42" s="30"/>
+      <c r="N42" s="25"/>
+      <c r="O42" s="24"/>
       <c r="P42" s="8" t="s">
         <v>122</v>
       </c>
@@ -4634,25 +4634,25 @@
       <c r="S42" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T42" s="27"/>
+      <c r="T42" s="31"/>
       <c r="U42" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V42" s="30"/>
+      <c r="V42" s="24"/>
       <c r="W42" s="8"/>
       <c r="X42" s="8"/>
       <c r="Y42" s="21"/>
       <c r="Z42" s="8"/>
       <c r="AA42" s="8"/>
       <c r="AB42" s="8"/>
-      <c r="AC42" s="30"/>
+      <c r="AC42" s="24"/>
       <c r="AD42" s="8"/>
       <c r="AE42" s="8"/>
       <c r="AF42" s="21"/>
       <c r="AG42" s="8"/>
       <c r="AH42" s="8"/>
       <c r="AI42" s="8"/>
-      <c r="AJ42" s="30"/>
+      <c r="AJ42" s="24"/>
       <c r="AK42" s="5">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -4684,7 +4684,7 @@
       <c r="G43" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H43" s="30"/>
+      <c r="H43" s="24"/>
       <c r="I43" s="20" t="s">
         <v>122</v>
       </c>
@@ -4700,8 +4700,8 @@
       <c r="M43" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N43" s="31"/>
-      <c r="O43" s="30"/>
+      <c r="N43" s="25"/>
+      <c r="O43" s="24"/>
       <c r="P43" s="8" t="s">
         <v>122</v>
       </c>
@@ -4714,25 +4714,25 @@
       <c r="S43" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T43" s="27"/>
+      <c r="T43" s="31"/>
       <c r="U43" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V43" s="30"/>
+      <c r="V43" s="24"/>
       <c r="W43" s="8"/>
       <c r="X43" s="8"/>
       <c r="Y43" s="21"/>
       <c r="Z43" s="8"/>
       <c r="AA43" s="8"/>
       <c r="AB43" s="8"/>
-      <c r="AC43" s="30"/>
+      <c r="AC43" s="24"/>
       <c r="AD43" s="8"/>
       <c r="AE43" s="8"/>
       <c r="AF43" s="21"/>
       <c r="AG43" s="8"/>
       <c r="AH43" s="8"/>
       <c r="AI43" s="8"/>
-      <c r="AJ43" s="30"/>
+      <c r="AJ43" s="24"/>
       <c r="AK43" s="5">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -4764,7 +4764,7 @@
       <c r="G44" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="H44" s="30"/>
+      <c r="H44" s="24"/>
       <c r="I44" s="20" t="s">
         <v>122</v>
       </c>
@@ -4780,8 +4780,8 @@
       <c r="M44" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N44" s="31"/>
-      <c r="O44" s="30"/>
+      <c r="N44" s="25"/>
+      <c r="O44" s="24"/>
       <c r="P44" s="8" t="s">
         <v>122</v>
       </c>
@@ -4794,25 +4794,25 @@
       <c r="S44" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T44" s="27"/>
+      <c r="T44" s="31"/>
       <c r="U44" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V44" s="30"/>
+      <c r="V44" s="24"/>
       <c r="W44" s="8"/>
       <c r="X44" s="8"/>
       <c r="Y44" s="21"/>
       <c r="Z44" s="8"/>
       <c r="AA44" s="8"/>
       <c r="AB44" s="8"/>
-      <c r="AC44" s="30"/>
+      <c r="AC44" s="24"/>
       <c r="AD44" s="8"/>
       <c r="AE44" s="8"/>
       <c r="AF44" s="21"/>
       <c r="AG44" s="8"/>
       <c r="AH44" s="8"/>
       <c r="AI44" s="8"/>
-      <c r="AJ44" s="30"/>
+      <c r="AJ44" s="24"/>
       <c r="AK44" s="5">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -4844,7 +4844,7 @@
       <c r="G45" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H45" s="30"/>
+      <c r="H45" s="24"/>
       <c r="I45" s="20" t="s">
         <v>122</v>
       </c>
@@ -4860,8 +4860,8 @@
       <c r="M45" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N45" s="31"/>
-      <c r="O45" s="30"/>
+      <c r="N45" s="25"/>
+      <c r="O45" s="24"/>
       <c r="P45" s="8" t="s">
         <v>122</v>
       </c>
@@ -4874,25 +4874,25 @@
       <c r="S45" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T45" s="27"/>
+      <c r="T45" s="31"/>
       <c r="U45" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V45" s="30"/>
+      <c r="V45" s="24"/>
       <c r="W45" s="8"/>
       <c r="X45" s="8"/>
       <c r="Y45" s="21"/>
       <c r="Z45" s="8"/>
       <c r="AA45" s="8"/>
       <c r="AB45" s="8"/>
-      <c r="AC45" s="30"/>
+      <c r="AC45" s="24"/>
       <c r="AD45" s="8"/>
       <c r="AE45" s="8"/>
       <c r="AF45" s="21"/>
       <c r="AG45" s="8"/>
       <c r="AH45" s="8"/>
       <c r="AI45" s="8"/>
-      <c r="AJ45" s="30"/>
+      <c r="AJ45" s="24"/>
       <c r="AK45" s="5">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -4924,7 +4924,7 @@
       <c r="G46" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H46" s="30"/>
+      <c r="H46" s="24"/>
       <c r="I46" s="20" t="s">
         <v>122</v>
       </c>
@@ -4940,8 +4940,8 @@
       <c r="M46" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N46" s="31"/>
-      <c r="O46" s="30"/>
+      <c r="N46" s="25"/>
+      <c r="O46" s="24"/>
       <c r="P46" s="8" t="s">
         <v>122</v>
       </c>
@@ -4954,25 +4954,25 @@
       <c r="S46" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T46" s="27"/>
+      <c r="T46" s="31"/>
       <c r="U46" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V46" s="30"/>
+      <c r="V46" s="24"/>
       <c r="W46" s="8"/>
       <c r="X46" s="8"/>
       <c r="Y46" s="21"/>
       <c r="Z46" s="8"/>
       <c r="AA46" s="8"/>
       <c r="AB46" s="8"/>
-      <c r="AC46" s="30"/>
+      <c r="AC46" s="24"/>
       <c r="AD46" s="8"/>
       <c r="AE46" s="8"/>
       <c r="AF46" s="21"/>
       <c r="AG46" s="8"/>
       <c r="AH46" s="8"/>
       <c r="AI46" s="8"/>
-      <c r="AJ46" s="30"/>
+      <c r="AJ46" s="24"/>
       <c r="AK46" s="5">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -5002,7 +5002,7 @@
       <c r="G47" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H47" s="30"/>
+      <c r="H47" s="24"/>
       <c r="I47" s="20" t="s">
         <v>122</v>
       </c>
@@ -5018,8 +5018,8 @@
       <c r="M47" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N47" s="31"/>
-      <c r="O47" s="30"/>
+      <c r="N47" s="25"/>
+      <c r="O47" s="24"/>
       <c r="P47" s="8" t="s">
         <v>122</v>
       </c>
@@ -5032,25 +5032,25 @@
       <c r="S47" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T47" s="27"/>
+      <c r="T47" s="31"/>
       <c r="U47" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V47" s="30"/>
+      <c r="V47" s="24"/>
       <c r="W47" s="8"/>
       <c r="X47" s="8"/>
       <c r="Y47" s="21"/>
       <c r="Z47" s="8"/>
       <c r="AA47" s="8"/>
       <c r="AB47" s="8"/>
-      <c r="AC47" s="30"/>
+      <c r="AC47" s="24"/>
       <c r="AD47" s="8"/>
       <c r="AE47" s="8"/>
       <c r="AF47" s="21"/>
       <c r="AG47" s="8"/>
       <c r="AH47" s="8"/>
       <c r="AI47" s="8"/>
-      <c r="AJ47" s="30"/>
+      <c r="AJ47" s="24"/>
       <c r="AK47" s="5">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -5082,7 +5082,7 @@
       <c r="G48" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H48" s="30"/>
+      <c r="H48" s="24"/>
       <c r="I48" s="20" t="s">
         <v>122</v>
       </c>
@@ -5098,8 +5098,8 @@
       <c r="M48" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N48" s="31"/>
-      <c r="O48" s="30"/>
+      <c r="N48" s="25"/>
+      <c r="O48" s="24"/>
       <c r="P48" s="8" t="s">
         <v>122</v>
       </c>
@@ -5112,25 +5112,25 @@
       <c r="S48" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="T48" s="27"/>
+      <c r="T48" s="31"/>
       <c r="U48" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V48" s="30"/>
+      <c r="V48" s="24"/>
       <c r="W48" s="8"/>
       <c r="X48" s="8"/>
       <c r="Y48" s="21"/>
       <c r="Z48" s="8"/>
       <c r="AA48" s="8"/>
       <c r="AB48" s="8"/>
-      <c r="AC48" s="30"/>
+      <c r="AC48" s="24"/>
       <c r="AD48" s="8"/>
       <c r="AE48" s="8"/>
       <c r="AF48" s="21"/>
       <c r="AG48" s="8"/>
       <c r="AH48" s="8"/>
       <c r="AI48" s="8"/>
-      <c r="AJ48" s="30"/>
+      <c r="AJ48" s="24"/>
       <c r="AK48" s="5">
         <f t="shared" si="4"/>
         <v>9</v>
@@ -5160,7 +5160,7 @@
       <c r="G49" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H49" s="30"/>
+      <c r="H49" s="24"/>
       <c r="I49" s="20" t="s">
         <v>122</v>
       </c>
@@ -5176,8 +5176,8 @@
       <c r="M49" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N49" s="31"/>
-      <c r="O49" s="30"/>
+      <c r="N49" s="25"/>
+      <c r="O49" s="24"/>
       <c r="P49" s="8" t="s">
         <v>122</v>
       </c>
@@ -5190,25 +5190,25 @@
       <c r="S49" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T49" s="27"/>
+      <c r="T49" s="31"/>
       <c r="U49" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V49" s="30"/>
+      <c r="V49" s="24"/>
       <c r="W49" s="8"/>
       <c r="X49" s="8"/>
       <c r="Y49" s="21"/>
       <c r="Z49" s="8"/>
       <c r="AA49" s="8"/>
       <c r="AB49" s="8"/>
-      <c r="AC49" s="30"/>
+      <c r="AC49" s="24"/>
       <c r="AD49" s="8"/>
       <c r="AE49" s="8"/>
       <c r="AF49" s="21"/>
       <c r="AG49" s="8"/>
       <c r="AH49" s="8"/>
       <c r="AI49" s="8"/>
-      <c r="AJ49" s="30"/>
+      <c r="AJ49" s="24"/>
       <c r="AK49" s="5">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -5238,7 +5238,7 @@
       <c r="G50" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H50" s="30"/>
+      <c r="H50" s="24"/>
       <c r="I50" s="20" t="s">
         <v>122</v>
       </c>
@@ -5254,8 +5254,8 @@
       <c r="M50" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N50" s="31"/>
-      <c r="O50" s="30"/>
+      <c r="N50" s="25"/>
+      <c r="O50" s="24"/>
       <c r="P50" s="8" t="s">
         <v>122</v>
       </c>
@@ -5268,25 +5268,25 @@
       <c r="S50" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T50" s="27"/>
+      <c r="T50" s="31"/>
       <c r="U50" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="V50" s="30"/>
+      <c r="V50" s="24"/>
       <c r="W50" s="8"/>
       <c r="X50" s="8"/>
       <c r="Y50" s="21"/>
       <c r="Z50" s="8"/>
       <c r="AA50" s="8"/>
       <c r="AB50" s="8"/>
-      <c r="AC50" s="30"/>
+      <c r="AC50" s="24"/>
       <c r="AD50" s="8"/>
       <c r="AE50" s="8"/>
       <c r="AF50" s="21"/>
       <c r="AG50" s="8"/>
       <c r="AH50" s="8"/>
       <c r="AI50" s="8"/>
-      <c r="AJ50" s="30"/>
+      <c r="AJ50" s="24"/>
       <c r="AK50" s="5">
         <f t="shared" si="4"/>
         <v>8</v>
@@ -5316,7 +5316,7 @@
       <c r="G51" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H51" s="30"/>
+      <c r="H51" s="24"/>
       <c r="I51" s="20" t="s">
         <v>122</v>
       </c>
@@ -5332,8 +5332,8 @@
       <c r="M51" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N51" s="31"/>
-      <c r="O51" s="30"/>
+      <c r="N51" s="25"/>
+      <c r="O51" s="24"/>
       <c r="P51" s="8" t="s">
         <v>122</v>
       </c>
@@ -5346,25 +5346,25 @@
       <c r="S51" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T51" s="27"/>
+      <c r="T51" s="31"/>
       <c r="U51" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V51" s="30"/>
+      <c r="V51" s="24"/>
       <c r="W51" s="8"/>
       <c r="X51" s="8"/>
       <c r="Y51" s="21"/>
       <c r="Z51" s="8"/>
       <c r="AA51" s="8"/>
       <c r="AB51" s="8"/>
-      <c r="AC51" s="30"/>
+      <c r="AC51" s="24"/>
       <c r="AD51" s="8"/>
       <c r="AE51" s="8"/>
       <c r="AF51" s="21"/>
       <c r="AG51" s="8"/>
       <c r="AH51" s="8"/>
       <c r="AI51" s="8"/>
-      <c r="AJ51" s="30"/>
+      <c r="AJ51" s="24"/>
       <c r="AK51" s="5">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -5394,7 +5394,7 @@
       <c r="G52" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H52" s="30"/>
+      <c r="H52" s="24"/>
       <c r="I52" s="20" t="s">
         <v>122</v>
       </c>
@@ -5410,8 +5410,8 @@
       <c r="M52" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N52" s="31"/>
-      <c r="O52" s="30"/>
+      <c r="N52" s="25"/>
+      <c r="O52" s="24"/>
       <c r="P52" s="8" t="s">
         <v>122</v>
       </c>
@@ -5424,25 +5424,25 @@
       <c r="S52" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="T52" s="27"/>
+      <c r="T52" s="31"/>
       <c r="U52" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V52" s="30"/>
+      <c r="V52" s="24"/>
       <c r="W52" s="8"/>
       <c r="X52" s="8"/>
       <c r="Y52" s="21"/>
       <c r="Z52" s="8"/>
       <c r="AA52" s="8"/>
       <c r="AB52" s="8"/>
-      <c r="AC52" s="30"/>
+      <c r="AC52" s="24"/>
       <c r="AD52" s="8"/>
       <c r="AE52" s="8"/>
       <c r="AF52" s="21"/>
       <c r="AG52" s="8"/>
       <c r="AH52" s="8"/>
       <c r="AI52" s="8"/>
-      <c r="AJ52" s="30"/>
+      <c r="AJ52" s="24"/>
       <c r="AK52" s="5">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -5472,7 +5472,7 @@
       <c r="G53" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H53" s="30"/>
+      <c r="H53" s="24"/>
       <c r="I53" s="20" t="s">
         <v>123</v>
       </c>
@@ -5488,8 +5488,8 @@
       <c r="M53" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="N53" s="31"/>
-      <c r="O53" s="30"/>
+      <c r="N53" s="25"/>
+      <c r="O53" s="24"/>
       <c r="P53" s="8" t="s">
         <v>122</v>
       </c>
@@ -5502,25 +5502,25 @@
       <c r="S53" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T53" s="27"/>
+      <c r="T53" s="31"/>
       <c r="U53" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="V53" s="30"/>
+      <c r="V53" s="24"/>
       <c r="W53" s="8"/>
       <c r="X53" s="8"/>
       <c r="Y53" s="21"/>
       <c r="Z53" s="8"/>
       <c r="AA53" s="8"/>
       <c r="AB53" s="8"/>
-      <c r="AC53" s="30"/>
+      <c r="AC53" s="24"/>
       <c r="AD53" s="8"/>
       <c r="AE53" s="8"/>
       <c r="AF53" s="21"/>
       <c r="AG53" s="8"/>
       <c r="AH53" s="8"/>
       <c r="AI53" s="8"/>
-      <c r="AJ53" s="30"/>
+      <c r="AJ53" s="24"/>
       <c r="AK53" s="5">
         <f t="shared" ref="AK53:AK54" si="6">COUNTIF(F53:AJ53,"P")</f>
         <v>8</v>
@@ -5550,7 +5550,7 @@
       <c r="G54" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H54" s="30"/>
+      <c r="H54" s="24"/>
       <c r="I54" s="20" t="s">
         <v>122</v>
       </c>
@@ -5566,8 +5566,8 @@
       <c r="M54" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N54" s="31"/>
-      <c r="O54" s="30"/>
+      <c r="N54" s="25"/>
+      <c r="O54" s="24"/>
       <c r="P54" s="8" t="s">
         <v>122</v>
       </c>
@@ -5580,25 +5580,25 @@
       <c r="S54" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T54" s="27"/>
+      <c r="T54" s="31"/>
       <c r="U54" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V54" s="30"/>
+      <c r="V54" s="24"/>
       <c r="W54" s="8"/>
       <c r="X54" s="8"/>
       <c r="Y54" s="21"/>
       <c r="Z54" s="8"/>
       <c r="AA54" s="8"/>
       <c r="AB54" s="8"/>
-      <c r="AC54" s="30"/>
+      <c r="AC54" s="24"/>
       <c r="AD54" s="8"/>
       <c r="AE54" s="8"/>
       <c r="AF54" s="21"/>
       <c r="AG54" s="8"/>
       <c r="AH54" s="8"/>
       <c r="AI54" s="8"/>
-      <c r="AJ54" s="30"/>
+      <c r="AJ54" s="24"/>
       <c r="AK54" s="5">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -5626,7 +5626,7 @@
       <c r="G55" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H55" s="30"/>
+      <c r="H55" s="24"/>
       <c r="I55" s="20" t="s">
         <v>122</v>
       </c>
@@ -5642,8 +5642,8 @@
       <c r="M55" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N55" s="31"/>
-      <c r="O55" s="30"/>
+      <c r="N55" s="25"/>
+      <c r="O55" s="24"/>
       <c r="P55" s="8" t="s">
         <v>123</v>
       </c>
@@ -5656,25 +5656,25 @@
       <c r="S55" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T55" s="27"/>
+      <c r="T55" s="31"/>
       <c r="U55" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V55" s="30"/>
+      <c r="V55" s="24"/>
       <c r="W55" s="8"/>
       <c r="X55" s="8"/>
       <c r="Y55" s="21"/>
       <c r="Z55" s="8"/>
       <c r="AA55" s="8"/>
       <c r="AB55" s="8"/>
-      <c r="AC55" s="30"/>
+      <c r="AC55" s="24"/>
       <c r="AD55" s="8"/>
       <c r="AE55" s="8"/>
       <c r="AF55" s="21"/>
       <c r="AG55" s="8"/>
       <c r="AH55" s="8"/>
       <c r="AI55" s="8"/>
-      <c r="AJ55" s="30"/>
+      <c r="AJ55" s="24"/>
       <c r="AK55" s="5">
         <f t="shared" ref="AK55" si="8">COUNTIF(F55:AJ55,"P")</f>
         <v>11</v>
@@ -5702,7 +5702,7 @@
       <c r="G56" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="H56" s="30"/>
+      <c r="H56" s="24"/>
       <c r="I56" s="20" t="s">
         <v>123</v>
       </c>
@@ -5718,8 +5718,8 @@
       <c r="M56" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="N56" s="31"/>
-      <c r="O56" s="30"/>
+      <c r="N56" s="25"/>
+      <c r="O56" s="24"/>
       <c r="P56" s="8" t="s">
         <v>123</v>
       </c>
@@ -5732,25 +5732,25 @@
       <c r="S56" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="T56" s="27"/>
+      <c r="T56" s="31"/>
       <c r="U56" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="V56" s="30"/>
+      <c r="V56" s="24"/>
       <c r="W56" s="8"/>
       <c r="X56" s="8"/>
       <c r="Y56" s="21"/>
       <c r="Z56" s="8"/>
       <c r="AA56" s="8"/>
       <c r="AB56" s="8"/>
-      <c r="AC56" s="30"/>
+      <c r="AC56" s="24"/>
       <c r="AD56" s="8"/>
       <c r="AE56" s="8"/>
       <c r="AF56" s="21"/>
       <c r="AG56" s="8"/>
       <c r="AH56" s="8"/>
       <c r="AI56" s="8"/>
-      <c r="AJ56" s="30"/>
+      <c r="AJ56" s="24"/>
       <c r="AK56" s="5">
         <f t="shared" ref="AK56:AK58" si="10">COUNTIF(F56:AJ56,"P")</f>
         <v>2</v>
@@ -5780,7 +5780,7 @@
       <c r="G57" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="H57" s="30"/>
+      <c r="H57" s="24"/>
       <c r="I57" s="20" t="s">
         <v>130</v>
       </c>
@@ -5796,8 +5796,8 @@
       <c r="M57" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="N57" s="31"/>
-      <c r="O57" s="30"/>
+      <c r="N57" s="25"/>
+      <c r="O57" s="24"/>
       <c r="P57" s="8" t="s">
         <v>122</v>
       </c>
@@ -5810,25 +5810,25 @@
       <c r="S57" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T57" s="27"/>
+      <c r="T57" s="31"/>
       <c r="U57" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V57" s="30"/>
+      <c r="V57" s="24"/>
       <c r="W57" s="8"/>
       <c r="X57" s="8"/>
       <c r="Y57" s="21"/>
       <c r="Z57" s="8"/>
       <c r="AA57" s="8"/>
       <c r="AB57" s="8"/>
-      <c r="AC57" s="30"/>
+      <c r="AC57" s="24"/>
       <c r="AD57" s="8"/>
       <c r="AE57" s="8"/>
       <c r="AF57" s="21"/>
       <c r="AG57" s="8"/>
       <c r="AH57" s="8"/>
       <c r="AI57" s="8"/>
-      <c r="AJ57" s="30"/>
+      <c r="AJ57" s="24"/>
       <c r="AK57" s="5">
         <f t="shared" si="10"/>
         <v>5</v>
@@ -5858,7 +5858,7 @@
       <c r="G58" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="H58" s="30"/>
+      <c r="H58" s="24"/>
       <c r="I58" s="20" t="s">
         <v>130</v>
       </c>
@@ -5874,8 +5874,8 @@
       <c r="M58" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="N58" s="31"/>
-      <c r="O58" s="30"/>
+      <c r="N58" s="25"/>
+      <c r="O58" s="24"/>
       <c r="P58" s="8" t="s">
         <v>122</v>
       </c>
@@ -5888,25 +5888,25 @@
       <c r="S58" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="T58" s="27"/>
+      <c r="T58" s="31"/>
       <c r="U58" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="V58" s="30"/>
+      <c r="V58" s="24"/>
       <c r="W58" s="8"/>
       <c r="X58" s="8"/>
       <c r="Y58" s="21"/>
       <c r="Z58" s="8"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="30"/>
+      <c r="AC58" s="24"/>
       <c r="AD58" s="8"/>
       <c r="AE58" s="8"/>
       <c r="AF58" s="21"/>
       <c r="AG58" s="8"/>
       <c r="AH58" s="8"/>
       <c r="AI58" s="8"/>
-      <c r="AJ58" s="30"/>
+      <c r="AJ58" s="24"/>
       <c r="AK58" s="5">
         <f t="shared" si="10"/>
         <v>5</v>
@@ -5918,14 +5918,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A2:AJ2"/>
-    <mergeCell ref="A1:AJ1"/>
-    <mergeCell ref="H5:H58"/>
-    <mergeCell ref="N5:N58"/>
-    <mergeCell ref="O5:O58"/>
-    <mergeCell ref="V5:V58"/>
-    <mergeCell ref="AC5:AC58"/>
-    <mergeCell ref="AJ5:AJ58"/>
     <mergeCell ref="AM16:AP16"/>
     <mergeCell ref="AL3:AL4"/>
     <mergeCell ref="AM3:AN3"/>
@@ -5937,6 +5929,14 @@
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="T5:T58"/>
+    <mergeCell ref="A2:AJ2"/>
+    <mergeCell ref="A1:AJ1"/>
+    <mergeCell ref="H5:H58"/>
+    <mergeCell ref="N5:N58"/>
+    <mergeCell ref="O5:O58"/>
+    <mergeCell ref="V5:V58"/>
+    <mergeCell ref="AC5:AC58"/>
+    <mergeCell ref="AJ5:AJ58"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:AJ5 F6:G58 I6:M58 P6:S58 U6:U58 W6:X58 Z6:AB58 AD6:AE58 AG6:AI58 AM4:AN4">
     <cfRule type="expression" dxfId="10" priority="18">
